--- a/docs/test-cases/test-cases.xlsx
+++ b/docs/test-cases/test-cases.xlsx
@@ -420,7 +420,7 @@
     <t>Dịch vụ AI (tuỳ case)</t>
   </si>
   <si>
-    <t>AI-Services/topic-recommender :8891</t>
+    <t>AI-Services/services/topic-recommender-8891 :8891</t>
   </si>
   <si>
     <t>Hệ thống</t>

--- a/docs/test-cases/test-cases.xlsx
+++ b/docs/test-cases/test-cases.xlsx
@@ -24,9 +24,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'01-AUTH'!$A$1:$O$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'02-ADMIN'!$A$1:$O$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'02-ADMIN'!$A$1:$O$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'03-STAT'!$A$1:$O$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'04-LECT'!$A$1:$O$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'04-LECT'!$A$1:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'05-STU'!$A$1:$O$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'06-CHAT'!$A$1:$O$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'07-MOD'!$A$1:$O$28</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1721">
   <si>
     <t>Nhóm</t>
   </si>
@@ -279,7 +279,7 @@
     <t>TC-ADMIN — Nhóm 02 — Quản trị người dùng, môn học &amp; lớp học phần</t>
   </si>
   <si>
-    <t>php artisan test tests/Feature/SubjectTest.php tests/Feature/AdminClassManagementTest.php tests/Feature/ViewSmokeTest.php tests/Feature/AdminSoftDeleteTest.php</t>
+    <t>php artisan test tests/Feature/SubjectTest.php tests/Feature/AdminClassManagementTest.php tests/Feature/ClassMembershipStatusTest.php tests/Feature/ViewSmokeTest.php tests/Feature/AdminSoftDeleteTest.php</t>
   </si>
   <si>
     <t>TC-STAT — Nhóm 03 — Thống kê &amp; thông báo</t>
@@ -291,7 +291,7 @@
     <t>TC-LECT — Nhóm 04 — Giảng viên &amp; lớp học phần</t>
   </si>
   <si>
-    <t>php artisan test tests/Feature/LecturerClassTest.php tests/Feature/StudentClassDetailTest.php tests/Feature/ClassJoinTest.php</t>
+    <t>php artisan test tests/Feature/LecturerClassTest.php tests/Feature/StudentClassDetailTest.php tests/Feature/ClassJoinTest.php tests/Feature/ClassMembershipStatusTest.php</t>
   </si>
   <si>
     <t>TC-STU — Nhóm 05 — Sinh viên: nhóm &amp; đăng ký đề tài</t>
@@ -1466,7 +1466,7 @@
     <t>Sinh viên trong lớp (#5)</t>
   </si>
   <si>
-    <t>Admin thêm sinh viên vào lớp (không thêm trùng) và xóa sinh viên khỏi lớp</t>
+    <t>Admin thêm sinh viên vào lớp (không thêm trùng) và cho sinh viên RỜI lớp (xóa mềm)</t>
   </si>
   <si>
     <t>Lớp có sv1; sv3 chưa thuộc lớp</t>
@@ -1474,38 +1474,86 @@
   <si>
     <t>Thêm sv3 vào lớp
 Thêm lại sv3 (case âm)
-Xóa sv1 khỏi lớp
-Thử xóa một sv không thuộc lớp (case âm)</t>
+Cho sv1 rời lớp
+Thử cho một sv không thuộc lớp rời lớp (case âm)</t>
   </si>
   <si>
     <t>POST /admin/classes/{id}/students · POST /admin/classes/{id}/students/{studentId}/remove</t>
   </si>
   <si>
-    <t>Thêm mới OK; thêm trùng bị chặn; xóa OK; xóa sinh viên không thuộc lớp chỉ hiện cảnh báo và KHÔNG đổi dữ liệu</t>
+    <t>Thêm mới OK; thêm trùng bị chặn; cho rời lớp = XÓA MỀM (status=left) nên SV vẫn hiện ở bộ lọc "Đã rời"; SV không thuộc lớp chỉ hiện cảnh báo và KHÔNG đổi dữ liệu</t>
+  </si>
+  <si>
+    <t>tests/Feature/AdminClassManagementTest.php · tests/Feature/ClassMembershipStatusTest.php</t>
   </si>
   <si>
     <t>TC-ADMIN-20</t>
   </si>
   <si>
-    <t>Xóa trưởng nhóm khỏi lớp: chuyển quyền trưởng nhóm cho thành viên còn lại; nhóm rỗng thì giải tán; lớp khác không bị ảnh hưởng</t>
+    <t>Người CUỐI CÙNG rời lớp: giữ nhóm lại với trưởng nhóm = người cuối cùng rời (không bỏ trưởng nhóm, không giải tán nhóm); lớp khác không bị ảnh hưởng</t>
   </si>
   <si>
     <t>Nhóm Alpha (trưởng nhóm sv1 + thành viên sv3); sv1 đồng thời thuộc lớp khác</t>
   </si>
   <si>
-    <t>Xóa sv1 khỏi lớp CNTT01-K1
+    <t>Cho sv3 rời lớp (còn sv1)
 Kiểm tra nhóm Alpha
-Kiểm tra lớp còn lại của sv1
-Lặp lại với tình huống nhóm chỉ có 1 người</t>
+Cho sv1 rời lớp (người cuối cùng)
+Kiểm tra nhóm Alpha + lớp còn lại của sv1</t>
   </si>
   <si>
     <t>POST /admin/classes/{id}/students/{studentId}/remove</t>
   </si>
   <si>
-    <t>Nhóm còn thành viên ⇒ người còn lại thành trưởng nhóm; nhóm rỗng ⇒ bị giải tán; lớp khác của sv1 giữ nguyên</t>
+    <t>Còn thành viên đang học ⇒ chuyển quyền trưởng nhóm cho người đó; hết người ⇒ nhóm VẪN TỒN TẠI với leader_id = người cuối cùng rời lớp, 0 thành viên đang học; lớp khác của sv1 giữ nguyên</t>
   </si>
   <si>
     <t>TC-ADMIN-21</t>
+  </si>
+  <si>
+    <t>Sinh viên từng rời lớp quay lại (Thêm lại / nhập mã lớp): khôi phục "Đang học" và trưởng nhóm nhóm cũ được hồi sinh, KHÔNG tạo nhóm mới</t>
+  </si>
+  <si>
+    <t>sv1 từng là trưởng nhóm của nhóm Alpha trong lớp rồi rời lớp (user_classes.status = left)</t>
+  </si>
+  <si>
+    <t>Admin bấm "Thêm lại" sv1 (hoặc sv1 nhập lại mã lớp)
+Kiểm tra user_classes
+Kiểm tra nhóm Alpha
+sv1 thử tạo nhóm mới trong lớp</t>
+  </si>
+  <si>
+    <t>POST /admin/classes/{id}/students {student_ids[]} · POST /user/classes/join {class_code}</t>
+  </si>
+  <si>
+    <t>sv1 trở lại "Đang học" (left_at = null, không sinh dòng trùng); nhóm Alpha hồi sinh với sv1 là trưởng nhóm; KHÔNG tạo được nhóm mới vì vẫn thuộc nhóm cũ</t>
+  </si>
+  <si>
+    <t>tests/Feature/ClassMembershipStatusTest.php</t>
+  </si>
+  <si>
+    <t>TC-ADMIN-22</t>
+  </si>
+  <si>
+    <t>Hiển thị trạng thái Đang học / Đã rời lớp: bộ lọc + badge + nút "Cho rời lớp"/"Thêm lại"; nhóm rỗng hiện "Đã rời hết"</t>
+  </si>
+  <si>
+    <t>Lớp có 1 SV đang học, 1 SV đã rời lớp và 1 nhóm rỗng (trưởng nhóm đã rời lớp)</t>
+  </si>
+  <si>
+    <t>Mở chi tiết lớp
+Lọc "Đã rời"
+Lọc "Đang học"
+Mở tab Nhóm</t>
+  </si>
+  <si>
+    <t>GET /admin/classes/{id}?status=left | status=studying</t>
+  </si>
+  <si>
+    <t>Bộ lọc trả đúng danh sách; dòng đã rời làm xám + badge "Đã rời lớp" + nút "Thêm lại"; nhóm rỗng hiển thị 0 thành viên + badge "Đã rời hết"; header tách "x đang học · y đã rời"</t>
+  </si>
+  <si>
+    <t>TC-ADMIN-23</t>
   </si>
   <si>
     <t>Phân công giảng viên (#4)</t>
@@ -1529,7 +1577,7 @@
     <t>Danh sách sinh viên giữ nguyên ở cả 2 thao tác; chỉ pivot `user_classes` của giảng viên thay đổi</t>
   </si>
   <si>
-    <t>TC-ADMIN-22</t>
+    <t>TC-ADMIN-24</t>
   </si>
   <si>
     <t>Phân quyền lớp học phần (#4)</t>
@@ -1553,7 +1601,7 @@
     <t>GV/SV bị chuyển hướng hoặc 403 (không lộ trang quản trị); GV không xóa được sinh viên; admin mở URL cũ /classes ⇒ tự chuyển hướng về /admin/classes</t>
   </si>
   <si>
-    <t>TC-ADMIN-23</t>
+    <t>TC-ADMIN-25</t>
   </si>
   <si>
     <t>Import môn học (#3)</t>
@@ -1576,7 +1624,7 @@
     <t>Template tải được; import báo số dòng thành công; môn mới xuất hiện trong /admin/subjects với mã tự sinh</t>
   </si>
   <si>
-    <t>TC-ADMIN-24</t>
+    <t>TC-ADMIN-26</t>
   </si>
   <si>
     <t>Admin khóa/mở lớp học phần và xóa lớp học phần rỗng</t>
@@ -1597,7 +1645,7 @@
     <t>Khóa/mở cập nhật đúng `is_active`; xóa lớp trống thành công; xóa lớp đang có dữ liệu bị chặn kèm cảnh báo</t>
   </si>
   <si>
-    <t>TC-ADMIN-25</t>
+    <t>TC-ADMIN-27</t>
   </si>
   <si>
     <t>Môn học có 2 bài báo cáo (giữa kì + cuối kì) tạo được và lưu đúng</t>
@@ -1617,7 +1665,7 @@
     <t>Không chọn ⇒ mặc định 1 (chỉ cuối kì); giá trị khác 1/2 bị chặn (HTTP 422).</t>
   </si>
   <si>
-    <t>TC-ADMIN-26</t>
+    <t>TC-ADMIN-28</t>
   </si>
   <si>
     <t>Import môn học: cột so_bai_bao_cao=2 ⇒ 2 bài; thiếu cột/để trống ⇒ 1; KHÔNG hạ môn đang 2 bài</t>
@@ -1986,24 +2034,48 @@
     <t>TC-LECT-07</t>
   </si>
   <si>
-    <t>Xóa sinh viên khỏi lớp thì dữ liệu nhóm của sinh viên đó được dọn dẹp</t>
+    <t>Thêm sinh viên vào lớp / thêm LẠI sinh viên đã rời lớp (không lỗi trùng unique)</t>
+  </si>
+  <si>
+    <t>Lớp có nhóm 2 thành viên (trưởng nhóm sv1 + thành viên sv3); sv3 từng rời lớp</t>
+  </si>
+  <si>
+    <t>Mở chi tiết lớp
+Thêm sv3 vào lớp (thành công)
+Thêm lại sv3 và thêm lại sv1 (trùng)
+Cho sv3 rời lớp rồi bấm "Thêm lại"</t>
+  </si>
+  <si>
+    <t>POST /lecturer/classes/{id}/students {student_ids[]}</t>
+  </si>
+  <si>
+    <t>sv3 được thêm 1 lần; thêm trùng bị từ chối kèm thông báo (không lỗi 500); "Thêm lại" sinh viên đã rời khôi phục trạng thái Đang học, không sinh dòng pivot trùng</t>
+  </si>
+  <si>
+    <t>tests/Feature/LecturerClassTest.php · tests/Feature/ClassMembershipStatusTest.php</t>
+  </si>
+  <si>
+    <t>TC-LECT-08</t>
+  </si>
+  <si>
+    <t>Cho sinh viên rời lớp (xóa mềm) thì dữ liệu nhóm của sinh viên đó được dọn dẹp</t>
   </si>
   <si>
     <t>Lớp có nhóm 2 thành viên (trưởng nhóm sv1 + thành viên sv3)</t>
   </si>
   <si>
-    <t>Xóa sv3 khỏi lớp
+    <t>Cho sv3 rời lớp
 Kiểm tra nhóm và bảng tin
-Xóa tiếp trưởng nhóm sv1 rồi kiểm tra nhóm</t>
+Cho tiếp trưởng nhóm sv1 rời lớp rồi kiểm tra nhóm</t>
   </si>
   <si>
     <t>POST /lecturer/classes/{id}/students/{studentId}/remove</t>
   </si>
   <si>
-    <t>sv3 bị gỡ khỏi `user_classes` và khỏi nhóm; khi xóa trưởng nhóm: quyền trưởng nhóm chuyển cho thành viên còn lại; nhóm rỗng thì giải tán</t>
-  </si>
-  <si>
-    <t>TC-LECT-08</t>
+    <t>sv3 bị đánh dấu rời lớp (KHÔNG xóa dòng `user_classes`) và bị rút khỏi nhóm; khi trưởng nhóm rời: quyền trưởng nhóm chuyển cho thành viên đang học; hết thành viên thì nhóm GIỮ LẠI với trưởng nhóm = người cuối cùng rời (Chốt 2a)</t>
+  </si>
+  <si>
+    <t>TC-LECT-09</t>
   </si>
   <si>
     <t>Giảng viên không quản lý được lớp mình KHÔNG phụ trách (case âm)</t>
@@ -2023,7 +2095,7 @@
     <t>Bị chặn 403/chuyển hướng ở mọi hành động; dữ liệu lớp B không đổi</t>
   </si>
   <si>
-    <t>TC-LECT-09</t>
+    <t>TC-LECT-10</t>
   </si>
   <si>
     <t>Khóa / mở lớp (#4)</t>
@@ -2047,7 +2119,7 @@
     <t>Khóa ⇒ is_active = 0 và sinh viên không tạo nhóm/tham gia lớp được; mở ⇒ hoạt động bình thường</t>
   </si>
   <si>
-    <t>TC-LECT-10</t>
+    <t>TC-LECT-11</t>
   </si>
   <si>
     <t>Phân quyền trang giảng viên (#4)</t>
@@ -2070,7 +2142,7 @@
     <t>Bị chuyển hướng về dashboard sinh viên (middleware `lecturer`); không tạo được lớp</t>
   </si>
   <si>
-    <t>TC-LECT-11</t>
+    <t>TC-LECT-12</t>
   </si>
   <si>
     <t>Danh sách lớp của tôi (#4)</t>
@@ -2096,7 +2168,7 @@
     <t>tests/Feature/StudentClassDetailTest.php + tests/Feature/ViewSmokeTest.php</t>
   </si>
   <si>
-    <t>TC-LECT-12</t>
+    <t>TC-LECT-13</t>
   </si>
   <si>
     <t>Chi tiết lớp của tôi (#4)</t>
@@ -2121,7 +2193,7 @@
     <t>tests/Feature/StudentClassDetailTest.php</t>
   </si>
   <si>
-    <t>TC-LECT-13</t>
+    <t>TC-LECT-14</t>
   </si>
   <si>
     <t>Sinh viên không xem được chi tiết lớp mình chưa tham gia (case âm)</t>
@@ -2136,7 +2208,7 @@
     <t>Bị chặn (403/chuyển hướng) — không lộ dữ liệu lớp khác</t>
   </si>
   <si>
-    <t>TC-LECT-14</t>
+    <t>TC-LECT-15</t>
   </si>
   <si>
     <t>Tham gia lớp bằng mã (#4)</t>
@@ -2163,7 +2235,7 @@
     <t>tests/Feature/ClassJoinTest.php</t>
   </si>
   <si>
-    <t>TC-LECT-15</t>
+    <t>TC-LECT-16</t>
   </si>
   <si>
     <t>Tạo nhóm theo từng lớp học phần (#4 + #8)</t>
@@ -6072,10 +6144,10 @@
         <v>14</v>
       </c>
       <c r="D3" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
@@ -6124,10 +6196,10 @@
         <v>22</v>
       </c>
       <c r="D5" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="3">
         <v>0</v>
@@ -6328,10 +6400,10 @@
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="4">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E13" s="4">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F13" s="4">
         <v>5</v>
@@ -6431,7 +6503,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1085</v>
+        <v>1106</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>127</v>
@@ -6440,7 +6512,7 @@
         <v>32</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1086</v>
+        <v>1107</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -6449,19 +6521,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1087</v>
+        <v>1108</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1088</v>
+        <v>1109</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1089</v>
+        <v>1110</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1090</v>
+        <v>1111</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1091</v>
+        <v>1112</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -6470,13 +6542,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1092</v>
+        <v>1113</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1093</v>
+        <v>1114</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>127</v>
@@ -6485,7 +6557,7 @@
         <v>32</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1094</v>
+        <v>1115</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -6494,19 +6566,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1096</v>
+        <v>1117</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1097</v>
+        <v>1118</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1098</v>
+        <v>1119</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1099</v>
+        <v>1120</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -6515,13 +6587,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1100</v>
+        <v>1121</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1101</v>
+        <v>1122</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>127</v>
@@ -6530,7 +6602,7 @@
         <v>32</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1102</v>
+        <v>1123</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -6539,19 +6611,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1103</v>
+        <v>1124</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1104</v>
+        <v>1125</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1105</v>
+        <v>1126</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1106</v>
+        <v>1127</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1107</v>
+        <v>1128</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -6560,13 +6632,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1092</v>
+        <v>1113</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1108</v>
+        <v>1129</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>127</v>
@@ -6575,7 +6647,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1109</v>
+        <v>1130</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -6584,19 +6656,19 @@
         <v>188</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1110</v>
+        <v>1131</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1104</v>
+        <v>1125</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1111</v>
+        <v>1132</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1112</v>
+        <v>1133</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1113</v>
+        <v>1134</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -6605,13 +6677,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1114</v>
+        <v>1135</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1115</v>
+        <v>1136</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>127</v>
@@ -6620,7 +6692,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1116</v>
+        <v>1137</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -6629,19 +6701,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1117</v>
+        <v>1138</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1118</v>
+        <v>1139</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1119</v>
+        <v>1140</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1120</v>
+        <v>1141</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1121</v>
+        <v>1142</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -6650,13 +6722,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1092</v>
+        <v>1113</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1122</v>
+        <v>1143</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>127</v>
@@ -6665,7 +6737,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1116</v>
+        <v>1137</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -6674,19 +6746,19 @@
         <v>188</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1123</v>
+        <v>1144</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1124</v>
+        <v>1145</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1125</v>
+        <v>1146</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1126</v>
+        <v>1147</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1127</v>
+        <v>1148</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -6695,13 +6767,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1100</v>
+        <v>1121</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1128</v>
+        <v>1149</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>127</v>
@@ -6710,7 +6782,7 @@
         <v>32</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1129</v>
+        <v>1150</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -6719,19 +6791,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1130</v>
+        <v>1151</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1131</v>
+        <v>1152</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1132</v>
+        <v>1153</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1133</v>
+        <v>1154</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1134</v>
+        <v>1155</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -6740,13 +6812,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1092</v>
+        <v>1113</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1135</v>
+        <v>1156</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>127</v>
@@ -6755,7 +6827,7 @@
         <v>32</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1136</v>
+        <v>1157</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -6764,19 +6836,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1137</v>
+        <v>1158</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1138</v>
+        <v>1159</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1139</v>
+        <v>1160</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1140</v>
+        <v>1161</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1141</v>
+        <v>1162</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -6785,15 +6857,15 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1092</v>
+        <v>1113</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>1142</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>127</v>
@@ -6802,7 +6874,7 @@
         <v>32</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1144</v>
+        <v>1165</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -6811,19 +6883,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1145</v>
+        <v>1166</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1146</v>
+        <v>1167</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1147</v>
+        <v>1168</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1148</v>
+        <v>1169</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1149</v>
+        <v>1170</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -6832,13 +6904,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1092</v>
+        <v>1113</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1150</v>
+        <v>1171</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -6847,7 +6919,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1151</v>
+        <v>1172</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -6856,19 +6928,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1152</v>
+        <v>1173</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1153</v>
+        <v>1174</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1154</v>
+        <v>1175</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1155</v>
+        <v>1176</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1156</v>
+        <v>1177</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -6877,13 +6949,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1157</v>
+        <v>1178</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1158</v>
+        <v>1179</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -6892,7 +6964,7 @@
         <v>32</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1151</v>
+        <v>1172</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -6901,19 +6973,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1159</v>
+        <v>1180</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1104</v>
+        <v>1125</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1160</v>
+        <v>1181</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1161</v>
+        <v>1182</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1162</v>
+        <v>1183</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -6922,13 +6994,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1163</v>
+        <v>1184</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1164</v>
+        <v>1185</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -6937,7 +7009,7 @@
         <v>32</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1151</v>
+        <v>1172</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -6946,19 +7018,19 @@
         <v>151</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1165</v>
+        <v>1186</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1166</v>
+        <v>1187</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1167</v>
+        <v>1188</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1168</v>
+        <v>1189</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1169</v>
+        <v>1190</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -6967,13 +7039,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1170</v>
+        <v>1191</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1171</v>
+        <v>1192</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>110</v>
@@ -6982,7 +7054,7 @@
         <v>32</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1172</v>
+        <v>1193</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -6991,19 +7063,19 @@
         <v>151</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1173</v>
+        <v>1194</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1174</v>
+        <v>1195</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1175</v>
+        <v>1196</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1176</v>
+        <v>1197</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1177</v>
+        <v>1198</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -7012,13 +7084,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1178</v>
+        <v>1199</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1179</v>
+        <v>1200</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -7027,7 +7099,7 @@
         <v>32</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1151</v>
+        <v>1172</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -7036,19 +7108,19 @@
         <v>188</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1180</v>
+        <v>1201</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1181</v>
+        <v>1202</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1182</v>
+        <v>1203</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1183</v>
+        <v>1204</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1184</v>
+        <v>1205</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -7057,13 +7129,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>1157</v>
+        <v>1178</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>1185</v>
+        <v>1206</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>104</v>
@@ -7072,7 +7144,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1186</v>
+        <v>1207</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>160</v>
@@ -7081,19 +7153,19 @@
         <v>151</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1187</v>
+        <v>1208</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>1188</v>
+        <v>1209</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1189</v>
+        <v>1210</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>1190</v>
+        <v>1211</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>1191</v>
+        <v>1212</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -7102,13 +7174,13 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>1192</v>
+        <v>1213</v>
       </c>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>1193</v>
+        <v>1214</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>104</v>
@@ -7117,7 +7189,7 @@
         <v>32</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1194</v>
+        <v>1215</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>160</v>
@@ -7126,19 +7198,19 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>1195</v>
+        <v>1216</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>1196</v>
+        <v>1217</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>1197</v>
+        <v>1218</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>1198</v>
+        <v>1219</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>1199</v>
+        <v>1220</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>166</v>
@@ -7147,13 +7219,13 @@
         <v>4</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>1200</v>
+        <v>1221</v>
       </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7" t="s">
-        <v>1201</v>
+        <v>1222</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>104</v>
@@ -7162,7 +7234,7 @@
         <v>32</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1202</v>
+        <v>1223</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>160</v>
@@ -7171,19 +7243,19 @@
         <v>151</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>1203</v>
+        <v>1224</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>1204</v>
+        <v>1225</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>1205</v>
+        <v>1226</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>1206</v>
+        <v>1227</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>1207</v>
+        <v>1228</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>166</v>
@@ -7192,13 +7264,13 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>1192</v>
+        <v>1213</v>
       </c>
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="7" t="s">
-        <v>1208</v>
+        <v>1229</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>104</v>
@@ -7207,7 +7279,7 @@
         <v>32</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1209</v>
+        <v>1230</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>160</v>
@@ -7216,19 +7288,19 @@
         <v>188</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>1210</v>
+        <v>1231</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>1211</v>
+        <v>1232</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>1213</v>
+        <v>1234</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>1214</v>
+        <v>1235</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>166</v>
@@ -7237,13 +7309,13 @@
         <v>4</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>1215</v>
+        <v>1236</v>
       </c>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="7" t="s">
-        <v>1216</v>
+        <v>1237</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>104</v>
@@ -7252,7 +7324,7 @@
         <v>32</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>160</v>
@@ -7261,19 +7333,19 @@
         <v>151</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1218</v>
+        <v>1239</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>1219</v>
+        <v>1240</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>1220</v>
+        <v>1241</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>1221</v>
+        <v>1242</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>1222</v>
+        <v>1243</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>166</v>
@@ -7282,13 +7354,13 @@
         <v>4</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>1223</v>
+        <v>1244</v>
       </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="7" t="s">
-        <v>1224</v>
+        <v>1245</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>104</v>
@@ -7297,7 +7369,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>160</v>
@@ -7306,19 +7378,19 @@
         <v>188</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>1225</v>
+        <v>1246</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>1226</v>
+        <v>1247</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>1227</v>
+        <v>1248</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>1228</v>
+        <v>1249</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>1229</v>
+        <v>1250</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>166</v>
@@ -7327,13 +7399,13 @@
         <v>4</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>1230</v>
+        <v>1251</v>
       </c>
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="7" t="s">
-        <v>1231</v>
+        <v>1252</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>110</v>
@@ -7342,7 +7414,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1232</v>
+        <v>1253</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>160</v>
@@ -7351,34 +7423,34 @@
         <v>151</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1233</v>
+        <v>1254</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>1235</v>
+        <v>1256</v>
       </c>
       <c r="J22" s="6" t="s">
+        <v>1257</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>1258</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="6" t="s">
         <v>1236</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>1237</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>1215</v>
       </c>
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="7" t="s">
-        <v>1238</v>
+        <v>1259</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>104</v>
@@ -7387,7 +7459,7 @@
         <v>32</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1239</v>
+        <v>1260</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>150</v>
@@ -7396,19 +7468,19 @@
         <v>188</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>1240</v>
+        <v>1261</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>1241</v>
+        <v>1262</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>1242</v>
+        <v>1263</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>1243</v>
+        <v>1264</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>1244</v>
+        <v>1265</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>166</v>
@@ -7417,13 +7489,13 @@
         <v>4</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>1192</v>
+        <v>1213</v>
       </c>
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="7" t="s">
-        <v>1245</v>
+        <v>1266</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>104</v>
@@ -7432,7 +7504,7 @@
         <v>32</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1246</v>
+        <v>1267</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>150</v>
@@ -7441,19 +7513,19 @@
         <v>254</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1247</v>
+        <v>1268</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>372</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>1249</v>
+        <v>1270</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>1250</v>
+        <v>1271</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>166</v>
@@ -7462,13 +7534,13 @@
         <v>4</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>1192</v>
+        <v>1213</v>
       </c>
       <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="7" t="s">
-        <v>1251</v>
+        <v>1272</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>104</v>
@@ -7477,7 +7549,7 @@
         <v>32</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>150</v>
@@ -7486,19 +7558,19 @@
         <v>188</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>1253</v>
+        <v>1274</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>1254</v>
+        <v>1275</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>1255</v>
+        <v>1276</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>1256</v>
+        <v>1277</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>1257</v>
+        <v>1278</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>166</v>
@@ -7507,13 +7579,13 @@
         <v>4</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>1223</v>
+        <v>1244</v>
       </c>
       <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="7" t="s">
-        <v>1258</v>
+        <v>1279</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>104</v>
@@ -7522,7 +7594,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>160</v>
@@ -7531,19 +7603,19 @@
         <v>188</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>1259</v>
+        <v>1280</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>372</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>1260</v>
+        <v>1281</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>1261</v>
+        <v>1282</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>1262</v>
+        <v>1283</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>166</v>
@@ -7552,13 +7624,13 @@
         <v>4</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>1223</v>
+        <v>1244</v>
       </c>
       <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="7" t="s">
-        <v>1263</v>
+        <v>1284</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>104</v>
@@ -7567,7 +7639,7 @@
         <v>32</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1264</v>
+        <v>1285</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>150</v>
@@ -7576,19 +7648,19 @@
         <v>254</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>1265</v>
+        <v>1286</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>1266</v>
+        <v>1287</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>1267</v>
+        <v>1288</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>1268</v>
+        <v>1289</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>1269</v>
+        <v>1290</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>166</v>
@@ -7597,13 +7669,13 @@
         <v>4</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>1192</v>
+        <v>1213</v>
       </c>
       <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="7" t="s">
-        <v>1270</v>
+        <v>1291</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>110</v>
@@ -7612,7 +7684,7 @@
         <v>32</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1271</v>
+        <v>1292</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>150</v>
@@ -7621,19 +7693,19 @@
         <v>151</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>1272</v>
+        <v>1293</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>1274</v>
+        <v>1295</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>1275</v>
+        <v>1296</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>1276</v>
+        <v>1297</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>6</v>
@@ -7642,10 +7714,10 @@
         <v>6</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>1277</v>
+        <v>1298</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>1278</v>
+        <v>1299</v>
       </c>
     </row>
   </sheetData>
@@ -7739,7 +7811,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1279</v>
+        <v>1300</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -7748,7 +7820,7 @@
         <v>36</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1280</v>
+        <v>1301</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -7757,19 +7829,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1281</v>
+        <v>1302</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1282</v>
+        <v>1303</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1283</v>
+        <v>1304</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1284</v>
+        <v>1305</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1285</v>
+        <v>1306</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -7778,13 +7850,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1286</v>
+        <v>1307</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1287</v>
+        <v>1308</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -7793,7 +7865,7 @@
         <v>36</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1288</v>
+        <v>1309</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -7802,19 +7874,19 @@
         <v>188</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1289</v>
+        <v>1310</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1290</v>
+        <v>1311</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1291</v>
+        <v>1312</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1292</v>
+        <v>1313</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1293</v>
+        <v>1314</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -7823,13 +7895,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1295</v>
+        <v>1316</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -7838,7 +7910,7 @@
         <v>36</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1296</v>
+        <v>1317</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -7847,19 +7919,19 @@
         <v>151</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1297</v>
+        <v>1318</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1298</v>
+        <v>1319</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1299</v>
+        <v>1320</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1300</v>
+        <v>1321</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1301</v>
+        <v>1322</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -7868,13 +7940,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1286</v>
+        <v>1307</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1302</v>
+        <v>1323</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -7883,43 +7955,43 @@
         <v>36</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1303</v>
+        <v>1324</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1304</v>
+        <v>1325</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1305</v>
+        <v>1326</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1306</v>
+        <v>1327</v>
       </c>
       <c r="J5" s="6" t="s">
+        <v>1328</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>1329</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>1307</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>1308</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>1286</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1309</v>
+        <v>1330</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>110</v>
@@ -7928,7 +8000,7 @@
         <v>36</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1310</v>
+        <v>1331</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -7937,19 +8009,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1311</v>
+        <v>1332</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1312</v>
+        <v>1333</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1313</v>
+        <v>1334</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1314</v>
+        <v>1335</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1315</v>
+        <v>1336</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -7958,13 +8030,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1286</v>
+        <v>1307</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1316</v>
+        <v>1337</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -7973,7 +8045,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1317</v>
+        <v>1338</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -7982,19 +8054,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1318</v>
+        <v>1339</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1319</v>
+        <v>1340</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1320</v>
+        <v>1341</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1321</v>
+        <v>1342</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1322</v>
+        <v>1343</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -8003,15 +8075,15 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1323</v>
+        <v>1344</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>1324</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1325</v>
+        <v>1346</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -8020,7 +8092,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1326</v>
+        <v>1347</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -8029,19 +8101,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1327</v>
+        <v>1348</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1328</v>
+        <v>1349</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1329</v>
+        <v>1350</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1321</v>
+        <v>1342</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1330</v>
+        <v>1351</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -8050,13 +8122,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1323</v>
+        <v>1344</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1331</v>
+        <v>1352</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -8065,7 +8137,7 @@
         <v>36</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1332</v>
+        <v>1353</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -8074,19 +8146,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1333</v>
+        <v>1354</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1334</v>
+        <v>1355</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1335</v>
+        <v>1356</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1336</v>
+        <v>1357</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1337</v>
+        <v>1358</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -8095,13 +8167,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1286</v>
+        <v>1307</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1338</v>
+        <v>1359</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -8110,7 +8182,7 @@
         <v>36</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1339</v>
+        <v>1360</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>150</v>
@@ -8119,19 +8191,19 @@
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1340</v>
+        <v>1361</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1341</v>
+        <v>1362</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1342</v>
+        <v>1363</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>856</v>
+        <v>877</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1343</v>
+        <v>1364</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -8140,13 +8212,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1286</v>
+        <v>1307</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1344</v>
+        <v>1365</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>127</v>
@@ -8155,7 +8227,7 @@
         <v>36</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1345</v>
+        <v>1366</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -8164,19 +8236,19 @@
         <v>188</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1346</v>
+        <v>1367</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1347</v>
+        <v>1368</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1348</v>
+        <v>1369</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1349</v>
+        <v>1370</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1350</v>
+        <v>1371</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -8185,13 +8257,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1351</v>
+        <v>1372</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>127</v>
@@ -8200,28 +8272,28 @@
         <v>36</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1352</v>
+        <v>1373</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1353</v>
+        <v>1374</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1354</v>
+        <v>1375</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1355</v>
+        <v>1376</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1356</v>
+        <v>1377</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1357</v>
+        <v>1378</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -8230,13 +8302,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1358</v>
+        <v>1379</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1359</v>
+        <v>1380</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>127</v>
@@ -8245,7 +8317,7 @@
         <v>36</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1360</v>
+        <v>1381</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -8254,19 +8326,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1361</v>
+        <v>1382</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1347</v>
+        <v>1368</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1362</v>
+        <v>1383</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1363</v>
+        <v>1384</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1364</v>
+        <v>1385</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -8275,13 +8347,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1365</v>
+        <v>1386</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>127</v>
@@ -8290,7 +8362,7 @@
         <v>36</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1366</v>
+        <v>1387</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -8299,19 +8371,19 @@
         <v>151</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1367</v>
+        <v>1388</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1368</v>
+        <v>1389</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1369</v>
+        <v>1390</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1370</v>
+        <v>1391</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1371</v>
+        <v>1392</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -8320,13 +8392,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1372</v>
+        <v>1393</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>127</v>
@@ -8335,7 +8407,7 @@
         <v>36</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1373</v>
+        <v>1394</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -8344,19 +8416,19 @@
         <v>188</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1374</v>
+        <v>1395</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1375</v>
+        <v>1396</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1376</v>
+        <v>1397</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1377</v>
+        <v>1398</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1378</v>
+        <v>1399</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -8365,13 +8437,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>1379</v>
+        <v>1400</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -8380,7 +8452,7 @@
         <v>36</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1380</v>
+        <v>1401</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>160</v>
@@ -8389,19 +8461,19 @@
         <v>188</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1381</v>
+        <v>1402</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>1382</v>
+        <v>1403</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1383</v>
+        <v>1404</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>1384</v>
+        <v>1405</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>1385</v>
+        <v>1406</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -8410,15 +8482,15 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>1386</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>1387</v>
+        <v>1408</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>110</v>
@@ -8427,7 +8499,7 @@
         <v>36</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1388</v>
+        <v>1409</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>150</v>
@@ -8436,19 +8508,19 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>1389</v>
+        <v>1410</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>1390</v>
+        <v>1411</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>1391</v>
+        <v>1412</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>1392</v>
+        <v>1413</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>1393</v>
+        <v>1414</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>166</v>
@@ -8457,13 +8529,13 @@
         <v>4</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>1286</v>
+        <v>1307</v>
       </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7" t="s">
-        <v>1394</v>
+        <v>1415</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>110</v>
@@ -8472,7 +8544,7 @@
         <v>36</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1395</v>
+        <v>1416</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>150</v>
@@ -8481,19 +8553,19 @@
         <v>151</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>1396</v>
+        <v>1417</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>1397</v>
+        <v>1418</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>1398</v>
+        <v>1419</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>856</v>
+        <v>877</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>1399</v>
+        <v>1420</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>166</v>
@@ -8502,13 +8574,13 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>1286</v>
+        <v>1307</v>
       </c>
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="7" t="s">
-        <v>1400</v>
+        <v>1421</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>110</v>
@@ -8517,7 +8589,7 @@
         <v>36</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1395</v>
+        <v>1416</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>160</v>
@@ -8526,19 +8598,19 @@
         <v>151</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>1401</v>
+        <v>1422</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>1402</v>
+        <v>1423</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>1403</v>
+        <v>1424</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>1404</v>
+        <v>1425</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>1405</v>
+        <v>1426</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>166</v>
@@ -8547,13 +8619,13 @@
         <v>4</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>1286</v>
+        <v>1307</v>
       </c>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="7" t="s">
-        <v>1406</v>
+        <v>1427</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>110</v>
@@ -8562,7 +8634,7 @@
         <v>36</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1407</v>
+        <v>1428</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>150</v>
@@ -8571,19 +8643,19 @@
         <v>188</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1408</v>
+        <v>1429</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>1409</v>
+        <v>1430</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>1410</v>
+        <v>1431</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>1411</v>
+        <v>1432</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>1412</v>
+        <v>1433</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>166</v>
@@ -8592,22 +8664,22 @@
         <v>4</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>1286</v>
+        <v>1307</v>
       </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="7" t="s">
-        <v>1413</v>
+        <v>1434</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1414</v>
+        <v>1435</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1415</v>
+        <v>1436</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>160</v>
@@ -8616,19 +8688,19 @@
         <v>151</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>1416</v>
+        <v>1437</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>1417</v>
+        <v>1438</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>1418</v>
+        <v>1439</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>1419</v>
+        <v>1440</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>1420</v>
+        <v>1441</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>166</v>
@@ -8637,10 +8709,10 @@
         <v>4</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>1286</v>
+        <v>1307</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>1421</v>
+        <v>1442</v>
       </c>
     </row>
   </sheetData>
@@ -8734,7 +8806,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1422</v>
+        <v>1443</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>107</v>
@@ -8743,7 +8815,7 @@
         <v>40</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1423</v>
+        <v>1444</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -8752,19 +8824,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1424</v>
+        <v>1445</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1425</v>
+        <v>1446</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1426</v>
+        <v>1447</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1427</v>
+        <v>1448</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1428</v>
+        <v>1449</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -8773,13 +8845,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1430</v>
+        <v>1451</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -8788,7 +8860,7 @@
         <v>40</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1431</v>
+        <v>1452</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -8797,19 +8869,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1432</v>
+        <v>1453</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1433</v>
+        <v>1454</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1434</v>
+        <v>1455</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1435</v>
+        <v>1456</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1436</v>
+        <v>1457</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -8818,13 +8890,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1437</v>
+        <v>1458</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -8833,7 +8905,7 @@
         <v>40</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1438</v>
+        <v>1459</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>150</v>
@@ -8842,19 +8914,19 @@
         <v>151</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1439</v>
+        <v>1460</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1440</v>
+        <v>1461</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1441</v>
+        <v>1462</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1442</v>
+        <v>1463</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1443</v>
+        <v>1464</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -8863,13 +8935,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1444</v>
+        <v>1465</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>127</v>
@@ -8878,43 +8950,43 @@
         <v>40</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1445</v>
+        <v>1466</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1446</v>
+        <v>1467</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1447</v>
+        <v>1468</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1448</v>
+        <v>1469</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1449</v>
+        <v>1470</v>
       </c>
       <c r="K5" s="6" t="s">
+        <v>1471</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>1450</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>1429</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1451</v>
+        <v>1472</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>127</v>
@@ -8923,28 +8995,28 @@
         <v>40</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1445</v>
+        <v>1466</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1452</v>
+        <v>1473</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1453</v>
+        <v>1474</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1454</v>
+        <v>1475</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1455</v>
+        <v>1476</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1456</v>
+        <v>1477</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -8953,13 +9025,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1457</v>
+        <v>1478</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>127</v>
@@ -8968,28 +9040,28 @@
         <v>40</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1445</v>
+        <v>1466</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1458</v>
+        <v>1479</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1459</v>
+        <v>1480</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1460</v>
+        <v>1481</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>817</v>
+        <v>838</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1461</v>
+        <v>1482</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -8998,13 +9070,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1462</v>
+        <v>1483</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>107</v>
@@ -9013,7 +9085,7 @@
         <v>40</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1463</v>
+        <v>1484</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -9022,19 +9094,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1464</v>
+        <v>1485</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1465</v>
+        <v>1486</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1466</v>
+        <v>1487</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1467</v>
+        <v>1488</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1468</v>
+        <v>1489</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -9043,13 +9115,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1469</v>
+        <v>1490</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -9058,7 +9130,7 @@
         <v>40</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1470</v>
+        <v>1491</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -9067,19 +9139,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1471</v>
+        <v>1492</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1472</v>
+        <v>1493</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1473</v>
+        <v>1494</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1474</v>
+        <v>1495</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1475</v>
+        <v>1496</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -9088,13 +9160,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1476</v>
+        <v>1497</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>104</v>
@@ -9103,28 +9175,28 @@
         <v>40</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1477</v>
+        <v>1498</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1478</v>
+        <v>1499</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1479</v>
+        <v>1500</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1480</v>
+        <v>1501</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1481</v>
+        <v>1502</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1482</v>
+        <v>1503</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1483</v>
+        <v>1504</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -9133,13 +9205,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1484</v>
+        <v>1505</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>127</v>
@@ -9148,7 +9220,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1485</v>
+        <v>1506</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -9157,19 +9229,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1486</v>
+        <v>1507</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1487</v>
+        <v>1508</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1488</v>
+        <v>1509</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1489</v>
+        <v>1510</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1490</v>
+        <v>1511</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -9178,13 +9250,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1491</v>
+        <v>1512</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>127</v>
@@ -9193,7 +9265,7 @@
         <v>40</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1492</v>
+        <v>1513</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -9202,19 +9274,19 @@
         <v>254</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1493</v>
+        <v>1514</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1347</v>
+        <v>1368</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1494</v>
+        <v>1515</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1495</v>
+        <v>1516</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1496</v>
+        <v>1517</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -9223,13 +9295,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1497</v>
+        <v>1518</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1498</v>
+        <v>1519</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>127</v>
@@ -9238,7 +9310,7 @@
         <v>40</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1499</v>
+        <v>1520</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -9247,19 +9319,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1500</v>
+        <v>1521</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1347</v>
+        <v>1368</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1501</v>
+        <v>1522</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1502</v>
+        <v>1523</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1503</v>
+        <v>1524</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -9268,13 +9340,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1497</v>
+        <v>1518</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1504</v>
+        <v>1525</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>127</v>
@@ -9283,7 +9355,7 @@
         <v>40</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1505</v>
+        <v>1526</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -9292,19 +9364,19 @@
         <v>188</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1506</v>
+        <v>1527</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1347</v>
+        <v>1368</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1507</v>
+        <v>1528</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1508</v>
+        <v>1529</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1509</v>
+        <v>1530</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -9313,13 +9385,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1510</v>
+        <v>1531</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1511</v>
+        <v>1532</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -9328,7 +9400,7 @@
         <v>40</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1512</v>
+        <v>1533</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>150</v>
@@ -9337,19 +9409,19 @@
         <v>254</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1513</v>
+        <v>1534</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1514</v>
+        <v>1535</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1515</v>
+        <v>1536</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1516</v>
+        <v>1537</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1517</v>
+        <v>1538</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>6</v>
@@ -9361,12 +9433,12 @@
         <v>157</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>1518</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>1519</v>
+        <v>1540</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -9375,28 +9447,28 @@
         <v>40</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1520</v>
+        <v>1541</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1521</v>
+        <v>1542</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1522</v>
+        <v>1543</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>1523</v>
+        <v>1544</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1524</v>
+        <v>1545</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>1525</v>
+        <v>1546</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>1526</v>
+        <v>1547</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>6</v>
@@ -9408,7 +9480,7 @@
         <v>157</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>1527</v>
+        <v>1548</v>
       </c>
     </row>
   </sheetData>
@@ -9502,7 +9574,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1528</v>
+        <v>1549</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -9511,28 +9583,28 @@
         <v>44</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1529</v>
+        <v>1550</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1530</v>
+        <v>1551</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1531</v>
+        <v>1552</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1532</v>
+        <v>1553</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1533</v>
+        <v>1554</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1534</v>
+        <v>1555</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -9541,13 +9613,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1535</v>
+        <v>1556</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1536</v>
+        <v>1557</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -9556,28 +9628,28 @@
         <v>44</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1529</v>
+        <v>1550</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1537</v>
+        <v>1558</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1538</v>
+        <v>1559</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1539</v>
+        <v>1560</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1540</v>
+        <v>1561</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1541</v>
+        <v>1562</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -9586,13 +9658,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1535</v>
+        <v>1556</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1542</v>
+        <v>1563</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -9601,7 +9673,7 @@
         <v>44</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1543</v>
+        <v>1564</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -9610,19 +9682,19 @@
         <v>151</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1544</v>
+        <v>1565</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1545</v>
+        <v>1566</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1546</v>
+        <v>1567</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1547</v>
+        <v>1568</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1548</v>
+        <v>1569</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -9631,13 +9703,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1549</v>
+        <v>1570</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1550</v>
+        <v>1571</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -9646,7 +9718,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1551</v>
+        <v>1572</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -9655,19 +9727,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1552</v>
+        <v>1573</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1553</v>
+        <v>1574</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1554</v>
+        <v>1575</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1555</v>
+        <v>1576</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1556</v>
+        <v>1577</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -9676,13 +9748,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1557</v>
+        <v>1578</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1558</v>
+        <v>1579</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>170</v>
@@ -9691,7 +9763,7 @@
         <v>44</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1551</v>
+        <v>1572</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -9700,19 +9772,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1559</v>
+        <v>1580</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>190</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1560</v>
+        <v>1581</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1561</v>
+        <v>1582</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -9721,13 +9793,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1535</v>
+        <v>1556</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1562</v>
+        <v>1583</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -9736,28 +9808,28 @@
         <v>44</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1563</v>
+        <v>1584</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1564</v>
+        <v>1585</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1565</v>
+        <v>1586</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1566</v>
+        <v>1587</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1567</v>
+        <v>1588</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1568</v>
+        <v>1589</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -9766,13 +9838,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1569</v>
+        <v>1590</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1570</v>
+        <v>1591</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -9781,28 +9853,28 @@
         <v>44</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1563</v>
+        <v>1584</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1521</v>
+        <v>1542</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1571</v>
+        <v>1592</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1572</v>
+        <v>1593</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1573</v>
+        <v>1594</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1574</v>
+        <v>1595</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1575</v>
+        <v>1596</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -9811,13 +9883,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1569</v>
+        <v>1590</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1576</v>
+        <v>1597</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -9826,7 +9898,7 @@
         <v>44</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1577</v>
+        <v>1598</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -9835,19 +9907,19 @@
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1578</v>
+        <v>1599</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1579</v>
+        <v>1600</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1580</v>
+        <v>1601</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1581</v>
+        <v>1602</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1582</v>
+        <v>1603</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -9856,13 +9928,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1569</v>
+        <v>1590</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1583</v>
+        <v>1604</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>170</v>
@@ -9871,7 +9943,7 @@
         <v>44</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1577</v>
+        <v>1598</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -9880,19 +9952,19 @@
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1584</v>
+        <v>1605</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>190</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1586</v>
+        <v>1607</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -9901,13 +9973,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1569</v>
+        <v>1590</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1587</v>
+        <v>1608</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -9916,7 +9988,7 @@
         <v>44</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1588</v>
+        <v>1609</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>150</v>
@@ -9925,19 +9997,19 @@
         <v>188</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1589</v>
+        <v>1610</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1590</v>
+        <v>1611</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1591</v>
+        <v>1612</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1030</v>
+        <v>1051</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1592</v>
+        <v>1613</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>6</v>
@@ -9949,12 +10021,12 @@
         <v>157</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>1593</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1594</v>
+        <v>1615</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -9963,7 +10035,7 @@
         <v>44</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1595</v>
+        <v>1616</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -9972,19 +10044,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1596</v>
+        <v>1617</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1597</v>
+        <v>1618</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1598</v>
+        <v>1619</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1599</v>
+        <v>1620</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1600</v>
+        <v>1621</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -9993,13 +10065,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1569</v>
+        <v>1590</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1601</v>
+        <v>1622</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -10008,7 +10080,7 @@
         <v>44</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1602</v>
+        <v>1623</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>150</v>
@@ -10017,19 +10089,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1603</v>
+        <v>1624</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1604</v>
+        <v>1625</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1605</v>
+        <v>1626</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1606</v>
+        <v>1627</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1607</v>
+        <v>1628</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -10038,13 +10110,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1569</v>
+        <v>1590</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>127</v>
@@ -10053,28 +10125,28 @@
         <v>44</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1609</v>
+        <v>1630</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1610</v>
+        <v>1631</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1611</v>
+        <v>1632</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1612</v>
+        <v>1633</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1613</v>
+        <v>1634</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1614</v>
+        <v>1635</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -10083,13 +10155,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1615</v>
+        <v>1636</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1616</v>
+        <v>1637</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>127</v>
@@ -10098,7 +10170,7 @@
         <v>44</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1617</v>
+        <v>1638</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -10107,19 +10179,19 @@
         <v>254</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1618</v>
+        <v>1639</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1619</v>
+        <v>1640</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1620</v>
+        <v>1641</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1621</v>
+        <v>1642</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1622</v>
+        <v>1643</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -10128,7 +10200,7 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>1615</v>
+        <v>1636</v>
       </c>
       <c r="O15" s="6"/>
     </row>
@@ -10223,7 +10295,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1623</v>
+        <v>1644</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -10232,7 +10304,7 @@
         <v>48</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1624</v>
+        <v>1645</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -10241,19 +10313,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1625</v>
+        <v>1646</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1626</v>
+        <v>1647</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1627</v>
+        <v>1648</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1628</v>
+        <v>1649</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1629</v>
+        <v>1650</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -10262,13 +10334,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1630</v>
+        <v>1651</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1631</v>
+        <v>1652</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -10277,7 +10349,7 @@
         <v>48</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1632</v>
+        <v>1653</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -10286,19 +10358,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1633</v>
+        <v>1654</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1634</v>
+        <v>1655</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1635</v>
+        <v>1656</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1636</v>
+        <v>1657</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1637</v>
+        <v>1658</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -10307,13 +10379,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1630</v>
+        <v>1651</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1638</v>
+        <v>1659</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -10322,7 +10394,7 @@
         <v>48</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1639</v>
+        <v>1660</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -10331,19 +10403,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1640</v>
+        <v>1661</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1641</v>
+        <v>1662</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1642</v>
+        <v>1663</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1643</v>
+        <v>1664</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1644</v>
+        <v>1665</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -10352,13 +10424,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1630</v>
+        <v>1651</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1645</v>
+        <v>1666</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -10367,7 +10439,7 @@
         <v>48</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1646</v>
+        <v>1667</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -10376,34 +10448,34 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1647</v>
+        <v>1668</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1648</v>
+        <v>1669</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1649</v>
+        <v>1670</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1650</v>
+        <v>1671</v>
       </c>
       <c r="K5" s="6" t="s">
+        <v>1672</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>1651</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>1630</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1652</v>
+        <v>1673</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>110</v>
@@ -10412,7 +10484,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1653</v>
+        <v>1674</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>150</v>
@@ -10421,19 +10493,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1654</v>
+        <v>1675</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1655</v>
+        <v>1676</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1656</v>
+        <v>1677</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1657</v>
+        <v>1678</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1658</v>
+        <v>1679</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>6</v>
@@ -10445,12 +10517,12 @@
         <v>157</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>1659</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1660</v>
+        <v>1681</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -10459,7 +10531,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1661</v>
+        <v>1682</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -10468,19 +10540,19 @@
         <v>188</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1662</v>
+        <v>1683</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1663</v>
+        <v>1684</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1664</v>
+        <v>1685</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1665</v>
+        <v>1686</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1666</v>
+        <v>1687</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>6</v>
@@ -10492,12 +10564,12 @@
         <v>157</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>1667</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1668</v>
+        <v>1689</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -10506,7 +10578,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1669</v>
+        <v>1690</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -10515,19 +10587,19 @@
         <v>151</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1670</v>
+        <v>1691</v>
       </c>
       <c r="H8" s="6" t="s">
+        <v>1692</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>1693</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>1671</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>1672</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>1650</v>
-      </c>
       <c r="K8" s="6" t="s">
-        <v>1673</v>
+        <v>1694</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -10536,13 +10608,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1630</v>
+        <v>1651</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1674</v>
+        <v>1695</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -10551,7 +10623,7 @@
         <v>48</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1675</v>
+        <v>1696</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -10560,19 +10632,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1676</v>
+        <v>1697</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1677</v>
+        <v>1698</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1678</v>
+        <v>1699</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1650</v>
+        <v>1671</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1679</v>
+        <v>1700</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -10581,13 +10653,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1630</v>
+        <v>1651</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1680</v>
+        <v>1701</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -10596,7 +10668,7 @@
         <v>48</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1681</v>
+        <v>1702</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -10605,19 +10677,19 @@
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1682</v>
+        <v>1703</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1683</v>
+        <v>1704</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1684</v>
+        <v>1705</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1650</v>
+        <v>1671</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1685</v>
+        <v>1706</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -10626,13 +10698,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1630</v>
+        <v>1651</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1686</v>
+        <v>1707</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -10641,7 +10713,7 @@
         <v>48</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1687</v>
+        <v>1708</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -10650,19 +10722,19 @@
         <v>188</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1688</v>
+        <v>1709</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1689</v>
+        <v>1710</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1690</v>
+        <v>1711</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1650</v>
+        <v>1671</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1691</v>
+        <v>1712</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -10671,13 +10743,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1630</v>
+        <v>1651</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1692</v>
+        <v>1713</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -10686,7 +10758,7 @@
         <v>48</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1693</v>
+        <v>1714</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>150</v>
@@ -10695,19 +10767,19 @@
         <v>188</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1694</v>
+        <v>1715</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1695</v>
+        <v>1716</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1696</v>
+        <v>1717</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1697</v>
+        <v>1718</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1698</v>
+        <v>1719</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -10716,10 +10788,10 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1630</v>
+        <v>1651</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>1699</v>
+        <v>1720</v>
       </c>
     </row>
   </sheetData>
@@ -12384,7 +12456,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="true" style="0"/>
@@ -13304,13 +13376,13 @@
         <v>4</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>104</v>
@@ -13328,19 +13400,19 @@
         <v>151</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>166</v>
@@ -13349,13 +13421,13 @@
         <v>4</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="7" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>104</v>
@@ -13364,13 +13436,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>160</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>458</v>
@@ -13394,13 +13466,13 @@
         <v>4</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>104</v>
@@ -13409,13 +13481,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>465</v>
@@ -13439,7 +13511,7 @@
         <v>4</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="O23" s="6"/>
     </row>
@@ -13457,7 +13529,7 @@
         <v>471</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>188</v>
@@ -13478,13 +13550,13 @@
         <v>476</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="M24" s="8" t="s">
-        <v>6</v>
+        <v>166</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>157</v>
+        <v>430</v>
       </c>
       <c r="O24" s="6"/>
     </row>
@@ -13499,43 +13571,43 @@
         <v>12</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>424</v>
+        <v>478</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>160</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>6</v>
+        <v>166</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>4</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>157</v>
+        <v>430</v>
       </c>
       <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>104</v>
@@ -13544,45 +13616,43 @@
         <v>12</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>395</v>
+        <v>485</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>372</v>
+        <v>487</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>6</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>488</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="7" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>104</v>
@@ -13591,42 +13661,134 @@
         <v>12</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>160</v>
       </c>
       <c r="F27" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="O27" s="6"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>490</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>491</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N27" s="6" t="s">
+      <c r="G28" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N28" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="O27" s="6"/>
+      <c r="O28" s="6" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="O29" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O27"/>
+  <autoFilter ref="A1:O29"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
@@ -13716,7 +13878,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>104</v>
@@ -13725,7 +13887,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>150</v>
@@ -13734,19 +13896,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -13755,13 +13917,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>104</v>
@@ -13770,7 +13932,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>150</v>
@@ -13779,19 +13941,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -13800,13 +13962,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>104</v>
@@ -13815,7 +13977,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>150</v>
@@ -13824,34 +13986,34 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="K4" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>516</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>502</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>104</v>
@@ -13860,7 +14022,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>150</v>
@@ -13869,19 +14031,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -13890,13 +14052,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>104</v>
@@ -13905,7 +14067,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>150</v>
@@ -13914,19 +14076,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -13935,13 +14097,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>107</v>
@@ -13950,7 +14112,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>533</v>
+        <v>547</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>150</v>
@@ -13959,19 +14121,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -13980,13 +14142,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>107</v>
@@ -13995,7 +14157,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>541</v>
+        <v>555</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>150</v>
@@ -14004,19 +14166,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>542</v>
+        <v>556</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -14025,13 +14187,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -14040,28 +14202,28 @@
         <v>16</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -14070,13 +14232,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>170</v>
@@ -14085,7 +14247,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -14094,19 +14256,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>190</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -14115,7 +14277,7 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="O10" s="6"/>
     </row>
@@ -14141,7 +14303,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="true" style="0"/>
@@ -14210,7 +14372,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>107</v>
@@ -14219,7 +14381,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>150</v>
@@ -14228,19 +14390,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>565</v>
+        <v>579</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -14249,13 +14411,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>107</v>
@@ -14264,7 +14426,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -14273,19 +14435,19 @@
         <v>188</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -14294,13 +14456,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>107</v>
@@ -14309,7 +14471,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -14318,19 +14480,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -14339,13 +14501,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>107</v>
@@ -14354,7 +14516,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>150</v>
@@ -14363,19 +14525,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>585</v>
+        <v>599</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -14384,13 +14546,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>107</v>
@@ -14399,7 +14561,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>150</v>
@@ -14408,19 +14570,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>592</v>
+        <v>606</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>593</v>
+        <v>607</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -14429,13 +14591,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>107</v>
@@ -14444,7 +14606,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -14453,19 +14615,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -14474,13 +14636,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>107</v>
@@ -14489,7 +14651,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -14498,19 +14660,19 @@
         <v>151</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -14519,13 +14681,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>568</v>
+        <v>622</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>107</v>
@@ -14534,7 +14696,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>464</v>
+        <v>610</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -14543,19 +14705,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>610</v>
+        <v>625</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>611</v>
+        <v>626</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>612</v>
+        <v>627</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>613</v>
+        <v>628</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -14564,13 +14726,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>568</v>
+        <v>622</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>614</v>
+        <v>629</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>107</v>
@@ -14579,7 +14741,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>615</v>
+        <v>478</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -14588,19 +14750,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>617</v>
+        <v>631</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>618</v>
+        <v>632</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>619</v>
+        <v>633</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>620</v>
+        <v>634</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -14609,22 +14771,22 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>621</v>
+        <v>635</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>622</v>
+        <v>636</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -14633,19 +14795,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>623</v>
+        <v>637</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>624</v>
+        <v>638</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>625</v>
+        <v>639</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>627</v>
+        <v>641</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -14654,13 +14816,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>628</v>
+        <v>642</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -14669,28 +14831,28 @@
         <v>20</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>629</v>
+        <v>643</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>631</v>
+        <v>645</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>632</v>
+        <v>646</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>633</v>
+        <v>647</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -14699,13 +14861,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>635</v>
+        <v>582</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>636</v>
+        <v>649</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -14714,28 +14876,28 @@
         <v>20</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>637</v>
+        <v>650</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>150</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>638</v>
+        <v>651</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>639</v>
+        <v>652</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>640</v>
+        <v>653</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>641</v>
+        <v>654</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -14744,13 +14906,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>643</v>
+        <v>656</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>644</v>
+        <v>657</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>110</v>
@@ -14759,28 +14921,28 @@
         <v>20</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>637</v>
+        <v>658</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>647</v>
+        <v>661</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>641</v>
+        <v>662</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -14789,13 +14951,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>643</v>
+        <v>664</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -14804,28 +14966,28 @@
         <v>20</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>653</v>
+        <v>668</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -14834,13 +14996,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>657</v>
+        <v>670</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -14849,7 +15011,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>658</v>
+        <v>671</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>150</v>
@@ -14858,19 +15020,19 @@
         <v>151</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>660</v>
+        <v>673</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>662</v>
+        <v>675</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>663</v>
+        <v>676</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -14879,14 +15041,59 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>664</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>665</v>
+        <v>677</v>
+      </c>
+      <c r="O16" s="6"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>686</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O16"/>
+  <autoFilter ref="A1:O17"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
@@ -14976,7 +15183,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -14985,7 +15192,7 @@
         <v>24</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>667</v>
+        <v>688</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>150</v>
@@ -14994,19 +15201,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>668</v>
+        <v>689</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>669</v>
+        <v>690</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>671</v>
+        <v>692</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>672</v>
+        <v>693</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -15015,13 +15222,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>674</v>
+        <v>695</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -15030,7 +15237,7 @@
         <v>24</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>667</v>
+        <v>688</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -15039,19 +15246,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>675</v>
+        <v>696</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>676</v>
+        <v>697</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>677</v>
+        <v>698</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>678</v>
+        <v>699</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>679</v>
+        <v>700</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -15060,13 +15267,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>680</v>
+        <v>701</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -15075,7 +15282,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>667</v>
+        <v>688</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -15084,19 +15291,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>681</v>
+        <v>702</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>682</v>
+        <v>703</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>683</v>
+        <v>704</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>685</v>
+        <v>706</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -15105,13 +15312,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>686</v>
+        <v>707</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>107</v>
@@ -15120,7 +15327,7 @@
         <v>24</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>687</v>
+        <v>708</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -15129,19 +15336,19 @@
         <v>188</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>688</v>
+        <v>709</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>689</v>
+        <v>710</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>690</v>
+        <v>711</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>691</v>
+        <v>712</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>692</v>
+        <v>713</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -15150,13 +15357,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>693</v>
+        <v>714</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>107</v>
@@ -15165,7 +15372,7 @@
         <v>24</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>687</v>
+        <v>708</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -15174,34 +15381,34 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N6" s="6" t="s">
         <v>694</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>695</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>696</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>697</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>698</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>673</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>699</v>
+        <v>720</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>107</v>
@@ -15210,7 +15417,7 @@
         <v>24</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>700</v>
+        <v>721</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -15219,19 +15426,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>701</v>
+        <v>722</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>702</v>
+        <v>723</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>703</v>
+        <v>724</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>704</v>
+        <v>725</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>705</v>
+        <v>726</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -15240,13 +15447,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>706</v>
+        <v>727</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -15255,28 +15462,28 @@
         <v>24</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>707</v>
+        <v>728</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>708</v>
+        <v>729</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>709</v>
+        <v>730</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>710</v>
+        <v>731</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>712</v>
+        <v>733</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -15285,13 +15492,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>713</v>
+        <v>734</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>127</v>
@@ -15300,28 +15507,28 @@
         <v>24</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>714</v>
+        <v>735</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>715</v>
+        <v>736</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>716</v>
+        <v>737</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>717</v>
+        <v>738</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>719</v>
+        <v>740</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -15330,13 +15537,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -15345,7 +15552,7 @@
         <v>24</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>721</v>
+        <v>742</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -15354,19 +15561,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>724</v>
+        <v>745</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>726</v>
+        <v>747</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -15375,13 +15582,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>728</v>
+        <v>749</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -15390,7 +15597,7 @@
         <v>24</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>721</v>
+        <v>742</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -15399,19 +15606,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>729</v>
+        <v>750</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>730</v>
+        <v>751</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>731</v>
+        <v>752</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>733</v>
+        <v>754</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -15420,13 +15627,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>734</v>
+        <v>755</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -15435,7 +15642,7 @@
         <v>24</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -15444,19 +15651,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>736</v>
+        <v>757</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>738</v>
+        <v>759</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>739</v>
+        <v>760</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>740</v>
+        <v>761</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -15465,13 +15672,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>741</v>
+        <v>762</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -15480,7 +15687,7 @@
         <v>24</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>742</v>
+        <v>763</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -15489,19 +15696,19 @@
         <v>151</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>743</v>
+        <v>764</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>744</v>
+        <v>765</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>745</v>
+        <v>766</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>746</v>
+        <v>767</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -15510,13 +15717,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>747</v>
+        <v>768</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>110</v>
@@ -15525,7 +15732,7 @@
         <v>24</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>748</v>
+        <v>769</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -15534,19 +15741,19 @@
         <v>188</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>749</v>
+        <v>770</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>750</v>
+        <v>771</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>751</v>
+        <v>772</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>752</v>
+        <v>773</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -15555,13 +15762,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>754</v>
+        <v>775</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -15570,7 +15777,7 @@
         <v>24</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>755</v>
+        <v>776</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>150</v>
@@ -15579,19 +15786,19 @@
         <v>151</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>756</v>
+        <v>777</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>757</v>
+        <v>778</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>758</v>
+        <v>779</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>759</v>
+        <v>780</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>760</v>
+        <v>781</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -15600,13 +15807,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>761</v>
+        <v>782</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -15615,7 +15822,7 @@
         <v>24</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>762</v>
+        <v>783</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>160</v>
@@ -15624,19 +15831,19 @@
         <v>151</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>763</v>
+        <v>784</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>764</v>
+        <v>785</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>765</v>
+        <v>786</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>766</v>
+        <v>787</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>767</v>
+        <v>788</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -15645,13 +15852,13 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>768</v>
+        <v>789</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>110</v>
@@ -15660,7 +15867,7 @@
         <v>24</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>769</v>
+        <v>790</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>160</v>
@@ -15669,19 +15876,19 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>770</v>
+        <v>791</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>771</v>
+        <v>792</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>773</v>
+        <v>794</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>774</v>
+        <v>795</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>166</v>
@@ -15690,13 +15897,13 @@
         <v>4</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7" t="s">
-        <v>775</v>
+        <v>796</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>110</v>
@@ -15705,28 +15912,28 @@
         <v>24</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>777</v>
+        <v>798</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>778</v>
+        <v>799</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>779</v>
+        <v>800</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>780</v>
+        <v>801</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>166</v>
@@ -15735,15 +15942,15 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>782</v>
+        <v>803</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>783</v>
+        <v>804</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="7" t="s">
-        <v>784</v>
+        <v>805</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>110</v>
@@ -15752,7 +15959,7 @@
         <v>24</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>785</v>
+        <v>806</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>150</v>
@@ -15761,19 +15968,19 @@
         <v>151</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>786</v>
+        <v>807</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>166</v>
@@ -15782,13 +15989,13 @@
         <v>4</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="7" t="s">
-        <v>791</v>
+        <v>812</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>110</v>
@@ -15797,7 +16004,7 @@
         <v>24</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>792</v>
+        <v>813</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>160</v>
@@ -15806,19 +16013,19 @@
         <v>151</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>794</v>
+        <v>815</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>795</v>
+        <v>816</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>796</v>
+        <v>817</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>797</v>
+        <v>818</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>166</v>
@@ -15827,13 +16034,13 @@
         <v>4</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="7" t="s">
-        <v>799</v>
+        <v>820</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>110</v>
@@ -15842,7 +16049,7 @@
         <v>24</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>800</v>
+        <v>821</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>160</v>
@@ -15851,19 +16058,19 @@
         <v>151</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>801</v>
+        <v>822</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>802</v>
+        <v>823</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>803</v>
+        <v>824</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>804</v>
+        <v>825</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>805</v>
+        <v>826</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>166</v>
@@ -15872,13 +16079,13 @@
         <v>4</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="7" t="s">
-        <v>806</v>
+        <v>827</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>110</v>
@@ -15887,7 +16094,7 @@
         <v>24</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>792</v>
+        <v>813</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>160</v>
@@ -15896,19 +16103,19 @@
         <v>188</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>810</v>
+        <v>831</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>811</v>
+        <v>832</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>166</v>
@@ -15917,13 +16124,13 @@
         <v>4</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="7" t="s">
-        <v>812</v>
+        <v>833</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>107</v>
@@ -15932,7 +16139,7 @@
         <v>24</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>813</v>
+        <v>834</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>160</v>
@@ -15941,19 +16148,19 @@
         <v>151</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>814</v>
+        <v>835</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>815</v>
+        <v>836</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>816</v>
+        <v>837</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>817</v>
+        <v>838</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>818</v>
+        <v>839</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>166</v>
@@ -15962,13 +16169,13 @@
         <v>4</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="7" t="s">
-        <v>819</v>
+        <v>840</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>107</v>
@@ -15977,7 +16184,7 @@
         <v>24</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>820</v>
+        <v>841</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>160</v>
@@ -15986,19 +16193,19 @@
         <v>151</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>821</v>
+        <v>842</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>822</v>
+        <v>843</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>823</v>
+        <v>844</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>824</v>
+        <v>845</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>825</v>
+        <v>846</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>166</v>
@@ -16007,13 +16214,13 @@
         <v>4</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="7" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>110</v>
@@ -16022,7 +16229,7 @@
         <v>24</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>160</v>
@@ -16031,19 +16238,19 @@
         <v>151</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>831</v>
+        <v>852</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>832</v>
+        <v>853</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>166</v>
@@ -16052,13 +16259,13 @@
         <v>4</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="7" t="s">
-        <v>833</v>
+        <v>854</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>110</v>
@@ -16067,7 +16274,7 @@
         <v>24</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>834</v>
+        <v>855</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>160</v>
@@ -16076,19 +16283,19 @@
         <v>188</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>835</v>
+        <v>856</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>836</v>
+        <v>857</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>837</v>
+        <v>858</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>838</v>
+        <v>859</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>839</v>
+        <v>860</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>166</v>
@@ -16097,13 +16304,13 @@
         <v>4</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="7" t="s">
-        <v>840</v>
+        <v>861</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>107</v>
@@ -16112,7 +16319,7 @@
         <v>24</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>813</v>
+        <v>834</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>160</v>
@@ -16121,19 +16328,19 @@
         <v>188</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>841</v>
+        <v>862</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>842</v>
+        <v>863</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>843</v>
+        <v>864</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>845</v>
+        <v>866</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>166</v>
@@ -16142,13 +16349,13 @@
         <v>4</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="7" t="s">
-        <v>846</v>
+        <v>867</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>104</v>
@@ -16157,7 +16364,7 @@
         <v>24</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>813</v>
+        <v>834</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>160</v>
@@ -16166,19 +16373,19 @@
         <v>188</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>847</v>
+        <v>868</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>848</v>
+        <v>869</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>849</v>
+        <v>870</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>831</v>
+        <v>852</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>166</v>
@@ -16187,13 +16394,13 @@
         <v>4</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="O28" s="6"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="7" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>110</v>
@@ -16202,7 +16409,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>852</v>
+        <v>873</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>150</v>
@@ -16211,19 +16418,19 @@
         <v>151</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>853</v>
+        <v>874</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>854</v>
+        <v>875</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>855</v>
+        <v>876</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>856</v>
+        <v>877</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>857</v>
+        <v>878</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>166</v>
@@ -16232,13 +16439,13 @@
         <v>4</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>858</v>
+        <v>879</v>
       </c>
       <c r="O29" s="6"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="7" t="s">
-        <v>859</v>
+        <v>880</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>104</v>
@@ -16247,7 +16454,7 @@
         <v>24</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>150</v>
@@ -16256,19 +16463,19 @@
         <v>151</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>861</v>
+        <v>882</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>862</v>
+        <v>883</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>864</v>
+        <v>885</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>865</v>
+        <v>886</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>166</v>
@@ -16277,13 +16484,13 @@
         <v>4</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>866</v>
+        <v>887</v>
       </c>
       <c r="O30" s="6"/>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="7" t="s">
-        <v>867</v>
+        <v>888</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>107</v>
@@ -16292,7 +16499,7 @@
         <v>24</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>160</v>
@@ -16301,19 +16508,19 @@
         <v>151</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>868</v>
+        <v>889</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>869</v>
+        <v>890</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>870</v>
+        <v>891</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>871</v>
+        <v>892</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>872</v>
+        <v>893</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>166</v>
@@ -16322,13 +16529,13 @@
         <v>4</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>866</v>
+        <v>887</v>
       </c>
       <c r="O31" s="6"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="7" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>104</v>
@@ -16337,7 +16544,7 @@
         <v>24</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>160</v>
@@ -16346,19 +16553,19 @@
         <v>188</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>875</v>
+        <v>896</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>876</v>
+        <v>897</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>877</v>
+        <v>898</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>878</v>
+        <v>899</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>166</v>
@@ -16367,15 +16574,15 @@
         <v>4</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>866</v>
+        <v>887</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>879</v>
+        <v>900</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="7" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>107</v>
@@ -16384,7 +16591,7 @@
         <v>24</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>160</v>
@@ -16393,19 +16600,19 @@
         <v>188</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>881</v>
+        <v>902</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>882</v>
+        <v>903</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>883</v>
+        <v>904</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>884</v>
+        <v>905</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>885</v>
+        <v>906</v>
       </c>
       <c r="L33" s="6" t="s">
         <v>166</v>
@@ -16414,13 +16621,13 @@
         <v>4</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>866</v>
+        <v>887</v>
       </c>
       <c r="O33" s="6"/>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="7" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>104</v>
@@ -16429,7 +16636,7 @@
         <v>24</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>150</v>
@@ -16438,19 +16645,19 @@
         <v>151</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>888</v>
+        <v>909</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>890</v>
+        <v>911</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>891</v>
+        <v>912</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>892</v>
+        <v>913</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>166</v>
@@ -16459,15 +16666,15 @@
         <v>4</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="7" t="s">
-        <v>895</v>
+        <v>916</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>107</v>
@@ -16476,7 +16683,7 @@
         <v>24</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>160</v>
@@ -16485,19 +16692,19 @@
         <v>151</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>896</v>
+        <v>917</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>898</v>
+        <v>919</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="L35" s="6" t="s">
         <v>166</v>
@@ -16506,13 +16713,13 @@
         <v>4</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="O35" s="6"/>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="7" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>104</v>
@@ -16521,7 +16728,7 @@
         <v>24</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>160</v>
@@ -16530,19 +16737,19 @@
         <v>188</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>902</v>
+        <v>923</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>903</v>
+        <v>924</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>904</v>
+        <v>925</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>906</v>
+        <v>927</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>166</v>
@@ -16551,13 +16758,13 @@
         <v>4</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="O36" s="6"/>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="7" t="s">
-        <v>907</v>
+        <v>928</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>110</v>
@@ -16566,7 +16773,7 @@
         <v>24</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>150</v>
@@ -16575,19 +16782,19 @@
         <v>151</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>910</v>
+        <v>931</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="L37" s="6" t="s">
         <v>166</v>
@@ -16596,15 +16803,15 @@
         <v>4</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>913</v>
+        <v>934</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>914</v>
+        <v>935</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="7" t="s">
-        <v>915</v>
+        <v>936</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>110</v>
@@ -16613,7 +16820,7 @@
         <v>24</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -16622,19 +16829,19 @@
         <v>151</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>916</v>
+        <v>937</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>917</v>
+        <v>938</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>918</v>
+        <v>939</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>919</v>
+        <v>940</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>920</v>
+        <v>941</v>
       </c>
       <c r="L38" s="6" t="s">
         <v>166</v>
@@ -16643,13 +16850,13 @@
         <v>4</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>913</v>
+        <v>934</v>
       </c>
       <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="7" t="s">
-        <v>921</v>
+        <v>942</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>110</v>
@@ -16658,28 +16865,28 @@
         <v>24</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>922</v>
+        <v>943</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>923</v>
+        <v>944</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>924</v>
+        <v>945</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>773</v>
+        <v>794</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>925</v>
+        <v>946</v>
       </c>
       <c r="L39" s="6" t="s">
         <v>166</v>
@@ -16688,13 +16895,13 @@
         <v>4</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>913</v>
+        <v>934</v>
       </c>
       <c r="O39" s="6"/>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" s="7" t="s">
-        <v>926</v>
+        <v>947</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>110</v>
@@ -16703,28 +16910,28 @@
         <v>24</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>927</v>
+        <v>948</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>928</v>
+        <v>949</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>929</v>
+        <v>950</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>930</v>
+        <v>951</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>931</v>
+        <v>952</v>
       </c>
       <c r="L40" s="6" t="s">
         <v>166</v>
@@ -16733,13 +16940,13 @@
         <v>4</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>913</v>
+        <v>934</v>
       </c>
       <c r="O40" s="6"/>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="7" t="s">
-        <v>932</v>
+        <v>953</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>110</v>
@@ -16748,7 +16955,7 @@
         <v>24</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>933</v>
+        <v>954</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>150</v>
@@ -16757,19 +16964,19 @@
         <v>151</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>934</v>
+        <v>955</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>935</v>
+        <v>956</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>936</v>
+        <v>957</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>937</v>
+        <v>958</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>938</v>
+        <v>959</v>
       </c>
       <c r="L41" s="6" t="s">
         <v>166</v>
@@ -16778,15 +16985,15 @@
         <v>4</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>664</v>
+        <v>685</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="7" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>110</v>
@@ -16795,7 +17002,7 @@
         <v>24</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>933</v>
+        <v>954</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -16804,19 +17011,19 @@
         <v>151</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>941</v>
+        <v>962</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>942</v>
+        <v>963</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>944</v>
+        <v>965</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>945</v>
+        <v>966</v>
       </c>
       <c r="L42" s="6" t="s">
         <v>166</v>
@@ -16825,13 +17032,13 @@
         <v>4</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>664</v>
+        <v>685</v>
       </c>
       <c r="O42" s="6"/>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="7" t="s">
-        <v>946</v>
+        <v>967</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>110</v>
@@ -16840,7 +17047,7 @@
         <v>24</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>947</v>
+        <v>968</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>150</v>
@@ -16849,19 +17056,19 @@
         <v>151</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>949</v>
+        <v>970</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>950</v>
+        <v>971</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>951</v>
+        <v>972</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>952</v>
+        <v>973</v>
       </c>
       <c r="L43" s="6" t="s">
         <v>166</v>
@@ -16870,22 +17077,22 @@
         <v>4</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>664</v>
+        <v>685</v>
       </c>
       <c r="O43" s="6"/>
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="7" t="s">
-        <v>953</v>
+        <v>974</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>954</v>
+        <v>975</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>933</v>
+        <v>954</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -16894,19 +17101,19 @@
         <v>151</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>957</v>
+        <v>978</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>958</v>
+        <v>979</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>959</v>
+        <v>980</v>
       </c>
       <c r="L44" s="6" t="s">
         <v>166</v>
@@ -16915,24 +17122,24 @@
         <v>4</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>664</v>
+        <v>685</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>960</v>
+        <v>981</v>
       </c>
     </row>
     <row r="45" spans="1:15">
       <c r="A45" s="7" t="s">
-        <v>961</v>
+        <v>982</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>962</v>
+        <v>983</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>160</v>
@@ -16941,19 +17148,19 @@
         <v>151</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>963</v>
+        <v>984</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>964</v>
+        <v>985</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>965</v>
+        <v>986</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>966</v>
+        <v>987</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>967</v>
+        <v>988</v>
       </c>
       <c r="L45" s="6" t="s">
         <v>166</v>
@@ -16962,24 +17169,24 @@
         <v>4</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>968</v>
+        <v>989</v>
       </c>
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="7" t="s">
-        <v>969</v>
+        <v>990</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>962</v>
+        <v>983</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>160</v>
@@ -16988,19 +17195,19 @@
         <v>188</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>970</v>
+        <v>991</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>971</v>
+        <v>992</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>973</v>
+        <v>994</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>974</v>
+        <v>995</v>
       </c>
       <c r="L46" s="6" t="s">
         <v>166</v>
@@ -17009,24 +17216,24 @@
         <v>4</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>975</v>
+        <v>996</v>
       </c>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="7" t="s">
-        <v>976</v>
+        <v>997</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>962</v>
+        <v>983</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>160</v>
@@ -17035,19 +17242,19 @@
         <v>151</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>977</v>
+        <v>998</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>978</v>
+        <v>999</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>979</v>
+        <v>1000</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>980</v>
+        <v>1001</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>981</v>
+        <v>1002</v>
       </c>
       <c r="L47" s="6" t="s">
         <v>166</v>
@@ -17056,24 +17263,24 @@
         <v>4</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>982</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="7" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>983</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>962</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>150</v>
@@ -17082,19 +17289,19 @@
         <v>254</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>984</v>
+        <v>1005</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>985</v>
+        <v>1006</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>986</v>
+        <v>1007</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>987</v>
+        <v>1008</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>988</v>
+        <v>1009</v>
       </c>
       <c r="L48" s="6" t="s">
         <v>166</v>
@@ -17103,24 +17310,24 @@
         <v>4</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>989</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" s="7" t="s">
-        <v>990</v>
+        <v>1011</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>962</v>
+        <v>983</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>160</v>
@@ -17129,19 +17336,19 @@
         <v>151</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>991</v>
+        <v>1012</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>992</v>
+        <v>1013</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>993</v>
+        <v>1014</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>995</v>
+        <v>1016</v>
       </c>
       <c r="L49" s="6" t="s">
         <v>166</v>
@@ -17150,15 +17357,15 @@
         <v>4</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>996</v>
+        <v>1017</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>997</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="7" t="s">
-        <v>998</v>
+        <v>1019</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>110</v>
@@ -17167,7 +17374,7 @@
         <v>24</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>999</v>
+        <v>1020</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>160</v>
@@ -17176,19 +17383,19 @@
         <v>151</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>1000</v>
+        <v>1021</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>1001</v>
+        <v>1022</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>1002</v>
+        <v>1023</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>1003</v>
+        <v>1024</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>1004</v>
+        <v>1025</v>
       </c>
       <c r="L50" s="6" t="s">
         <v>166</v>
@@ -17197,13 +17404,13 @@
         <v>4</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>996</v>
+        <v>1017</v>
       </c>
       <c r="O50" s="6"/>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="7" t="s">
-        <v>1005</v>
+        <v>1026</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>110</v>
@@ -17212,7 +17419,7 @@
         <v>24</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>999</v>
+        <v>1020</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>160</v>
@@ -17221,19 +17428,19 @@
         <v>151</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>1006</v>
+        <v>1027</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>1008</v>
+        <v>1029</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>1009</v>
+        <v>1030</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>1010</v>
+        <v>1031</v>
       </c>
       <c r="L51" s="6" t="s">
         <v>166</v>
@@ -17242,7 +17449,7 @@
         <v>4</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>996</v>
+        <v>1017</v>
       </c>
       <c r="O51" s="6"/>
     </row>
@@ -17337,7 +17544,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1011</v>
+        <v>1032</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -17346,7 +17553,7 @@
         <v>28</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1012</v>
+        <v>1033</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -17355,19 +17562,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1013</v>
+        <v>1034</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1014</v>
+        <v>1035</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1015</v>
+        <v>1036</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1016</v>
+        <v>1037</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1017</v>
+        <v>1038</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -17376,13 +17583,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1018</v>
+        <v>1039</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1019</v>
+        <v>1040</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -17391,28 +17598,28 @@
         <v>28</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1020</v>
+        <v>1041</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1021</v>
+        <v>1042</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1022</v>
+        <v>1043</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1023</v>
+        <v>1044</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1024</v>
+        <v>1045</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1025</v>
+        <v>1046</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -17421,13 +17628,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1018</v>
+        <v>1039</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1026</v>
+        <v>1047</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -17436,7 +17643,7 @@
         <v>28</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1020</v>
+        <v>1041</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>150</v>
@@ -17445,19 +17652,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1027</v>
+        <v>1048</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1028</v>
+        <v>1049</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1029</v>
+        <v>1050</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1030</v>
+        <v>1051</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1031</v>
+        <v>1052</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -17466,13 +17673,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1018</v>
+        <v>1039</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1032</v>
+        <v>1053</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -17481,7 +17688,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1033</v>
+        <v>1054</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -17490,19 +17697,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1034</v>
+        <v>1055</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1035</v>
+        <v>1056</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1036</v>
+        <v>1057</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1037</v>
+        <v>1058</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1038</v>
+        <v>1059</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -17511,13 +17718,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1018</v>
+        <v>1039</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1039</v>
+        <v>1060</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>110</v>
@@ -17526,7 +17733,7 @@
         <v>28</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1040</v>
+        <v>1061</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -17535,19 +17742,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1041</v>
+        <v>1062</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1042</v>
+        <v>1063</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1043</v>
+        <v>1064</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1044</v>
+        <v>1065</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1045</v>
+        <v>1066</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -17556,13 +17763,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1018</v>
+        <v>1039</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1046</v>
+        <v>1067</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -17571,7 +17778,7 @@
         <v>28</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1047</v>
+        <v>1068</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -17580,19 +17787,19 @@
         <v>188</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1048</v>
+        <v>1069</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1049</v>
+        <v>1070</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1050</v>
+        <v>1071</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1051</v>
+        <v>1072</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1052</v>
+        <v>1073</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -17601,13 +17808,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1053</v>
+        <v>1074</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1054</v>
+        <v>1075</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -17616,7 +17823,7 @@
         <v>28</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1055</v>
+        <v>1076</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -17625,19 +17832,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1056</v>
+        <v>1077</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1057</v>
+        <v>1078</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1058</v>
+        <v>1079</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1060</v>
+        <v>1081</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>6</v>
@@ -17649,12 +17856,12 @@
         <v>157</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>1061</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1062</v>
+        <v>1083</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -17663,7 +17870,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1063</v>
+        <v>1084</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>150</v>
@@ -17672,19 +17879,19 @@
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1065</v>
+        <v>1086</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1066</v>
+        <v>1087</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1067</v>
+        <v>1088</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1068</v>
+        <v>1089</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>6</v>
@@ -17696,12 +17903,12 @@
         <v>157</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>1069</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1070</v>
+        <v>1091</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -17710,7 +17917,7 @@
         <v>28</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1071</v>
+        <v>1092</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -17719,19 +17926,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1073</v>
+        <v>1094</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1075</v>
+        <v>1096</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>6</v>
@@ -17743,12 +17950,12 @@
         <v>157</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>1077</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>104</v>
@@ -17757,7 +17964,7 @@
         <v>28</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1079</v>
+        <v>1100</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>150</v>
@@ -17766,19 +17973,19 @@
         <v>254</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1080</v>
+        <v>1101</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1081</v>
+        <v>1102</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1083</v>
+        <v>1104</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1084</v>
+        <v>1105</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>6</v>

--- a/docs/test-cases/test-cases.xlsx
+++ b/docs/test-cases/test-cases.xlsx
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'01-AUTH'!$A$1:$O$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'02-ADMIN'!$A$1:$O$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'02-ADMIN'!$A$1:$O$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'03-STAT'!$A$1:$O$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'04-LECT'!$A$1:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'05-STU'!$A$1:$O$51</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1729">
   <si>
     <t>Nhóm</t>
   </si>
@@ -279,7 +279,7 @@
     <t>TC-ADMIN — Nhóm 02 — Quản trị người dùng, môn học &amp; lớp học phần</t>
   </si>
   <si>
-    <t>php artisan test tests/Feature/SubjectTest.php tests/Feature/AdminClassManagementTest.php tests/Feature/ClassMembershipStatusTest.php tests/Feature/ViewSmokeTest.php tests/Feature/AdminSoftDeleteTest.php</t>
+    <t>php artisan test tests/Feature/SubjectTest.php tests/Feature/AdminClassManagementTest.php tests/Feature/ClassMembershipStatusTest.php tests/Feature/ViewSmokeTest.php tests/Feature/AdminSoftDeleteTest.php tests/Feature/StudentQuickActionsTest.php</t>
   </si>
   <si>
     <t>TC-STAT — Nhóm 03 — Thống kê &amp; thông báo</t>
@@ -1683,6 +1683,34 @@
   </si>
   <si>
     <t>Môn mới 2 ⇒ 2 · trống/thiếu cột (môn mới) ⇒ 1 · môn đã có 2 bài + ô trống ⇒ giữ 2 · giá trị 3 ⇒ dòng lỗi</t>
+  </si>
+  <si>
+    <t>TC-ADMIN-29</t>
+  </si>
+  <si>
+    <t>L06 — Thao tác nhanh: Admin gửi email và reset mật khẩu sinh viên về mặc định; giảng viên KHÔNG có quyền</t>
+  </si>
+  <si>
+    <t>Đăng nhập admin; có 1 sinh viên trong lớp; môi trường test dùng MAIL_MAILER=array</t>
+  </si>
+  <si>
+    <t>Mở /students/{user_id} — chỉ Admin thấy 2 nút "Gửi email" và "Reset mật khẩu"
+Bấm "Gửi email" ⇒ modal nhập tiêu đề + nội dung ⇒ Gửi
+Bấm "Reset mật khẩu" ⇒ xác nhận ⇒ đọc flash trên màn hình
+Đăng xuất rồi đăng nhập bằng tài khoản sinh viên vừa reset (mật khẩu "password")
+Đăng nhập giảng viên rồi gọi trực tiếp 2 route (case âm)</t>
+  </si>
+  <si>
+    <t>POST /students/{id}/send-email {subject, message} · POST /students/{id}/reset-password</t>
+  </si>
+  <si>
+    <t>Gửi email: flash thành công, mail đúng người nhận/tiêu đề/nội dung · Reset: flash thành công, mật khẩu lưu là hash của "password", must_change_password=1, sinh viên đăng nhập bị đưa sang trang Đổi mật khẩu (chưa vào dashboard) · Giảng viên gọi trực tiếp ⇒ 403, không gửi mail và không đổi dữ liệu</t>
+  </si>
+  <si>
+    <t>tests/Feature/StudentQuickActionsTest.php</t>
+  </si>
+  <si>
+    <t>Chốt 5a-B (chỉ Admin, GV 403), 5b (reset về "password" + buộc đổi ở lần đăng nhập sau), 5c (đơn lẻ từng sinh viên, không bulk).</t>
   </si>
   <si>
     <t>TC-STAT-01</t>
@@ -6144,10 +6172,10 @@
         <v>14</v>
       </c>
       <c r="D3" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
@@ -6400,10 +6428,10 @@
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="4">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E13" s="4">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F13" s="4">
         <v>5</v>
@@ -6503,7 +6531,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>127</v>
@@ -6512,7 +6540,7 @@
         <v>32</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -6521,19 +6549,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -6542,13 +6570,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>127</v>
@@ -6557,7 +6585,7 @@
         <v>32</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -6566,19 +6594,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -6587,13 +6615,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>127</v>
@@ -6602,7 +6630,7 @@
         <v>32</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -6611,19 +6639,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -6632,13 +6660,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>127</v>
@@ -6647,7 +6675,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -6656,19 +6684,19 @@
         <v>188</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -6677,13 +6705,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>127</v>
@@ -6692,7 +6720,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -6701,19 +6729,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -6722,13 +6750,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>127</v>
@@ -6737,7 +6765,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -6746,19 +6774,19 @@
         <v>188</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -6767,13 +6795,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>127</v>
@@ -6782,7 +6810,7 @@
         <v>32</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -6791,19 +6819,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -6812,13 +6840,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>127</v>
@@ -6827,7 +6855,7 @@
         <v>32</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -6836,19 +6864,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -6857,15 +6885,15 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>127</v>
@@ -6874,7 +6902,7 @@
         <v>32</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -6883,19 +6911,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -6904,13 +6932,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -6919,7 +6947,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -6928,19 +6956,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -6949,13 +6977,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -6964,7 +6992,7 @@
         <v>32</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -6973,19 +7001,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -6994,13 +7022,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -7009,7 +7037,7 @@
         <v>32</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -7018,19 +7046,19 @@
         <v>151</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -7039,13 +7067,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>110</v>
@@ -7054,7 +7082,7 @@
         <v>32</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -7063,19 +7091,19 @@
         <v>151</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -7084,13 +7112,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -7099,7 +7127,7 @@
         <v>32</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -7108,19 +7136,19 @@
         <v>188</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -7129,13 +7157,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>104</v>
@@ -7144,7 +7172,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>160</v>
@@ -7153,19 +7181,19 @@
         <v>151</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -7174,13 +7202,13 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>104</v>
@@ -7189,7 +7217,7 @@
         <v>32</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>160</v>
@@ -7198,19 +7226,19 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>166</v>
@@ -7219,13 +7247,13 @@
         <v>4</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>104</v>
@@ -7234,7 +7262,7 @@
         <v>32</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>160</v>
@@ -7243,19 +7271,19 @@
         <v>151</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>166</v>
@@ -7264,13 +7292,13 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="7" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>104</v>
@@ -7279,7 +7307,7 @@
         <v>32</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>160</v>
@@ -7288,19 +7316,19 @@
         <v>188</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>166</v>
@@ -7309,13 +7337,13 @@
         <v>4</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="7" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>104</v>
@@ -7324,7 +7352,7 @@
         <v>32</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>160</v>
@@ -7333,19 +7361,19 @@
         <v>151</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>166</v>
@@ -7354,13 +7382,13 @@
         <v>4</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="7" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>104</v>
@@ -7369,7 +7397,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>160</v>
@@ -7378,19 +7406,19 @@
         <v>188</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>166</v>
@@ -7399,13 +7427,13 @@
         <v>4</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="7" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>110</v>
@@ -7414,7 +7442,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>160</v>
@@ -7423,19 +7451,19 @@
         <v>151</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>166</v>
@@ -7444,13 +7472,13 @@
         <v>4</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="7" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>104</v>
@@ -7459,7 +7487,7 @@
         <v>32</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>150</v>
@@ -7468,19 +7496,19 @@
         <v>188</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>166</v>
@@ -7489,13 +7517,13 @@
         <v>4</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="7" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>104</v>
@@ -7504,7 +7532,7 @@
         <v>32</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>150</v>
@@ -7513,19 +7541,19 @@
         <v>254</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>372</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>166</v>
@@ -7534,13 +7562,13 @@
         <v>4</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="7" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>104</v>
@@ -7549,7 +7577,7 @@
         <v>32</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>150</v>
@@ -7558,19 +7586,19 @@
         <v>188</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>166</v>
@@ -7579,13 +7607,13 @@
         <v>4</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="7" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>104</v>
@@ -7594,7 +7622,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>160</v>
@@ -7603,19 +7631,19 @@
         <v>188</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>372</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>166</v>
@@ -7624,13 +7652,13 @@
         <v>4</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="7" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>104</v>
@@ -7639,7 +7667,7 @@
         <v>32</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>150</v>
@@ -7648,19 +7676,19 @@
         <v>254</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>166</v>
@@ -7669,13 +7697,13 @@
         <v>4</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="7" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>110</v>
@@ -7684,7 +7712,7 @@
         <v>32</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>150</v>
@@ -7693,19 +7721,19 @@
         <v>151</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>6</v>
@@ -7714,10 +7742,10 @@
         <v>6</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
     </row>
   </sheetData>
@@ -7811,7 +7839,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -7820,7 +7848,7 @@
         <v>36</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -7829,19 +7857,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -7850,13 +7878,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -7865,7 +7893,7 @@
         <v>36</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -7874,19 +7902,19 @@
         <v>188</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -7895,13 +7923,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -7910,7 +7938,7 @@
         <v>36</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -7919,19 +7947,19 @@
         <v>151</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -7940,13 +7968,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -7955,28 +7983,28 @@
         <v>36</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1329</v>
+        <v>1337</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -7985,13 +8013,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>110</v>
@@ -8000,7 +8028,7 @@
         <v>36</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -8009,19 +8037,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1333</v>
+        <v>1341</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1335</v>
+        <v>1343</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -8030,13 +8058,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -8045,7 +8073,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -8054,19 +8082,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1343</v>
+        <v>1351</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -8075,15 +8103,15 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -8092,7 +8120,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -8101,19 +8129,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1349</v>
+        <v>1357</v>
       </c>
       <c r="I8" s="6" t="s">
+        <v>1358</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>1350</v>
       </c>
-      <c r="J8" s="6" t="s">
-        <v>1342</v>
-      </c>
       <c r="K8" s="6" t="s">
-        <v>1351</v>
+        <v>1359</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -8122,13 +8150,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1352</v>
+        <v>1360</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -8137,7 +8165,7 @@
         <v>36</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1353</v>
+        <v>1361</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -8146,19 +8174,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1354</v>
+        <v>1362</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1355</v>
+        <v>1363</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1356</v>
+        <v>1364</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1357</v>
+        <v>1365</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1358</v>
+        <v>1366</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -8167,13 +8195,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1359</v>
+        <v>1367</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -8182,7 +8210,7 @@
         <v>36</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>150</v>
@@ -8191,19 +8219,19 @@
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1361</v>
+        <v>1369</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -8212,13 +8240,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1365</v>
+        <v>1373</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>127</v>
@@ -8227,7 +8255,7 @@
         <v>36</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1366</v>
+        <v>1374</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -8236,19 +8264,19 @@
         <v>188</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1367</v>
+        <v>1375</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1369</v>
+        <v>1377</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1370</v>
+        <v>1378</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1371</v>
+        <v>1379</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -8257,13 +8285,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1372</v>
+        <v>1380</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>127</v>
@@ -8272,28 +8300,28 @@
         <v>36</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1373</v>
+        <v>1381</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1374</v>
+        <v>1382</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1375</v>
+        <v>1383</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1377</v>
+        <v>1385</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -8302,13 +8330,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1379</v>
+        <v>1387</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1380</v>
+        <v>1388</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>127</v>
@@ -8317,7 +8345,7 @@
         <v>36</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1381</v>
+        <v>1389</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -8326,19 +8354,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1382</v>
+        <v>1390</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1383</v>
+        <v>1391</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -8347,13 +8375,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1386</v>
+        <v>1394</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>127</v>
@@ -8362,7 +8390,7 @@
         <v>36</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -8371,19 +8399,19 @@
         <v>151</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1388</v>
+        <v>1396</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1389</v>
+        <v>1397</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1390</v>
+        <v>1398</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1391</v>
+        <v>1399</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -8392,13 +8420,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1393</v>
+        <v>1401</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>127</v>
@@ -8407,7 +8435,7 @@
         <v>36</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1394</v>
+        <v>1402</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -8416,19 +8444,19 @@
         <v>188</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1395</v>
+        <v>1403</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1396</v>
+        <v>1404</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1397</v>
+        <v>1405</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1398</v>
+        <v>1406</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1399</v>
+        <v>1407</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -8437,13 +8465,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>1400</v>
+        <v>1408</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -8452,7 +8480,7 @@
         <v>36</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1401</v>
+        <v>1409</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>160</v>
@@ -8461,19 +8489,19 @@
         <v>188</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1402</v>
+        <v>1410</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>1403</v>
+        <v>1411</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1404</v>
+        <v>1412</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>1405</v>
+        <v>1413</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>1406</v>
+        <v>1414</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -8482,15 +8510,15 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>1408</v>
+        <v>1416</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>110</v>
@@ -8499,7 +8527,7 @@
         <v>36</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1409</v>
+        <v>1417</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>150</v>
@@ -8508,19 +8536,19 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>1410</v>
+        <v>1418</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>1411</v>
+        <v>1419</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>1412</v>
+        <v>1420</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>1413</v>
+        <v>1421</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>1414</v>
+        <v>1422</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>166</v>
@@ -8529,13 +8557,13 @@
         <v>4</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7" t="s">
-        <v>1415</v>
+        <v>1423</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>110</v>
@@ -8544,7 +8572,7 @@
         <v>36</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1416</v>
+        <v>1424</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>150</v>
@@ -8553,19 +8581,19 @@
         <v>151</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>1417</v>
+        <v>1425</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>1418</v>
+        <v>1426</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>1419</v>
+        <v>1427</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>1420</v>
+        <v>1428</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>166</v>
@@ -8574,13 +8602,13 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="7" t="s">
-        <v>1421</v>
+        <v>1429</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>110</v>
@@ -8589,7 +8617,7 @@
         <v>36</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1416</v>
+        <v>1424</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>160</v>
@@ -8598,19 +8626,19 @@
         <v>151</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>1422</v>
+        <v>1430</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>1423</v>
+        <v>1431</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>1424</v>
+        <v>1432</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>1425</v>
+        <v>1433</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>1426</v>
+        <v>1434</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>166</v>
@@ -8619,13 +8647,13 @@
         <v>4</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="7" t="s">
-        <v>1427</v>
+        <v>1435</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>110</v>
@@ -8634,7 +8662,7 @@
         <v>36</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1428</v>
+        <v>1436</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>150</v>
@@ -8643,19 +8671,19 @@
         <v>188</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1429</v>
+        <v>1437</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>1430</v>
+        <v>1438</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>1431</v>
+        <v>1439</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>1432</v>
+        <v>1440</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>1433</v>
+        <v>1441</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>166</v>
@@ -8664,22 +8692,22 @@
         <v>4</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="7" t="s">
-        <v>1434</v>
+        <v>1442</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1435</v>
+        <v>1443</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1436</v>
+        <v>1444</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>160</v>
@@ -8688,19 +8716,19 @@
         <v>151</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>1437</v>
+        <v>1445</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>1438</v>
+        <v>1446</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>1439</v>
+        <v>1447</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>1440</v>
+        <v>1448</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>1441</v>
+        <v>1449</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>166</v>
@@ -8709,10 +8737,10 @@
         <v>4</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>1442</v>
+        <v>1450</v>
       </c>
     </row>
   </sheetData>
@@ -8806,7 +8834,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1443</v>
+        <v>1451</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>107</v>
@@ -8815,7 +8843,7 @@
         <v>40</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1444</v>
+        <v>1452</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -8824,19 +8852,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1445</v>
+        <v>1453</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1446</v>
+        <v>1454</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1447</v>
+        <v>1455</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1448</v>
+        <v>1456</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -8845,13 +8873,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1451</v>
+        <v>1459</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -8860,7 +8888,7 @@
         <v>40</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1452</v>
+        <v>1460</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -8869,19 +8897,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1453</v>
+        <v>1461</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1454</v>
+        <v>1462</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1455</v>
+        <v>1463</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1456</v>
+        <v>1464</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1457</v>
+        <v>1465</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -8890,13 +8918,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -8905,7 +8933,7 @@
         <v>40</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1459</v>
+        <v>1467</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>150</v>
@@ -8914,19 +8942,19 @@
         <v>151</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1460</v>
+        <v>1468</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1461</v>
+        <v>1469</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1462</v>
+        <v>1470</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1463</v>
+        <v>1471</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1464</v>
+        <v>1472</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -8935,13 +8963,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1465</v>
+        <v>1473</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>127</v>
@@ -8950,28 +8978,28 @@
         <v>40</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1466</v>
+        <v>1474</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1467</v>
+        <v>1475</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1468</v>
+        <v>1476</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1469</v>
+        <v>1477</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1470</v>
+        <v>1478</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1471</v>
+        <v>1479</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -8980,13 +9008,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1472</v>
+        <v>1480</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>127</v>
@@ -8995,28 +9023,28 @@
         <v>40</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1466</v>
+        <v>1474</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1473</v>
+        <v>1481</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1474</v>
+        <v>1482</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1475</v>
+        <v>1483</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1476</v>
+        <v>1484</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1477</v>
+        <v>1485</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -9025,13 +9053,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1478</v>
+        <v>1486</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>127</v>
@@ -9040,28 +9068,28 @@
         <v>40</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1466</v>
+        <v>1474</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1479</v>
+        <v>1487</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1480</v>
+        <v>1488</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1481</v>
+        <v>1489</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1482</v>
+        <v>1490</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -9070,13 +9098,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1483</v>
+        <v>1491</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>107</v>
@@ -9085,7 +9113,7 @@
         <v>40</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1484</v>
+        <v>1492</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -9094,19 +9122,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1485</v>
+        <v>1493</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1486</v>
+        <v>1494</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1487</v>
+        <v>1495</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1488</v>
+        <v>1496</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1489</v>
+        <v>1497</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -9115,13 +9143,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1490</v>
+        <v>1498</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -9130,7 +9158,7 @@
         <v>40</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1491</v>
+        <v>1499</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -9139,19 +9167,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1492</v>
+        <v>1500</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1493</v>
+        <v>1501</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1494</v>
+        <v>1502</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1495</v>
+        <v>1503</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1496</v>
+        <v>1504</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -9160,13 +9188,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1497</v>
+        <v>1505</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>104</v>
@@ -9175,28 +9203,28 @@
         <v>40</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1498</v>
+        <v>1506</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1499</v>
+        <v>1507</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1500</v>
+        <v>1508</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1501</v>
+        <v>1509</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1502</v>
+        <v>1510</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1503</v>
+        <v>1511</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -9205,13 +9233,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1505</v>
+        <v>1513</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>127</v>
@@ -9220,7 +9248,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1506</v>
+        <v>1514</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -9229,19 +9257,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1507</v>
+        <v>1515</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1508</v>
+        <v>1516</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1509</v>
+        <v>1517</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1510</v>
+        <v>1518</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1511</v>
+        <v>1519</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -9250,13 +9278,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1512</v>
+        <v>1520</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>127</v>
@@ -9265,7 +9293,7 @@
         <v>40</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1513</v>
+        <v>1521</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -9274,19 +9302,19 @@
         <v>254</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1514</v>
+        <v>1522</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1515</v>
+        <v>1523</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1516</v>
+        <v>1524</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1517</v>
+        <v>1525</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -9295,13 +9323,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1518</v>
+        <v>1526</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1519</v>
+        <v>1527</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>127</v>
@@ -9310,7 +9338,7 @@
         <v>40</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1520</v>
+        <v>1528</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -9319,19 +9347,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1521</v>
+        <v>1529</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1522</v>
+        <v>1530</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1523</v>
+        <v>1531</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1524</v>
+        <v>1532</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -9340,13 +9368,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1518</v>
+        <v>1526</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1525</v>
+        <v>1533</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>127</v>
@@ -9355,7 +9383,7 @@
         <v>40</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1526</v>
+        <v>1534</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -9364,19 +9392,19 @@
         <v>188</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1527</v>
+        <v>1535</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1528</v>
+        <v>1536</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1529</v>
+        <v>1537</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1530</v>
+        <v>1538</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -9385,13 +9413,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1531</v>
+        <v>1539</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1532</v>
+        <v>1540</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -9400,7 +9428,7 @@
         <v>40</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1533</v>
+        <v>1541</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>150</v>
@@ -9409,19 +9437,19 @@
         <v>254</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1534</v>
+        <v>1542</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1535</v>
+        <v>1543</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1536</v>
+        <v>1544</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1537</v>
+        <v>1545</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1538</v>
+        <v>1546</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>6</v>
@@ -9433,12 +9461,12 @@
         <v>157</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>1539</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>1540</v>
+        <v>1548</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -9447,28 +9475,28 @@
         <v>40</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1541</v>
+        <v>1549</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1542</v>
+        <v>1550</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1543</v>
+        <v>1551</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>1544</v>
+        <v>1552</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1545</v>
+        <v>1553</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>1546</v>
+        <v>1554</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>1547</v>
+        <v>1555</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>6</v>
@@ -9480,7 +9508,7 @@
         <v>157</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>1548</v>
+        <v>1556</v>
       </c>
     </row>
   </sheetData>
@@ -9574,7 +9602,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1549</v>
+        <v>1557</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -9583,28 +9611,28 @@
         <v>44</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1550</v>
+        <v>1558</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1551</v>
+        <v>1559</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1552</v>
+        <v>1560</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1553</v>
+        <v>1561</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1555</v>
+        <v>1563</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -9613,13 +9641,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1556</v>
+        <v>1564</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1557</v>
+        <v>1565</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -9628,28 +9656,28 @@
         <v>44</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1550</v>
+        <v>1558</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1558</v>
+        <v>1566</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1559</v>
+        <v>1567</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1560</v>
+        <v>1568</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1561</v>
+        <v>1569</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1562</v>
+        <v>1570</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -9658,13 +9686,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1556</v>
+        <v>1564</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1563</v>
+        <v>1571</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -9673,7 +9701,7 @@
         <v>44</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1564</v>
+        <v>1572</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -9682,19 +9710,19 @@
         <v>151</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1565</v>
+        <v>1573</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1566</v>
+        <v>1574</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1567</v>
+        <v>1575</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1568</v>
+        <v>1576</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1569</v>
+        <v>1577</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -9703,13 +9731,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1570</v>
+        <v>1578</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1571</v>
+        <v>1579</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -9718,7 +9746,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1572</v>
+        <v>1580</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -9727,19 +9755,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1573</v>
+        <v>1581</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1574</v>
+        <v>1582</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1575</v>
+        <v>1583</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1576</v>
+        <v>1584</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1577</v>
+        <v>1585</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -9748,13 +9776,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1578</v>
+        <v>1586</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1579</v>
+        <v>1587</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>170</v>
@@ -9763,7 +9791,7 @@
         <v>44</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1572</v>
+        <v>1580</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -9772,19 +9800,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1580</v>
+        <v>1588</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>190</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1581</v>
+        <v>1589</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1582</v>
+        <v>1590</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -9793,13 +9821,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1556</v>
+        <v>1564</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1583</v>
+        <v>1591</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -9808,28 +9836,28 @@
         <v>44</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1585</v>
+        <v>1593</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1586</v>
+        <v>1594</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1587</v>
+        <v>1595</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1588</v>
+        <v>1596</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1589</v>
+        <v>1597</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -9838,13 +9866,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1590</v>
+        <v>1598</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1591</v>
+        <v>1599</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -9853,28 +9881,28 @@
         <v>44</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1542</v>
+        <v>1550</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1592</v>
+        <v>1600</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1593</v>
+        <v>1601</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1594</v>
+        <v>1602</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1595</v>
+        <v>1603</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1596</v>
+        <v>1604</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -9883,13 +9911,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1590</v>
+        <v>1598</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1597</v>
+        <v>1605</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -9898,7 +9926,7 @@
         <v>44</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1598</v>
+        <v>1606</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -9907,19 +9935,19 @@
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1599</v>
+        <v>1607</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1600</v>
+        <v>1608</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1601</v>
+        <v>1609</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1602</v>
+        <v>1610</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1603</v>
+        <v>1611</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -9928,13 +9956,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1590</v>
+        <v>1598</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1604</v>
+        <v>1612</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>170</v>
@@ -9943,7 +9971,7 @@
         <v>44</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1598</v>
+        <v>1606</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -9952,19 +9980,19 @@
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1605</v>
+        <v>1613</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>190</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1606</v>
+        <v>1614</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1607</v>
+        <v>1615</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -9973,13 +10001,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1590</v>
+        <v>1598</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1608</v>
+        <v>1616</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -9988,7 +10016,7 @@
         <v>44</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1609</v>
+        <v>1617</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>150</v>
@@ -9997,19 +10025,19 @@
         <v>188</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1610</v>
+        <v>1618</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1611</v>
+        <v>1619</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1612</v>
+        <v>1620</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1613</v>
+        <v>1621</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>6</v>
@@ -10021,12 +10049,12 @@
         <v>157</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>1614</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1615</v>
+        <v>1623</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -10035,7 +10063,7 @@
         <v>44</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1616</v>
+        <v>1624</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -10044,19 +10072,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1617</v>
+        <v>1625</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1618</v>
+        <v>1626</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1619</v>
+        <v>1627</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1620</v>
+        <v>1628</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1621</v>
+        <v>1629</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -10065,13 +10093,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1590</v>
+        <v>1598</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1622</v>
+        <v>1630</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -10080,7 +10108,7 @@
         <v>44</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1623</v>
+        <v>1631</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>150</v>
@@ -10089,19 +10117,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1624</v>
+        <v>1632</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1625</v>
+        <v>1633</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1626</v>
+        <v>1634</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1627</v>
+        <v>1635</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1628</v>
+        <v>1636</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -10110,13 +10138,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1590</v>
+        <v>1598</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1629</v>
+        <v>1637</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>127</v>
@@ -10125,28 +10153,28 @@
         <v>44</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1630</v>
+        <v>1638</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1631</v>
+        <v>1639</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1632</v>
+        <v>1640</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1633</v>
+        <v>1641</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1634</v>
+        <v>1642</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1635</v>
+        <v>1643</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -10155,13 +10183,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1636</v>
+        <v>1644</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1637</v>
+        <v>1645</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>127</v>
@@ -10170,7 +10198,7 @@
         <v>44</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1638</v>
+        <v>1646</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -10179,19 +10207,19 @@
         <v>254</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1639</v>
+        <v>1647</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1640</v>
+        <v>1648</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1641</v>
+        <v>1649</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1642</v>
+        <v>1650</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1643</v>
+        <v>1651</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -10200,7 +10228,7 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>1636</v>
+        <v>1644</v>
       </c>
       <c r="O15" s="6"/>
     </row>
@@ -10295,7 +10323,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1644</v>
+        <v>1652</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -10304,7 +10332,7 @@
         <v>48</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1645</v>
+        <v>1653</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -10313,19 +10341,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1646</v>
+        <v>1654</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1647</v>
+        <v>1655</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1648</v>
+        <v>1656</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1649</v>
+        <v>1657</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1650</v>
+        <v>1658</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -10334,13 +10362,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1651</v>
+        <v>1659</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1652</v>
+        <v>1660</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -10349,7 +10377,7 @@
         <v>48</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1653</v>
+        <v>1661</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -10358,19 +10386,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1654</v>
+        <v>1662</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1655</v>
+        <v>1663</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1656</v>
+        <v>1664</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1657</v>
+        <v>1665</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1658</v>
+        <v>1666</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -10379,13 +10407,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1651</v>
+        <v>1659</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1659</v>
+        <v>1667</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -10394,7 +10422,7 @@
         <v>48</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1660</v>
+        <v>1668</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -10403,19 +10431,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1661</v>
+        <v>1669</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1662</v>
+        <v>1670</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1664</v>
+        <v>1672</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1665</v>
+        <v>1673</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -10424,13 +10452,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1651</v>
+        <v>1659</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1666</v>
+        <v>1674</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -10439,7 +10467,7 @@
         <v>48</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1667</v>
+        <v>1675</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -10448,19 +10476,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1668</v>
+        <v>1676</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1669</v>
+        <v>1677</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1670</v>
+        <v>1678</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1671</v>
+        <v>1679</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1672</v>
+        <v>1680</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -10469,13 +10497,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1651</v>
+        <v>1659</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1673</v>
+        <v>1681</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>110</v>
@@ -10484,7 +10512,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1674</v>
+        <v>1682</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>150</v>
@@ -10493,19 +10521,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1675</v>
+        <v>1683</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1676</v>
+        <v>1684</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1677</v>
+        <v>1685</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1678</v>
+        <v>1686</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1679</v>
+        <v>1687</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>6</v>
@@ -10517,12 +10545,12 @@
         <v>157</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>1680</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1681</v>
+        <v>1689</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -10531,7 +10559,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1682</v>
+        <v>1690</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -10540,19 +10568,19 @@
         <v>188</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1683</v>
+        <v>1691</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1684</v>
+        <v>1692</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1685</v>
+        <v>1693</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1686</v>
+        <v>1694</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1687</v>
+        <v>1695</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>6</v>
@@ -10564,12 +10592,12 @@
         <v>157</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>1688</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1689</v>
+        <v>1697</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -10578,7 +10606,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1690</v>
+        <v>1698</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -10587,19 +10615,19 @@
         <v>151</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1691</v>
+        <v>1699</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1692</v>
+        <v>1700</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1693</v>
+        <v>1701</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1671</v>
+        <v>1679</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1694</v>
+        <v>1702</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -10608,13 +10636,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1651</v>
+        <v>1659</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1695</v>
+        <v>1703</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -10623,7 +10651,7 @@
         <v>48</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1696</v>
+        <v>1704</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -10632,19 +10660,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1697</v>
+        <v>1705</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1698</v>
+        <v>1706</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1699</v>
+        <v>1707</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1671</v>
+        <v>1679</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1700</v>
+        <v>1708</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -10653,13 +10681,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1651</v>
+        <v>1659</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1701</v>
+        <v>1709</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -10668,7 +10696,7 @@
         <v>48</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1702</v>
+        <v>1710</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -10677,19 +10705,19 @@
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1703</v>
+        <v>1711</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1704</v>
+        <v>1712</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1705</v>
+        <v>1713</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1671</v>
+        <v>1679</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1706</v>
+        <v>1714</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -10698,13 +10726,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1651</v>
+        <v>1659</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1707</v>
+        <v>1715</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -10713,7 +10741,7 @@
         <v>48</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1708</v>
+        <v>1716</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -10722,19 +10750,19 @@
         <v>188</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1709</v>
+        <v>1717</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1710</v>
+        <v>1718</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1711</v>
+        <v>1719</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1671</v>
+        <v>1679</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1712</v>
+        <v>1720</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -10743,13 +10771,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1651</v>
+        <v>1659</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1713</v>
+        <v>1721</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -10758,7 +10786,7 @@
         <v>48</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1714</v>
+        <v>1722</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>150</v>
@@ -10767,19 +10795,19 @@
         <v>188</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1715</v>
+        <v>1723</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1716</v>
+        <v>1724</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1717</v>
+        <v>1725</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1718</v>
+        <v>1726</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1719</v>
+        <v>1727</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -10788,10 +10816,10 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1651</v>
+        <v>1659</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>1720</v>
+        <v>1728</v>
       </c>
     </row>
   </sheetData>
@@ -12456,7 +12484,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="true" style="0"/>
@@ -13787,8 +13815,55 @@
       </c>
       <c r="O29" s="6"/>
     </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>516</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O29"/>
+  <autoFilter ref="A1:O30"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
@@ -13878,7 +13953,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>104</v>
@@ -13887,7 +13962,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>150</v>
@@ -13896,19 +13971,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -13917,13 +13992,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>104</v>
@@ -13932,7 +14007,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>150</v>
@@ -13941,19 +14016,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -13962,13 +14037,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>104</v>
@@ -13977,7 +14052,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>150</v>
@@ -13986,19 +14061,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -14007,13 +14082,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>104</v>
@@ -14022,7 +14097,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>150</v>
@@ -14031,19 +14106,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -14052,13 +14127,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>104</v>
@@ -14067,7 +14142,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>150</v>
@@ -14076,19 +14151,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -14097,13 +14172,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>107</v>
@@ -14112,7 +14187,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>150</v>
@@ -14121,19 +14196,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -14142,13 +14217,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>107</v>
@@ -14157,7 +14232,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>150</v>
@@ -14166,19 +14241,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -14187,13 +14262,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -14202,28 +14277,28 @@
         <v>16</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -14232,13 +14307,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>170</v>
@@ -14247,7 +14322,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -14256,19 +14331,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>190</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -14277,7 +14352,7 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="O10" s="6"/>
     </row>
@@ -14372,7 +14447,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>107</v>
@@ -14381,7 +14456,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>150</v>
@@ -14390,19 +14465,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -14411,13 +14486,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>107</v>
@@ -14426,7 +14501,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -14435,19 +14510,19 @@
         <v>188</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -14456,13 +14531,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>107</v>
@@ -14471,7 +14546,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -14480,34 +14555,34 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>590</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>591</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>593</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>582</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>107</v>
@@ -14516,7 +14591,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>150</v>
@@ -14525,19 +14600,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -14546,13 +14621,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>107</v>
@@ -14561,7 +14636,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>150</v>
@@ -14570,19 +14645,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -14591,13 +14666,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>107</v>
@@ -14606,7 +14681,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -14615,19 +14690,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -14636,13 +14711,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>107</v>
@@ -14651,7 +14726,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -14660,19 +14735,19 @@
         <v>151</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -14681,13 +14756,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>107</v>
@@ -14696,7 +14771,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -14705,19 +14780,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -14726,13 +14801,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>107</v>
@@ -14750,19 +14825,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -14771,13 +14846,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>107</v>
@@ -14786,7 +14861,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -14795,19 +14870,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -14816,13 +14891,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -14831,7 +14906,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -14840,19 +14915,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -14861,13 +14936,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -14876,7 +14951,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>150</v>
@@ -14885,19 +14960,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -14906,13 +14981,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>110</v>
@@ -14921,7 +14996,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>150</v>
@@ -14930,19 +15005,19 @@
         <v>151</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -14951,13 +15026,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -14966,7 +15041,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -14975,19 +15050,19 @@
         <v>151</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -14996,13 +15071,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -15011,7 +15086,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>150</v>
@@ -15020,19 +15095,19 @@
         <v>151</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -15041,13 +15116,13 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>110</v>
@@ -15056,7 +15131,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>150</v>
@@ -15065,19 +15140,19 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>166</v>
@@ -15086,10 +15161,10 @@
         <v>4</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -15183,7 +15258,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -15192,7 +15267,7 @@
         <v>24</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>150</v>
@@ -15201,19 +15276,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -15222,13 +15297,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -15237,7 +15312,7 @@
         <v>24</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -15246,19 +15321,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -15267,13 +15342,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -15282,7 +15357,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -15291,34 +15366,34 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>702</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>703</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>704</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>705</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>706</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>694</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>107</v>
@@ -15327,7 +15402,7 @@
         <v>24</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -15336,19 +15411,19 @@
         <v>188</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -15357,13 +15432,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>107</v>
@@ -15372,7 +15447,7 @@
         <v>24</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -15381,19 +15456,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -15402,13 +15477,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>107</v>
@@ -15417,7 +15492,7 @@
         <v>24</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -15426,19 +15501,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -15447,13 +15522,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -15462,28 +15537,28 @@
         <v>24</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -15492,13 +15567,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>127</v>
@@ -15507,28 +15582,28 @@
         <v>24</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -15537,13 +15612,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -15552,7 +15627,7 @@
         <v>24</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -15561,19 +15636,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -15582,13 +15657,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -15597,7 +15672,7 @@
         <v>24</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -15606,19 +15681,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -15627,13 +15702,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -15642,7 +15717,7 @@
         <v>24</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -15651,19 +15726,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -15672,13 +15747,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -15687,7 +15762,7 @@
         <v>24</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -15696,19 +15771,19 @@
         <v>151</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -15717,13 +15792,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>110</v>
@@ -15732,7 +15807,7 @@
         <v>24</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -15741,19 +15816,19 @@
         <v>188</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -15762,13 +15837,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -15777,7 +15852,7 @@
         <v>24</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>150</v>
@@ -15786,19 +15861,19 @@
         <v>151</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -15807,13 +15882,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -15822,7 +15897,7 @@
         <v>24</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>160</v>
@@ -15831,19 +15906,19 @@
         <v>151</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -15852,13 +15927,13 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>110</v>
@@ -15867,7 +15942,7 @@
         <v>24</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>160</v>
@@ -15876,19 +15951,19 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>166</v>
@@ -15897,13 +15972,13 @@
         <v>4</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>110</v>
@@ -15912,28 +15987,28 @@
         <v>24</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>166</v>
@@ -15942,15 +16017,15 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="7" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>110</v>
@@ -15959,7 +16034,7 @@
         <v>24</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>150</v>
@@ -15968,19 +16043,19 @@
         <v>151</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>166</v>
@@ -15989,13 +16064,13 @@
         <v>4</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="7" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>110</v>
@@ -16004,7 +16079,7 @@
         <v>24</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>160</v>
@@ -16013,19 +16088,19 @@
         <v>151</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>166</v>
@@ -16034,13 +16109,13 @@
         <v>4</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="7" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>110</v>
@@ -16049,7 +16124,7 @@
         <v>24</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>160</v>
@@ -16058,19 +16133,19 @@
         <v>151</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>166</v>
@@ -16079,13 +16154,13 @@
         <v>4</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="7" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>110</v>
@@ -16094,7 +16169,7 @@
         <v>24</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>160</v>
@@ -16103,19 +16178,19 @@
         <v>188</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>166</v>
@@ -16124,13 +16199,13 @@
         <v>4</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="7" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>107</v>
@@ -16139,7 +16214,7 @@
         <v>24</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>160</v>
@@ -16148,19 +16223,19 @@
         <v>151</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>166</v>
@@ -16169,13 +16244,13 @@
         <v>4</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="7" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>107</v>
@@ -16184,7 +16259,7 @@
         <v>24</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>160</v>
@@ -16193,19 +16268,19 @@
         <v>151</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>166</v>
@@ -16214,13 +16289,13 @@
         <v>4</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="7" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>110</v>
@@ -16229,7 +16304,7 @@
         <v>24</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>160</v>
@@ -16238,19 +16313,19 @@
         <v>151</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>166</v>
@@ -16259,13 +16334,13 @@
         <v>4</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="7" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>110</v>
@@ -16274,7 +16349,7 @@
         <v>24</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>160</v>
@@ -16283,19 +16358,19 @@
         <v>188</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>166</v>
@@ -16304,13 +16379,13 @@
         <v>4</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="7" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>107</v>
@@ -16319,7 +16394,7 @@
         <v>24</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>160</v>
@@ -16328,19 +16403,19 @@
         <v>188</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>166</v>
@@ -16349,13 +16424,13 @@
         <v>4</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="7" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>104</v>
@@ -16364,7 +16439,7 @@
         <v>24</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>160</v>
@@ -16373,19 +16448,19 @@
         <v>188</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>166</v>
@@ -16394,13 +16469,13 @@
         <v>4</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="O28" s="6"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="7" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>110</v>
@@ -16409,7 +16484,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>150</v>
@@ -16418,19 +16493,19 @@
         <v>151</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>166</v>
@@ -16439,13 +16514,13 @@
         <v>4</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="O29" s="6"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="7" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>104</v>
@@ -16454,7 +16529,7 @@
         <v>24</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>150</v>
@@ -16463,19 +16538,19 @@
         <v>151</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>166</v>
@@ -16484,13 +16559,13 @@
         <v>4</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="O30" s="6"/>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="7" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>107</v>
@@ -16499,7 +16574,7 @@
         <v>24</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>160</v>
@@ -16508,19 +16583,19 @@
         <v>151</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>166</v>
@@ -16529,13 +16604,13 @@
         <v>4</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="O31" s="6"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="7" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>104</v>
@@ -16544,7 +16619,7 @@
         <v>24</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>160</v>
@@ -16553,36 +16628,36 @@
         <v>188</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>906</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="H32" s="6" t="s">
-        <v>896</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>897</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>898</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>899</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M32" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="6" t="s">
-        <v>887</v>
-      </c>
       <c r="O32" s="6" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="7" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>107</v>
@@ -16591,7 +16666,7 @@
         <v>24</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>160</v>
@@ -16600,19 +16675,19 @@
         <v>188</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="L33" s="6" t="s">
         <v>166</v>
@@ -16621,13 +16696,13 @@
         <v>4</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="O33" s="6"/>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="7" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>104</v>
@@ -16636,7 +16711,7 @@
         <v>24</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>150</v>
@@ -16645,19 +16720,19 @@
         <v>151</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>166</v>
@@ -16666,15 +16741,15 @@
         <v>4</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="7" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>107</v>
@@ -16683,7 +16758,7 @@
         <v>24</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>160</v>
@@ -16692,19 +16767,19 @@
         <v>151</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="L35" s="6" t="s">
         <v>166</v>
@@ -16713,13 +16788,13 @@
         <v>4</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="O35" s="6"/>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="7" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>104</v>
@@ -16728,7 +16803,7 @@
         <v>24</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>160</v>
@@ -16737,19 +16812,19 @@
         <v>188</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>166</v>
@@ -16758,13 +16833,13 @@
         <v>4</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="O36" s="6"/>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="7" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>110</v>
@@ -16773,7 +16848,7 @@
         <v>24</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>150</v>
@@ -16782,19 +16857,19 @@
         <v>151</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="L37" s="6" t="s">
         <v>166</v>
@@ -16803,15 +16878,15 @@
         <v>4</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="7" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>110</v>
@@ -16820,7 +16895,7 @@
         <v>24</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -16829,19 +16904,19 @@
         <v>151</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="L38" s="6" t="s">
         <v>166</v>
@@ -16850,13 +16925,13 @@
         <v>4</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="7" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>110</v>
@@ -16865,28 +16940,28 @@
         <v>24</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="L39" s="6" t="s">
         <v>166</v>
@@ -16895,13 +16970,13 @@
         <v>4</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="O39" s="6"/>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" s="7" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>110</v>
@@ -16910,28 +16985,28 @@
         <v>24</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="L40" s="6" t="s">
         <v>166</v>
@@ -16940,13 +17015,13 @@
         <v>4</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="O40" s="6"/>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="7" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>110</v>
@@ -16955,7 +17030,7 @@
         <v>24</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>150</v>
@@ -16964,19 +17039,19 @@
         <v>151</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="L41" s="6" t="s">
         <v>166</v>
@@ -16985,15 +17060,15 @@
         <v>4</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="7" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>110</v>
@@ -17002,7 +17077,7 @@
         <v>24</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -17011,19 +17086,19 @@
         <v>151</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="L42" s="6" t="s">
         <v>166</v>
@@ -17032,13 +17107,13 @@
         <v>4</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="O42" s="6"/>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="7" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>110</v>
@@ -17047,7 +17122,7 @@
         <v>24</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>150</v>
@@ -17056,19 +17131,19 @@
         <v>151</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="L43" s="6" t="s">
         <v>166</v>
@@ -17077,22 +17152,22 @@
         <v>4</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="O43" s="6"/>
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="7" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -17101,19 +17176,19 @@
         <v>151</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="L44" s="6" t="s">
         <v>166</v>
@@ -17122,24 +17197,24 @@
         <v>4</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
     </row>
     <row r="45" spans="1:15">
       <c r="A45" s="7" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>160</v>
@@ -17148,19 +17223,19 @@
         <v>151</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="L45" s="6" t="s">
         <v>166</v>
@@ -17169,24 +17244,24 @@
         <v>4</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="7" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>160</v>
@@ -17195,19 +17270,19 @@
         <v>188</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="L46" s="6" t="s">
         <v>166</v>
@@ -17216,24 +17291,24 @@
         <v>4</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="7" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>160</v>
@@ -17242,19 +17317,19 @@
         <v>151</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="L47" s="6" t="s">
         <v>166</v>
@@ -17263,24 +17338,24 @@
         <v>4</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="7" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>150</v>
@@ -17289,19 +17364,19 @@
         <v>254</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="L48" s="6" t="s">
         <v>166</v>
@@ -17310,24 +17385,24 @@
         <v>4</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" s="7" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>160</v>
@@ -17336,19 +17411,19 @@
         <v>151</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="L49" s="6" t="s">
         <v>166</v>
@@ -17357,15 +17432,15 @@
         <v>4</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="7" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>110</v>
@@ -17374,7 +17449,7 @@
         <v>24</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>160</v>
@@ -17383,34 +17458,34 @@
         <v>151</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="K50" s="6" t="s">
+        <v>1033</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M50" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N50" s="6" t="s">
         <v>1025</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M50" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N50" s="6" t="s">
-        <v>1017</v>
       </c>
       <c r="O50" s="6"/>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="7" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>110</v>
@@ -17419,7 +17494,7 @@
         <v>24</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>160</v>
@@ -17428,19 +17503,19 @@
         <v>151</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="L51" s="6" t="s">
         <v>166</v>
@@ -17449,7 +17524,7 @@
         <v>4</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="O51" s="6"/>
     </row>
@@ -17544,7 +17619,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -17553,7 +17628,7 @@
         <v>28</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -17562,19 +17637,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -17583,13 +17658,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -17598,28 +17673,28 @@
         <v>28</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -17628,13 +17703,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -17643,7 +17718,7 @@
         <v>28</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>150</v>
@@ -17652,19 +17727,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -17673,13 +17748,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -17688,7 +17763,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -17697,19 +17772,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -17718,13 +17793,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>110</v>
@@ -17733,7 +17808,7 @@
         <v>28</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -17742,19 +17817,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -17763,13 +17838,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -17778,7 +17853,7 @@
         <v>28</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -17787,19 +17862,19 @@
         <v>188</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -17808,13 +17883,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -17823,7 +17898,7 @@
         <v>28</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -17832,19 +17907,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>6</v>
@@ -17856,12 +17931,12 @@
         <v>157</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -17870,7 +17945,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>150</v>
@@ -17879,19 +17954,19 @@
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>6</v>
@@ -17903,12 +17978,12 @@
         <v>157</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -17917,7 +17992,7 @@
         <v>28</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -17926,19 +18001,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>6</v>
@@ -17950,12 +18025,12 @@
         <v>157</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>104</v>
@@ -17964,7 +18039,7 @@
         <v>28</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>150</v>
@@ -17973,19 +18048,19 @@
         <v>254</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>6</v>

--- a/docs/test-cases/test-cases.xlsx
+++ b/docs/test-cases/test-cases.xlsx
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'01-AUTH'!$A$1:$O$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'02-ADMIN'!$A$1:$O$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'02-ADMIN'!$A$1:$O$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'03-STAT'!$A$1:$O$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'04-LECT'!$A$1:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'05-STU'!$A$1:$O$51</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1737">
   <si>
     <t>Nhóm</t>
   </si>
@@ -279,7 +279,7 @@
     <t>TC-ADMIN — Nhóm 02 — Quản trị người dùng, môn học &amp; lớp học phần</t>
   </si>
   <si>
-    <t>php artisan test tests/Feature/SubjectTest.php tests/Feature/AdminClassManagementTest.php tests/Feature/ClassMembershipStatusTest.php tests/Feature/ViewSmokeTest.php tests/Feature/AdminSoftDeleteTest.php tests/Feature/StudentQuickActionsTest.php</t>
+    <t>php artisan test tests/Feature/SubjectTest.php tests/Feature/AdminClassManagementTest.php tests/Feature/ClassMembershipStatusTest.php tests/Feature/ViewSmokeTest.php tests/Feature/AdminSoftDeleteTest.php tests/Feature/StudentQuickActionsTest.php tests/Feature/ClassCodeFiveCharsTest.php</t>
   </si>
   <si>
     <t>TC-STAT — Nhóm 03 — Thống kê &amp; thông báo</t>
@@ -1711,6 +1711,33 @@
   </si>
   <si>
     <t>Chốt 5a-B (chỉ Admin, GV 403), 5b (reset về "password" + buộc đổi ở lần đăng nhập sau), 5c (đơn lẻ từng sinh viên, không bulk).</t>
+  </si>
+  <si>
+    <t>TC-ADMIN-30</t>
+  </si>
+  <si>
+    <t>L07 — Mã lớp thống nhất ĐÚNG 5 ký tự cho cả Admin và Giảng viên; mã cũ dài/NULL đã được quy đổi</t>
+  </si>
+  <si>
+    <t>Đăng nhập admin (và giảng viên ở bước đối chiếu); DB đã chạy migration quy đổi mã lớp</t>
+  </si>
+  <si>
+    <t>Admin tạo liên tiếp 5 lớp học phần
+Giảng viên tạo 1 lớp học phần
+Đọc mã lớp của từng lớp vừa tạo và đối chiếu quy tắc 5 ký tự
+Sinh viên thử tham gia bằng mã 4 ký tự rồi 6 ký tự (case âm)</t>
+  </si>
+  <si>
+    <t>POST /admin/classes · POST /lecturer/classes · POST /user/classes/join {class_code}</t>
+  </si>
+  <si>
+    <t>Mọi mã lớp tự sinh khớp /^[A-Z0-9]{5}$/ và không trùng nhau (kể cả giữa admin và giảng viên); mã 4/6 ký tự bị từ chối kèm thông báo "Mã lớp gồm đúng 5 ký tự. Vui lòng kiểm tra lại mã được giảng viên cung cấp!"; mã 5 ký tự không tồn tại báo "Không tìm thấy lớp học với mã này!"</t>
+  </si>
+  <si>
+    <t>tests/Feature/ClassCodeFiveCharsTest.php</t>
+  </si>
+  <si>
+    <t>Generator dùng chung `generateUniqueClassCode()` (bỏ ký tự dễ nhầm I,O,0,1); generator cũ `generateClassCode()` kiểu {subject_code}-NN đã bị xóa; seeder dữ liệu mẫu + Fixtures của test cũng tuân quy tắc 5 ký tự.</t>
   </si>
   <si>
     <t>TC-STAT-01</t>
@@ -6172,10 +6199,10 @@
         <v>14</v>
       </c>
       <c r="D3" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
@@ -6428,10 +6455,10 @@
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="4">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E13" s="4">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F13" s="4">
         <v>5</v>
@@ -6531,7 +6558,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>127</v>
@@ -6540,7 +6567,7 @@
         <v>32</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -6549,19 +6576,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -6570,13 +6597,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>127</v>
@@ -6585,7 +6612,7 @@
         <v>32</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -6594,19 +6621,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -6615,13 +6642,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>127</v>
@@ -6630,7 +6657,7 @@
         <v>32</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -6639,19 +6666,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -6660,13 +6687,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>127</v>
@@ -6675,7 +6702,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -6684,19 +6711,19 @@
         <v>188</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -6705,13 +6732,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>127</v>
@@ -6720,7 +6747,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -6729,19 +6756,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -6750,13 +6777,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>127</v>
@@ -6765,7 +6792,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -6774,19 +6801,19 @@
         <v>188</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -6795,13 +6822,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>127</v>
@@ -6810,7 +6837,7 @@
         <v>32</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -6819,19 +6846,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -6840,13 +6867,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>127</v>
@@ -6855,7 +6882,7 @@
         <v>32</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -6864,19 +6891,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -6885,15 +6912,15 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>127</v>
@@ -6902,7 +6929,7 @@
         <v>32</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -6911,19 +6938,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -6932,13 +6959,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -6947,7 +6974,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -6956,19 +6983,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -6977,13 +7004,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -6992,7 +7019,7 @@
         <v>32</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -7001,19 +7028,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -7022,13 +7049,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -7037,7 +7064,7 @@
         <v>32</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -7046,19 +7073,19 @@
         <v>151</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -7067,13 +7094,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>110</v>
@@ -7082,7 +7109,7 @@
         <v>32</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -7091,19 +7118,19 @@
         <v>151</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -7112,13 +7139,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -7127,7 +7154,7 @@
         <v>32</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -7136,19 +7163,19 @@
         <v>188</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -7157,13 +7184,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>104</v>
@@ -7172,7 +7199,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>160</v>
@@ -7181,19 +7208,19 @@
         <v>151</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -7202,13 +7229,13 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>104</v>
@@ -7217,7 +7244,7 @@
         <v>32</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>160</v>
@@ -7226,19 +7253,19 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>166</v>
@@ -7247,13 +7274,13 @@
         <v>4</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>104</v>
@@ -7262,7 +7289,7 @@
         <v>32</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>160</v>
@@ -7271,19 +7298,19 @@
         <v>151</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>166</v>
@@ -7292,13 +7319,13 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="7" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>104</v>
@@ -7307,7 +7334,7 @@
         <v>32</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>160</v>
@@ -7316,19 +7343,19 @@
         <v>188</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>166</v>
@@ -7337,13 +7364,13 @@
         <v>4</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="7" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>104</v>
@@ -7352,7 +7379,7 @@
         <v>32</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>160</v>
@@ -7361,19 +7388,19 @@
         <v>151</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>166</v>
@@ -7382,13 +7409,13 @@
         <v>4</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="7" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>104</v>
@@ -7397,7 +7424,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>160</v>
@@ -7406,19 +7433,19 @@
         <v>188</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>166</v>
@@ -7427,13 +7454,13 @@
         <v>4</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="7" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>110</v>
@@ -7442,7 +7469,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>160</v>
@@ -7451,19 +7478,19 @@
         <v>151</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>166</v>
@@ -7472,13 +7499,13 @@
         <v>4</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="7" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>104</v>
@@ -7487,7 +7514,7 @@
         <v>32</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>150</v>
@@ -7496,19 +7523,19 @@
         <v>188</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>166</v>
@@ -7517,13 +7544,13 @@
         <v>4</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="7" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>104</v>
@@ -7532,7 +7559,7 @@
         <v>32</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>150</v>
@@ -7541,19 +7568,19 @@
         <v>254</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>372</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>166</v>
@@ -7562,13 +7589,13 @@
         <v>4</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="7" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>104</v>
@@ -7577,7 +7604,7 @@
         <v>32</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>150</v>
@@ -7586,19 +7613,19 @@
         <v>188</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>166</v>
@@ -7607,13 +7634,13 @@
         <v>4</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="7" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>104</v>
@@ -7622,7 +7649,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>160</v>
@@ -7631,19 +7658,19 @@
         <v>188</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>372</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>166</v>
@@ -7652,13 +7679,13 @@
         <v>4</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="7" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>104</v>
@@ -7667,7 +7694,7 @@
         <v>32</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>150</v>
@@ -7676,19 +7703,19 @@
         <v>254</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>166</v>
@@ -7697,13 +7724,13 @@
         <v>4</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="7" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>110</v>
@@ -7712,7 +7739,7 @@
         <v>32</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>150</v>
@@ -7721,19 +7748,19 @@
         <v>151</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>6</v>
@@ -7742,10 +7769,10 @@
         <v>6</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
     </row>
   </sheetData>
@@ -7839,7 +7866,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -7848,7 +7875,7 @@
         <v>36</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -7857,19 +7884,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -7878,13 +7905,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -7893,7 +7920,7 @@
         <v>36</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -7902,19 +7929,19 @@
         <v>188</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -7923,13 +7950,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -7938,7 +7965,7 @@
         <v>36</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -7947,19 +7974,19 @@
         <v>151</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1329</v>
+        <v>1337</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -7968,13 +7995,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -7983,28 +8010,28 @@
         <v>36</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1333</v>
+        <v>1341</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1335</v>
+        <v>1343</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -8013,13 +8040,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>110</v>
@@ -8028,7 +8055,7 @@
         <v>36</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -8037,19 +8064,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1343</v>
+        <v>1351</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -8058,13 +8085,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -8073,7 +8100,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -8082,19 +8109,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1349</v>
+        <v>1357</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1350</v>
+        <v>1358</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1351</v>
+        <v>1359</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -8103,15 +8130,15 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1352</v>
+        <v>1360</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>1353</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1354</v>
+        <v>1362</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -8120,7 +8147,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1355</v>
+        <v>1363</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -8129,19 +8156,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1356</v>
+        <v>1364</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1357</v>
+        <v>1365</v>
       </c>
       <c r="I8" s="6" t="s">
+        <v>1366</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>1358</v>
       </c>
-      <c r="J8" s="6" t="s">
-        <v>1350</v>
-      </c>
       <c r="K8" s="6" t="s">
-        <v>1359</v>
+        <v>1367</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -8150,13 +8177,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1352</v>
+        <v>1360</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -8165,7 +8192,7 @@
         <v>36</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1361</v>
+        <v>1369</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -8174,19 +8201,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1365</v>
+        <v>1373</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1366</v>
+        <v>1374</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -8195,13 +8222,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1367</v>
+        <v>1375</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -8210,7 +8237,7 @@
         <v>36</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>150</v>
@@ -8219,19 +8246,19 @@
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1369</v>
+        <v>1377</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1370</v>
+        <v>1378</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1371</v>
+        <v>1379</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1372</v>
+        <v>1380</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -8240,13 +8267,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1373</v>
+        <v>1381</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>127</v>
@@ -8255,7 +8282,7 @@
         <v>36</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1374</v>
+        <v>1382</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -8264,19 +8291,19 @@
         <v>188</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1375</v>
+        <v>1383</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1377</v>
+        <v>1385</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1379</v>
+        <v>1387</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -8285,13 +8312,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1380</v>
+        <v>1388</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>127</v>
@@ -8300,28 +8327,28 @@
         <v>36</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1381</v>
+        <v>1389</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1382</v>
+        <v>1390</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1383</v>
+        <v>1391</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1386</v>
+        <v>1394</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -8330,13 +8357,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1388</v>
+        <v>1396</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>127</v>
@@ -8345,7 +8372,7 @@
         <v>36</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1389</v>
+        <v>1397</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -8354,19 +8381,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1390</v>
+        <v>1398</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1391</v>
+        <v>1399</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1393</v>
+        <v>1401</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -8375,13 +8402,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1394</v>
+        <v>1402</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>127</v>
@@ -8390,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1395</v>
+        <v>1403</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -8399,19 +8426,19 @@
         <v>151</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1396</v>
+        <v>1404</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1397</v>
+        <v>1405</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1398</v>
+        <v>1406</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1399</v>
+        <v>1407</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1400</v>
+        <v>1408</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -8420,13 +8447,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1401</v>
+        <v>1409</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>127</v>
@@ -8435,7 +8462,7 @@
         <v>36</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1402</v>
+        <v>1410</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -8444,19 +8471,19 @@
         <v>188</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1403</v>
+        <v>1411</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1404</v>
+        <v>1412</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1405</v>
+        <v>1413</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1406</v>
+        <v>1414</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -8465,13 +8492,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>1408</v>
+        <v>1416</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -8480,7 +8507,7 @@
         <v>36</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1409</v>
+        <v>1417</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>160</v>
@@ -8489,19 +8516,19 @@
         <v>188</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1410</v>
+        <v>1418</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>1411</v>
+        <v>1419</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1412</v>
+        <v>1420</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>1413</v>
+        <v>1421</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>1414</v>
+        <v>1422</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -8510,15 +8537,15 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>1415</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>1416</v>
+        <v>1424</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>110</v>
@@ -8527,7 +8554,7 @@
         <v>36</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1417</v>
+        <v>1425</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>150</v>
@@ -8536,19 +8563,19 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>1418</v>
+        <v>1426</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>1419</v>
+        <v>1427</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>1420</v>
+        <v>1428</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>1421</v>
+        <v>1429</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>1422</v>
+        <v>1430</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>166</v>
@@ -8557,13 +8584,13 @@
         <v>4</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7" t="s">
-        <v>1423</v>
+        <v>1431</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>110</v>
@@ -8572,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1424</v>
+        <v>1432</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>150</v>
@@ -8581,19 +8608,19 @@
         <v>151</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>1425</v>
+        <v>1433</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>1426</v>
+        <v>1434</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>1427</v>
+        <v>1435</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>1428</v>
+        <v>1436</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>166</v>
@@ -8602,13 +8629,13 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="7" t="s">
-        <v>1429</v>
+        <v>1437</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>110</v>
@@ -8617,7 +8644,7 @@
         <v>36</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1424</v>
+        <v>1432</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>160</v>
@@ -8626,19 +8653,19 @@
         <v>151</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>1430</v>
+        <v>1438</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>1431</v>
+        <v>1439</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>1432</v>
+        <v>1440</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>1433</v>
+        <v>1441</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>1434</v>
+        <v>1442</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>166</v>
@@ -8647,13 +8674,13 @@
         <v>4</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="7" t="s">
-        <v>1435</v>
+        <v>1443</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>110</v>
@@ -8662,7 +8689,7 @@
         <v>36</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1436</v>
+        <v>1444</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>150</v>
@@ -8671,19 +8698,19 @@
         <v>188</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1437</v>
+        <v>1445</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>1438</v>
+        <v>1446</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>1439</v>
+        <v>1447</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>1440</v>
+        <v>1448</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>1441</v>
+        <v>1449</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>166</v>
@@ -8692,22 +8719,22 @@
         <v>4</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="7" t="s">
-        <v>1442</v>
+        <v>1450</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1443</v>
+        <v>1451</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1444</v>
+        <v>1452</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>160</v>
@@ -8716,19 +8743,19 @@
         <v>151</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>1445</v>
+        <v>1453</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>1446</v>
+        <v>1454</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>1447</v>
+        <v>1455</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>1448</v>
+        <v>1456</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>166</v>
@@ -8737,10 +8764,10 @@
         <v>4</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
     </row>
   </sheetData>
@@ -8834,7 +8861,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1451</v>
+        <v>1459</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>107</v>
@@ -8843,7 +8870,7 @@
         <v>40</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1452</v>
+        <v>1460</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -8852,19 +8879,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1453</v>
+        <v>1461</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1454</v>
+        <v>1462</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1455</v>
+        <v>1463</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1456</v>
+        <v>1464</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1457</v>
+        <v>1465</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -8873,13 +8900,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1459</v>
+        <v>1467</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -8888,7 +8915,7 @@
         <v>40</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1460</v>
+        <v>1468</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -8897,19 +8924,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1461</v>
+        <v>1469</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1462</v>
+        <v>1470</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1463</v>
+        <v>1471</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1464</v>
+        <v>1472</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1465</v>
+        <v>1473</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -8918,13 +8945,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1466</v>
+        <v>1474</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -8933,7 +8960,7 @@
         <v>40</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1467</v>
+        <v>1475</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>150</v>
@@ -8942,19 +8969,19 @@
         <v>151</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1468</v>
+        <v>1476</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1469</v>
+        <v>1477</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1470</v>
+        <v>1478</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1471</v>
+        <v>1479</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1472</v>
+        <v>1480</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -8963,13 +8990,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1473</v>
+        <v>1481</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>127</v>
@@ -8978,28 +9005,28 @@
         <v>40</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1474</v>
+        <v>1482</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1475</v>
+        <v>1483</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1476</v>
+        <v>1484</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1477</v>
+        <v>1485</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1478</v>
+        <v>1486</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1479</v>
+        <v>1487</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -9008,13 +9035,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1480</v>
+        <v>1488</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>127</v>
@@ -9023,28 +9050,28 @@
         <v>40</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1474</v>
+        <v>1482</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1481</v>
+        <v>1489</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1482</v>
+        <v>1490</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1483</v>
+        <v>1491</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1484</v>
+        <v>1492</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1485</v>
+        <v>1493</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -9053,13 +9080,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1486</v>
+        <v>1494</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>127</v>
@@ -9068,28 +9095,28 @@
         <v>40</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1474</v>
+        <v>1482</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1487</v>
+        <v>1495</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1488</v>
+        <v>1496</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1489</v>
+        <v>1497</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1490</v>
+        <v>1498</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -9098,13 +9125,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1491</v>
+        <v>1499</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>107</v>
@@ -9113,7 +9140,7 @@
         <v>40</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1492</v>
+        <v>1500</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -9122,19 +9149,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1493</v>
+        <v>1501</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1494</v>
+        <v>1502</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1495</v>
+        <v>1503</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1496</v>
+        <v>1504</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1497</v>
+        <v>1505</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -9143,13 +9170,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1498</v>
+        <v>1506</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -9158,7 +9185,7 @@
         <v>40</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1499</v>
+        <v>1507</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -9167,19 +9194,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1500</v>
+        <v>1508</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1501</v>
+        <v>1509</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1502</v>
+        <v>1510</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1503</v>
+        <v>1511</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -9188,13 +9215,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1505</v>
+        <v>1513</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>104</v>
@@ -9203,28 +9230,28 @@
         <v>40</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1506</v>
+        <v>1514</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1507</v>
+        <v>1515</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1508</v>
+        <v>1516</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1509</v>
+        <v>1517</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1510</v>
+        <v>1518</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1511</v>
+        <v>1519</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1512</v>
+        <v>1520</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -9233,13 +9260,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1513</v>
+        <v>1521</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>127</v>
@@ -9248,7 +9275,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1514</v>
+        <v>1522</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -9257,19 +9284,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1515</v>
+        <v>1523</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1516</v>
+        <v>1524</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1517</v>
+        <v>1525</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1518</v>
+        <v>1526</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1519</v>
+        <v>1527</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -9278,13 +9305,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1458</v>
+        <v>1466</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1520</v>
+        <v>1528</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>127</v>
@@ -9293,7 +9320,7 @@
         <v>40</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1521</v>
+        <v>1529</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -9302,19 +9329,19 @@
         <v>254</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1522</v>
+        <v>1530</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1523</v>
+        <v>1531</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1524</v>
+        <v>1532</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1525</v>
+        <v>1533</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -9323,13 +9350,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1526</v>
+        <v>1534</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1527</v>
+        <v>1535</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>127</v>
@@ -9338,7 +9365,7 @@
         <v>40</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1528</v>
+        <v>1536</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -9347,19 +9374,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1529</v>
+        <v>1537</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1530</v>
+        <v>1538</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1531</v>
+        <v>1539</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1532</v>
+        <v>1540</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -9368,13 +9395,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1526</v>
+        <v>1534</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1533</v>
+        <v>1541</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>127</v>
@@ -9383,7 +9410,7 @@
         <v>40</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1534</v>
+        <v>1542</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -9392,19 +9419,19 @@
         <v>188</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1535</v>
+        <v>1543</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1536</v>
+        <v>1544</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1537</v>
+        <v>1545</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1538</v>
+        <v>1546</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -9413,13 +9440,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1539</v>
+        <v>1547</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1540</v>
+        <v>1548</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -9428,7 +9455,7 @@
         <v>40</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1541</v>
+        <v>1549</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>150</v>
@@ -9437,19 +9464,19 @@
         <v>254</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1542</v>
+        <v>1550</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1543</v>
+        <v>1551</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1544</v>
+        <v>1552</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1545</v>
+        <v>1553</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1546</v>
+        <v>1554</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>6</v>
@@ -9461,12 +9488,12 @@
         <v>157</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>1547</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>1548</v>
+        <v>1556</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -9475,28 +9502,28 @@
         <v>40</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1549</v>
+        <v>1557</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1550</v>
+        <v>1558</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1551</v>
+        <v>1559</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>1552</v>
+        <v>1560</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1553</v>
+        <v>1561</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>1555</v>
+        <v>1563</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>6</v>
@@ -9508,7 +9535,7 @@
         <v>157</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>1556</v>
+        <v>1564</v>
       </c>
     </row>
   </sheetData>
@@ -9602,7 +9629,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1557</v>
+        <v>1565</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -9611,28 +9638,28 @@
         <v>44</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1558</v>
+        <v>1566</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1559</v>
+        <v>1567</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1560</v>
+        <v>1568</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1561</v>
+        <v>1569</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1562</v>
+        <v>1570</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1563</v>
+        <v>1571</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -9641,13 +9668,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1564</v>
+        <v>1572</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1565</v>
+        <v>1573</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -9656,28 +9683,28 @@
         <v>44</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1558</v>
+        <v>1566</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1566</v>
+        <v>1574</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1567</v>
+        <v>1575</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1568</v>
+        <v>1576</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1569</v>
+        <v>1577</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1570</v>
+        <v>1578</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -9686,13 +9713,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1564</v>
+        <v>1572</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1571</v>
+        <v>1579</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -9701,7 +9728,7 @@
         <v>44</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1572</v>
+        <v>1580</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -9710,19 +9737,19 @@
         <v>151</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1573</v>
+        <v>1581</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1574</v>
+        <v>1582</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1575</v>
+        <v>1583</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1576</v>
+        <v>1584</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1577</v>
+        <v>1585</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -9731,13 +9758,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1578</v>
+        <v>1586</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1579</v>
+        <v>1587</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -9746,7 +9773,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1580</v>
+        <v>1588</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -9755,19 +9782,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1581</v>
+        <v>1589</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1582</v>
+        <v>1590</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1583</v>
+        <v>1591</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1585</v>
+        <v>1593</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -9776,13 +9803,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1586</v>
+        <v>1594</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1587</v>
+        <v>1595</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>170</v>
@@ -9791,7 +9818,7 @@
         <v>44</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1580</v>
+        <v>1588</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -9800,19 +9827,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1588</v>
+        <v>1596</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>190</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1589</v>
+        <v>1597</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1590</v>
+        <v>1598</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -9821,13 +9848,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1564</v>
+        <v>1572</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1591</v>
+        <v>1599</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -9836,28 +9863,28 @@
         <v>44</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1592</v>
+        <v>1600</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1593</v>
+        <v>1601</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1594</v>
+        <v>1602</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1595</v>
+        <v>1603</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1596</v>
+        <v>1604</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1597</v>
+        <v>1605</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -9866,13 +9893,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1598</v>
+        <v>1606</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1599</v>
+        <v>1607</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -9881,28 +9908,28 @@
         <v>44</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1592</v>
+        <v>1600</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1550</v>
+        <v>1558</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1600</v>
+        <v>1608</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1601</v>
+        <v>1609</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1602</v>
+        <v>1610</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1603</v>
+        <v>1611</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1604</v>
+        <v>1612</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -9911,13 +9938,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1598</v>
+        <v>1606</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1605</v>
+        <v>1613</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -9926,7 +9953,7 @@
         <v>44</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1606</v>
+        <v>1614</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -9935,19 +9962,19 @@
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1607</v>
+        <v>1615</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1608</v>
+        <v>1616</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1609</v>
+        <v>1617</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1610</v>
+        <v>1618</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1611</v>
+        <v>1619</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -9956,13 +9983,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1598</v>
+        <v>1606</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1612</v>
+        <v>1620</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>170</v>
@@ -9971,7 +9998,7 @@
         <v>44</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1606</v>
+        <v>1614</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -9980,19 +10007,19 @@
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1613</v>
+        <v>1621</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>190</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1614</v>
+        <v>1622</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1615</v>
+        <v>1623</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -10001,13 +10028,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1598</v>
+        <v>1606</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1616</v>
+        <v>1624</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -10016,7 +10043,7 @@
         <v>44</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1617</v>
+        <v>1625</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>150</v>
@@ -10025,19 +10052,19 @@
         <v>188</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1618</v>
+        <v>1626</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1619</v>
+        <v>1627</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1620</v>
+        <v>1628</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1621</v>
+        <v>1629</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>6</v>
@@ -10049,12 +10076,12 @@
         <v>157</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>1622</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1623</v>
+        <v>1631</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -10063,7 +10090,7 @@
         <v>44</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1624</v>
+        <v>1632</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -10072,19 +10099,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1625</v>
+        <v>1633</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1626</v>
+        <v>1634</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1627</v>
+        <v>1635</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1628</v>
+        <v>1636</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1629</v>
+        <v>1637</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -10093,13 +10120,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1598</v>
+        <v>1606</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1630</v>
+        <v>1638</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -10108,7 +10135,7 @@
         <v>44</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1631</v>
+        <v>1639</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>150</v>
@@ -10117,19 +10144,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1632</v>
+        <v>1640</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1633</v>
+        <v>1641</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1634</v>
+        <v>1642</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1635</v>
+        <v>1643</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1636</v>
+        <v>1644</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -10138,13 +10165,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1598</v>
+        <v>1606</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1637</v>
+        <v>1645</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>127</v>
@@ -10153,28 +10180,28 @@
         <v>44</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1638</v>
+        <v>1646</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1639</v>
+        <v>1647</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1640</v>
+        <v>1648</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1641</v>
+        <v>1649</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1642</v>
+        <v>1650</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1643</v>
+        <v>1651</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -10183,13 +10210,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1644</v>
+        <v>1652</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1645</v>
+        <v>1653</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>127</v>
@@ -10198,7 +10225,7 @@
         <v>44</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1646</v>
+        <v>1654</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -10207,19 +10234,19 @@
         <v>254</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1647</v>
+        <v>1655</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1648</v>
+        <v>1656</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1649</v>
+        <v>1657</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1650</v>
+        <v>1658</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1651</v>
+        <v>1659</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -10228,7 +10255,7 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>1644</v>
+        <v>1652</v>
       </c>
       <c r="O15" s="6"/>
     </row>
@@ -10323,7 +10350,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1652</v>
+        <v>1660</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -10332,7 +10359,7 @@
         <v>48</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1653</v>
+        <v>1661</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -10341,19 +10368,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1654</v>
+        <v>1662</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1655</v>
+        <v>1663</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1656</v>
+        <v>1664</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1657</v>
+        <v>1665</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1658</v>
+        <v>1666</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -10362,13 +10389,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1659</v>
+        <v>1667</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1660</v>
+        <v>1668</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -10377,7 +10404,7 @@
         <v>48</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1661</v>
+        <v>1669</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -10386,19 +10413,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1662</v>
+        <v>1670</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1664</v>
+        <v>1672</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1665</v>
+        <v>1673</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1666</v>
+        <v>1674</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -10407,13 +10434,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1659</v>
+        <v>1667</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1667</v>
+        <v>1675</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -10422,7 +10449,7 @@
         <v>48</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1668</v>
+        <v>1676</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -10431,19 +10458,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1669</v>
+        <v>1677</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1670</v>
+        <v>1678</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1671</v>
+        <v>1679</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1672</v>
+        <v>1680</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1673</v>
+        <v>1681</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -10452,13 +10479,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1659</v>
+        <v>1667</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1674</v>
+        <v>1682</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -10467,7 +10494,7 @@
         <v>48</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1675</v>
+        <v>1683</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -10476,19 +10503,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1676</v>
+        <v>1684</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1677</v>
+        <v>1685</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1678</v>
+        <v>1686</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1679</v>
+        <v>1687</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1680</v>
+        <v>1688</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -10497,13 +10524,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1659</v>
+        <v>1667</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1681</v>
+        <v>1689</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>110</v>
@@ -10512,7 +10539,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1682</v>
+        <v>1690</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>150</v>
@@ -10521,19 +10548,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1683</v>
+        <v>1691</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1684</v>
+        <v>1692</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1685</v>
+        <v>1693</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1686</v>
+        <v>1694</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1687</v>
+        <v>1695</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>6</v>
@@ -10545,12 +10572,12 @@
         <v>157</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>1688</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1689</v>
+        <v>1697</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -10559,7 +10586,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1690</v>
+        <v>1698</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -10568,19 +10595,19 @@
         <v>188</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1691</v>
+        <v>1699</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1692</v>
+        <v>1700</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1693</v>
+        <v>1701</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1694</v>
+        <v>1702</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1695</v>
+        <v>1703</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>6</v>
@@ -10592,12 +10619,12 @@
         <v>157</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>1696</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1697</v>
+        <v>1705</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -10606,7 +10633,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1698</v>
+        <v>1706</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -10615,19 +10642,19 @@
         <v>151</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1699</v>
+        <v>1707</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1700</v>
+        <v>1708</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1701</v>
+        <v>1709</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1679</v>
+        <v>1687</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1702</v>
+        <v>1710</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -10636,13 +10663,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1659</v>
+        <v>1667</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1703</v>
+        <v>1711</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -10651,7 +10678,7 @@
         <v>48</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1704</v>
+        <v>1712</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -10660,19 +10687,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1705</v>
+        <v>1713</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1706</v>
+        <v>1714</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1707</v>
+        <v>1715</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1679</v>
+        <v>1687</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1708</v>
+        <v>1716</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -10681,13 +10708,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1659</v>
+        <v>1667</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1709</v>
+        <v>1717</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -10696,7 +10723,7 @@
         <v>48</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1710</v>
+        <v>1718</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -10705,19 +10732,19 @@
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1711</v>
+        <v>1719</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1712</v>
+        <v>1720</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1713</v>
+        <v>1721</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1679</v>
+        <v>1687</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1714</v>
+        <v>1722</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -10726,13 +10753,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1659</v>
+        <v>1667</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1715</v>
+        <v>1723</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -10741,7 +10768,7 @@
         <v>48</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1716</v>
+        <v>1724</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -10750,19 +10777,19 @@
         <v>188</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1717</v>
+        <v>1725</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1718</v>
+        <v>1726</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1719</v>
+        <v>1727</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1679</v>
+        <v>1687</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1720</v>
+        <v>1728</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -10771,13 +10798,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1659</v>
+        <v>1667</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1721</v>
+        <v>1729</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -10786,7 +10813,7 @@
         <v>48</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1722</v>
+        <v>1730</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>150</v>
@@ -10795,19 +10822,19 @@
         <v>188</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1723</v>
+        <v>1731</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1724</v>
+        <v>1732</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1725</v>
+        <v>1733</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1726</v>
+        <v>1734</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1727</v>
+        <v>1735</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -10816,10 +10843,10 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1659</v>
+        <v>1667</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>1728</v>
+        <v>1736</v>
       </c>
     </row>
   </sheetData>
@@ -12484,7 +12511,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="true" style="0"/>
@@ -13862,8 +13889,55 @@
         <v>516</v>
       </c>
     </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N31" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="O31" s="6" t="s">
+        <v>524</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O30"/>
+  <autoFilter ref="A1:O31"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
@@ -13953,7 +14027,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>104</v>
@@ -13962,7 +14036,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>150</v>
@@ -13971,19 +14045,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -13992,13 +14066,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>104</v>
@@ -14007,7 +14081,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>150</v>
@@ -14016,19 +14090,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -14037,13 +14111,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>104</v>
@@ -14052,7 +14126,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>150</v>
@@ -14061,19 +14135,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -14082,13 +14156,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>104</v>
@@ -14097,7 +14171,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>150</v>
@@ -14106,19 +14180,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -14127,13 +14201,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>104</v>
@@ -14142,7 +14216,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>150</v>
@@ -14151,19 +14225,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -14172,13 +14246,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>107</v>
@@ -14187,7 +14261,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>150</v>
@@ -14196,19 +14270,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -14217,13 +14291,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>107</v>
@@ -14232,7 +14306,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>150</v>
@@ -14241,19 +14315,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -14262,13 +14336,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -14277,28 +14351,28 @@
         <v>16</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -14307,13 +14381,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>170</v>
@@ -14322,7 +14396,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -14331,19 +14405,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>190</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -14352,7 +14426,7 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="O10" s="6"/>
     </row>
@@ -14447,7 +14521,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>107</v>
@@ -14456,7 +14530,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>150</v>
@@ -14465,19 +14539,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -14486,13 +14560,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>107</v>
@@ -14501,7 +14575,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -14510,19 +14584,19 @@
         <v>188</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -14531,13 +14605,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>107</v>
@@ -14546,7 +14620,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -14555,34 +14629,34 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>598</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>599</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>600</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>602</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>590</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>107</v>
@@ -14591,7 +14665,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>150</v>
@@ -14600,19 +14674,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -14621,13 +14695,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>107</v>
@@ -14636,7 +14710,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>150</v>
@@ -14645,19 +14719,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -14666,13 +14740,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>107</v>
@@ -14681,7 +14755,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -14690,19 +14764,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -14711,13 +14785,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>107</v>
@@ -14726,7 +14800,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -14735,19 +14809,19 @@
         <v>151</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -14756,13 +14830,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>107</v>
@@ -14771,7 +14845,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -14780,19 +14854,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -14801,13 +14875,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>107</v>
@@ -14825,19 +14899,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -14846,13 +14920,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>107</v>
@@ -14861,7 +14935,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -14870,19 +14944,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -14891,13 +14965,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -14906,7 +14980,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -14915,19 +14989,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -14936,13 +15010,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -14951,7 +15025,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>150</v>
@@ -14960,19 +15034,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -14981,13 +15055,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>110</v>
@@ -14996,7 +15070,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>150</v>
@@ -15005,19 +15079,19 @@
         <v>151</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -15026,13 +15100,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -15041,7 +15115,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -15050,19 +15124,19 @@
         <v>151</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -15071,13 +15145,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -15086,7 +15160,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>150</v>
@@ -15095,19 +15169,19 @@
         <v>151</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -15116,13 +15190,13 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>110</v>
@@ -15131,7 +15205,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>150</v>
@@ -15140,19 +15214,19 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>166</v>
@@ -15161,10 +15235,10 @@
         <v>4</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>
@@ -15258,7 +15332,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -15267,7 +15341,7 @@
         <v>24</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>150</v>
@@ -15276,19 +15350,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -15297,13 +15371,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -15312,7 +15386,7 @@
         <v>24</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -15321,19 +15395,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -15342,13 +15416,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -15357,7 +15431,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -15366,34 +15440,34 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>710</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>711</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>712</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>713</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>714</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>702</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>107</v>
@@ -15402,7 +15476,7 @@
         <v>24</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -15411,19 +15485,19 @@
         <v>188</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -15432,13 +15506,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>107</v>
@@ -15447,7 +15521,7 @@
         <v>24</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -15456,19 +15530,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -15477,13 +15551,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>107</v>
@@ -15492,7 +15566,7 @@
         <v>24</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -15501,19 +15575,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -15522,13 +15596,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -15537,28 +15611,28 @@
         <v>24</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -15567,13 +15641,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>127</v>
@@ -15582,28 +15656,28 @@
         <v>24</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -15612,13 +15686,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -15627,7 +15701,7 @@
         <v>24</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -15636,19 +15710,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -15657,13 +15731,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -15672,7 +15746,7 @@
         <v>24</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -15681,19 +15755,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -15702,13 +15776,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -15717,7 +15791,7 @@
         <v>24</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -15726,19 +15800,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -15747,13 +15821,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -15762,7 +15836,7 @@
         <v>24</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -15771,19 +15845,19 @@
         <v>151</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -15792,13 +15866,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>110</v>
@@ -15807,7 +15881,7 @@
         <v>24</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -15816,19 +15890,19 @@
         <v>188</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -15837,13 +15911,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -15852,7 +15926,7 @@
         <v>24</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>150</v>
@@ -15861,19 +15935,19 @@
         <v>151</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -15882,13 +15956,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -15897,7 +15971,7 @@
         <v>24</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>160</v>
@@ -15906,19 +15980,19 @@
         <v>151</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -15927,13 +16001,13 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>110</v>
@@ -15942,7 +16016,7 @@
         <v>24</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>160</v>
@@ -15951,19 +16025,19 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>166</v>
@@ -15972,13 +16046,13 @@
         <v>4</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>110</v>
@@ -15987,28 +16061,28 @@
         <v>24</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>166</v>
@@ -16017,15 +16091,15 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="7" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>110</v>
@@ -16034,7 +16108,7 @@
         <v>24</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>150</v>
@@ -16043,19 +16117,19 @@
         <v>151</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>166</v>
@@ -16064,13 +16138,13 @@
         <v>4</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="7" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>110</v>
@@ -16079,7 +16153,7 @@
         <v>24</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>160</v>
@@ -16088,19 +16162,19 @@
         <v>151</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>166</v>
@@ -16109,13 +16183,13 @@
         <v>4</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="7" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>110</v>
@@ -16124,7 +16198,7 @@
         <v>24</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>160</v>
@@ -16133,19 +16207,19 @@
         <v>151</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>166</v>
@@ -16154,13 +16228,13 @@
         <v>4</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="7" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>110</v>
@@ -16169,7 +16243,7 @@
         <v>24</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>160</v>
@@ -16178,19 +16252,19 @@
         <v>188</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>166</v>
@@ -16199,13 +16273,13 @@
         <v>4</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="7" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>107</v>
@@ -16214,7 +16288,7 @@
         <v>24</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>160</v>
@@ -16223,19 +16297,19 @@
         <v>151</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>166</v>
@@ -16244,13 +16318,13 @@
         <v>4</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="7" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>107</v>
@@ -16259,7 +16333,7 @@
         <v>24</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>160</v>
@@ -16268,19 +16342,19 @@
         <v>151</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>166</v>
@@ -16289,13 +16363,13 @@
         <v>4</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="7" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>110</v>
@@ -16304,7 +16378,7 @@
         <v>24</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>160</v>
@@ -16313,19 +16387,19 @@
         <v>151</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>166</v>
@@ -16334,13 +16408,13 @@
         <v>4</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="7" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>110</v>
@@ -16349,7 +16423,7 @@
         <v>24</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>160</v>
@@ -16358,19 +16432,19 @@
         <v>188</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>166</v>
@@ -16379,13 +16453,13 @@
         <v>4</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="7" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>107</v>
@@ -16394,7 +16468,7 @@
         <v>24</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>160</v>
@@ -16403,19 +16477,19 @@
         <v>188</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>166</v>
@@ -16424,13 +16498,13 @@
         <v>4</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="7" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>104</v>
@@ -16439,7 +16513,7 @@
         <v>24</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>160</v>
@@ -16448,19 +16522,19 @@
         <v>188</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>166</v>
@@ -16469,13 +16543,13 @@
         <v>4</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="O28" s="6"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="7" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>110</v>
@@ -16484,7 +16558,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>150</v>
@@ -16493,19 +16567,19 @@
         <v>151</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>166</v>
@@ -16514,13 +16588,13 @@
         <v>4</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="O29" s="6"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="7" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>104</v>
@@ -16529,7 +16603,7 @@
         <v>24</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>150</v>
@@ -16538,19 +16612,19 @@
         <v>151</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>166</v>
@@ -16559,13 +16633,13 @@
         <v>4</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="O30" s="6"/>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="7" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>107</v>
@@ -16574,7 +16648,7 @@
         <v>24</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>160</v>
@@ -16583,19 +16657,19 @@
         <v>151</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>166</v>
@@ -16604,13 +16678,13 @@
         <v>4</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="O31" s="6"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="7" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>104</v>
@@ -16619,7 +16693,7 @@
         <v>24</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>160</v>
@@ -16628,36 +16702,36 @@
         <v>188</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>914</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="6" t="s">
         <v>903</v>
       </c>
-      <c r="H32" s="6" t="s">
-        <v>904</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>905</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>906</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>907</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M32" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="6" t="s">
-        <v>895</v>
-      </c>
       <c r="O32" s="6" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="7" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>107</v>
@@ -16666,7 +16740,7 @@
         <v>24</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>160</v>
@@ -16675,19 +16749,19 @@
         <v>188</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="L33" s="6" t="s">
         <v>166</v>
@@ -16696,13 +16770,13 @@
         <v>4</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="O33" s="6"/>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="7" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>104</v>
@@ -16711,7 +16785,7 @@
         <v>24</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>150</v>
@@ -16720,19 +16794,19 @@
         <v>151</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>166</v>
@@ -16741,15 +16815,15 @@
         <v>4</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="7" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>107</v>
@@ -16758,7 +16832,7 @@
         <v>24</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>160</v>
@@ -16767,19 +16841,19 @@
         <v>151</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="L35" s="6" t="s">
         <v>166</v>
@@ -16788,13 +16862,13 @@
         <v>4</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="O35" s="6"/>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="7" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>104</v>
@@ -16803,7 +16877,7 @@
         <v>24</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>160</v>
@@ -16812,19 +16886,19 @@
         <v>188</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>166</v>
@@ -16833,13 +16907,13 @@
         <v>4</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="O36" s="6"/>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="7" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>110</v>
@@ -16848,7 +16922,7 @@
         <v>24</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>150</v>
@@ -16857,19 +16931,19 @@
         <v>151</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="L37" s="6" t="s">
         <v>166</v>
@@ -16878,15 +16952,15 @@
         <v>4</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="7" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>110</v>
@@ -16895,7 +16969,7 @@
         <v>24</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -16904,19 +16978,19 @@
         <v>151</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="L38" s="6" t="s">
         <v>166</v>
@@ -16925,13 +16999,13 @@
         <v>4</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="7" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>110</v>
@@ -16940,28 +17014,28 @@
         <v>24</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="L39" s="6" t="s">
         <v>166</v>
@@ -16970,13 +17044,13 @@
         <v>4</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="O39" s="6"/>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" s="7" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>110</v>
@@ -16985,28 +17059,28 @@
         <v>24</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="L40" s="6" t="s">
         <v>166</v>
@@ -17015,13 +17089,13 @@
         <v>4</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="O40" s="6"/>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="7" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>110</v>
@@ -17030,7 +17104,7 @@
         <v>24</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>150</v>
@@ -17039,19 +17113,19 @@
         <v>151</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
       <c r="L41" s="6" t="s">
         <v>166</v>
@@ -17060,15 +17134,15 @@
         <v>4</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="7" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>110</v>
@@ -17077,7 +17151,7 @@
         <v>24</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -17086,19 +17160,19 @@
         <v>151</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="L42" s="6" t="s">
         <v>166</v>
@@ -17107,13 +17181,13 @@
         <v>4</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="O42" s="6"/>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="7" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>110</v>
@@ -17122,7 +17196,7 @@
         <v>24</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>150</v>
@@ -17131,19 +17205,19 @@
         <v>151</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="L43" s="6" t="s">
         <v>166</v>
@@ -17152,22 +17226,22 @@
         <v>4</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="O43" s="6"/>
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="7" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -17176,19 +17250,19 @@
         <v>151</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="L44" s="6" t="s">
         <v>166</v>
@@ -17197,24 +17271,24 @@
         <v>4</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
     </row>
     <row r="45" spans="1:15">
       <c r="A45" s="7" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>160</v>
@@ -17223,19 +17297,19 @@
         <v>151</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="L45" s="6" t="s">
         <v>166</v>
@@ -17244,24 +17318,24 @@
         <v>4</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="7" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>160</v>
@@ -17270,19 +17344,19 @@
         <v>188</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="L46" s="6" t="s">
         <v>166</v>
@@ -17291,24 +17365,24 @@
         <v>4</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="7" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>160</v>
@@ -17317,19 +17391,19 @@
         <v>151</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="L47" s="6" t="s">
         <v>166</v>
@@ -17338,24 +17412,24 @@
         <v>4</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="7" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>150</v>
@@ -17364,19 +17438,19 @@
         <v>254</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="L48" s="6" t="s">
         <v>166</v>
@@ -17385,24 +17459,24 @@
         <v>4</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" s="7" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>160</v>
@@ -17411,19 +17485,19 @@
         <v>151</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="L49" s="6" t="s">
         <v>166</v>
@@ -17432,15 +17506,15 @@
         <v>4</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="7" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>110</v>
@@ -17449,7 +17523,7 @@
         <v>24</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>160</v>
@@ -17458,34 +17532,34 @@
         <v>151</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="K50" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M50" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N50" s="6" t="s">
         <v>1033</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M50" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N50" s="6" t="s">
-        <v>1025</v>
       </c>
       <c r="O50" s="6"/>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="7" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>110</v>
@@ -17494,7 +17568,7 @@
         <v>24</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>160</v>
@@ -17503,19 +17577,19 @@
         <v>151</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="L51" s="6" t="s">
         <v>166</v>
@@ -17524,7 +17598,7 @@
         <v>4</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="O51" s="6"/>
     </row>
@@ -17619,7 +17693,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -17628,7 +17702,7 @@
         <v>28</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -17637,19 +17711,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -17658,13 +17732,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -17673,28 +17747,28 @@
         <v>28</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -17703,13 +17777,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -17718,7 +17792,7 @@
         <v>28</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>150</v>
@@ -17727,19 +17801,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -17748,13 +17822,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -17763,7 +17837,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -17772,19 +17846,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -17793,13 +17867,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>110</v>
@@ -17808,7 +17882,7 @@
         <v>28</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -17817,19 +17891,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -17838,13 +17912,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -17853,7 +17927,7 @@
         <v>28</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -17862,19 +17936,19 @@
         <v>188</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -17883,13 +17957,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -17898,7 +17972,7 @@
         <v>28</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -17907,19 +17981,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>6</v>
@@ -17931,12 +18005,12 @@
         <v>157</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -17945,7 +18019,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>150</v>
@@ -17954,19 +18028,19 @@
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>6</v>
@@ -17978,12 +18052,12 @@
         <v>157</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -17992,7 +18066,7 @@
         <v>28</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -18001,19 +18075,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>6</v>
@@ -18025,12 +18099,12 @@
         <v>157</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>104</v>
@@ -18039,7 +18113,7 @@
         <v>28</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>150</v>
@@ -18048,19 +18122,19 @@
         <v>254</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>6</v>

--- a/docs/test-cases/test-cases.xlsx
+++ b/docs/test-cases/test-cases.xlsx
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'02-ADMIN'!$A$1:$O$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'03-STAT'!$A$1:$O$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'04-LECT'!$A$1:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'05-STU'!$A$1:$O$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'05-STU'!$A$1:$O$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'06-CHAT'!$A$1:$O$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'07-MOD'!$A$1:$O$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'08-REC'!$A$1:$O$21</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1770">
   <si>
     <t>Nhóm</t>
   </si>
@@ -681,10 +681,10 @@
     <t>Hiện thông báo "đã gửi link đặt lại"; email chứa link reset được gửi tới inbox</t>
   </si>
   <si>
-    <t>Test đỏ: session thiếu key `status` (route trả về back kèm `success`/`error`, không phải `status`) ⇒ không đúng mong đợi của test</t>
-  </si>
-  <si>
-    <t>NGUYÊN NHÂN: `PasswordResetLinkController::store()` dùng `with('success'|'error')` còn test khẳng định `assertSessionHas('status')` — lệch đặc tả giữa test và code (không phải lỗi gửi mail). Sửa: thống nhất 1 tên key (khuyến nghị đổi test sang `success`) rồi chạy lại `php artisan test tests/Feature/Auth/ForgotPasswordTest.php`.</t>
+    <t>Đã sửa (L01): test khẳng định `assertSessionHas('success')` đúng như controller trả về ⇒ xanh</t>
+  </si>
+  <si>
+    <t>L01 — sửa TEST cho khớp đặc tả key `success`/`error` của controller (commit 027a4f3).</t>
   </si>
   <si>
     <t>TC-AUTH-08</t>
@@ -707,10 +707,10 @@
     <t>Hiện lỗi validate; không ghi password_reset_tokens; không gửi mail</t>
   </si>
   <si>
-    <t>Test đỏ: session thiếu key `errors` ⇒ không đúng mong đợi (không xác nhận được có báo lỗi cho người dùng hay không)</t>
-  </si>
-  <si>
-    <t>Cùng nguyên nhân với TC-AUTH-07: controller trả `back()-&gt;withInput()-&gt;with('error', ...)` thay vì `withErrors()`. Cần thống nhất cách báo lỗi (khuyến nghị dùng `withErrors`) rồi chạy lại test.</t>
+    <t>Đã sửa (L02): test khẳng định `assertSessionHas('error')` đúng như controller trả về ⇒ xanh</t>
+  </si>
+  <si>
+    <t>L02 — sửa TEST sang key `error` (commit 7d54489).</t>
   </si>
   <si>
     <t>TC-AUTH-09</t>
@@ -733,10 +733,10 @@
     <t>Đổi thành công, token bị xoá, đăng nhập được bằng mật khẩu mới</t>
   </si>
   <si>
-    <t>Test đỏ ở bước cuối: POST /reset-password chuyển hướng về /user/dashboard (hệ thống ĐĂNG NHẬP LUÔN sau khi đặt lại mật khẩu) trong khi test mong đợi /login</t>
-  </si>
-  <si>
-    <t>Đổi mật khẩu vẫn thành công (test khẳng định `Hash::check` đạt); chỉ lệch kỳ vọng điều hướng ⇒ cập nhật test cho khớp hành vi mới của `NewPasswordController::store()`.</t>
+    <t>Đã sửa (L03): test khẳng định redirect về `user.dashboard` + flash `success` (hệ thống ĐĂNG NHẬP LUÔN sau khi đặt lại mật khẩu)</t>
+  </si>
+  <si>
+    <t>L03 — cập nhật kỳ vọng điều hướng của test cho khớp `NewPasswordController::store()` (commit 6d18aa8).</t>
   </si>
   <si>
     <t>TC-AUTH-10</t>
@@ -783,13 +783,13 @@
     <t>Thông báo đổi thành công; đăng nhập lại bằng mật khẩu mới OK; mật khẩu cũ không dùng được</t>
   </si>
   <si>
-    <t>Đổi mật khẩu + hash đúng (2 khẳng định đầu đạt) nhưng bước “đăng nhập lại” trả HTTP 500 — RouteNotFoundException: Route [verification.notice] not defined</t>
+    <t>Đã sửa (L04): gỡ hẳn gate xác thực email khỏi `AuthController::login()` ⇒ đăng nhập lại thành công, không còn 500</t>
   </si>
   <si>
     <t>tests/Feature/ChangePasswordTest.php</t>
   </si>
   <si>
-    <t>BUG THẬT (không phải lỗi test): `AuthController::login()` gọi `route('verification.notice')` khi `email_verified_at` NULL, nhưng `bootstrap/app.php` chỉ nạp `routes/web.php` — file `routes/auth.php` (nơi định nghĩa `verification.notice`, `verification.verify`, `password.update`…) KHÔNG được nạp. Hệ quả: mọi tài khoản chưa xác thực email đăng nhập đều 500. Khắc phục: nạp `routes/auth.php` trong `bootstrap/app.php` (thêm `then:`/`withRouting(web: ...)`) hoặc bỏ nhánh redirect đó.</t>
+    <t>L04 — sửa CODE: bỏ nhánh `hasVerifiedEmail → verification.notice` (commit e1a53ad). Đăng nhập/tạo tài khoản KHÔNG cần xác thực mail; chỉ quên MK + đổi email mới cần.</t>
   </si>
   <si>
     <t>TC-AUTH-12</t>
@@ -1075,13 +1075,13 @@
     <t>Chuyển tới trang “yêu cầu xác thực email” (route `verification.notice`) kèm hướng dẫn gửi lại email — KHÔNG được 500</t>
   </si>
   <si>
-    <t>HTTP 500 — RouteNotFoundException: Route [verification.notice] not defined</t>
+    <t>Đã sửa (L04): tài khoản chưa xác thực email đăng nhập bình thường (redirect theo vai trò), không còn HTTP 500</t>
   </si>
   <si>
     <t>tests/Feature/ChangePasswordTest.php (case “đổi mật khẩu thành công…” phát hiện lỗi này)</t>
   </si>
   <si>
-    <t>BUG THẬT: `bootstrap/app.php` chỉ nạp `routes/web.php` + console + channels, KHÔNG nạp `routes/auth.php` (nơi định nghĩa `verification.notice`). Khắc phục rồi chạy lại `php artisan test` để xác nhận.</t>
+    <t>L04 — sửa CODE (commit e1a53ad): bỏ nhánh redirect tới `verification.notice` trong `AuthController::login()` (file `routes/auth.php` không được nạp nên route này không tồn tại).</t>
   </si>
   <si>
     <t>TC-AUTH-26</t>
@@ -3500,6 +3500,39 @@
     <t>Đăng ký cùng loại bị chặn kèm thông báo; duyệt giữa kì chỉ từ chối các yêu cầu CÙNG LOẠI ⇒ yêu cầu cuối kì vẫn Pending</t>
   </si>
   <si>
+    <t>TC-STU-51</t>
+  </si>
+  <si>
+    <t>Xóa mềm nhóm (#8)</t>
+  </si>
+  <si>
+    <t>L10 — Admin/GV xóa MỀM nhóm: ẩn khỏi danh sách, nhả đề tài về chưa đăng ký, SV tạo lại nhóm mới, có khôi phục</t>
+  </si>
+  <si>
+    <t>Nhóm có thành viên + đề tài đã được duyệt; đăng nhập lần lượt Admin, GV phụ trách, GV khác lớp, sinh viên</t>
+  </si>
+  <si>
+    <t>GV khác lớp gọi DELETE /groups/{id} (case âm)
+Sinh viên gọi DELETE /groups/{id} (case âm)
+Admin/GV phụ trách xóa nhóm (có đề tài)
+Kiểm tra danh sách + tab "Đã xóa" (?trashed=1)
+Sinh viên cũ tạo nhóm mới trong lớp
+Khôi phục nhóm → kiểm tra đề tài
+Admin xóa vĩnh viễn (case âm: giảng viên)</t>
+  </si>
+  <si>
+    <t>DELETE /groups/{id} · POST /groups/{id}/restore · DELETE /groups/{id}/force · GET /groups?trashed=1</t>
+  </si>
+  <si>
+    <t>GV khác lớp + sinh viên bị chặn kèm thông báo; xóa nhóm = xóa MỀM (nhóm biến mất khỏi danh sách nhưng DB còn `deleted_at`); đề tài nhả về chưa đăng ký (`groups.topic_id` = NULL, `topics.assigned_group_id` = NULL, `topic_requests` Pending/Accepted → Cancelled + lý do); lời mời/yêu cầu treo → Expired (giữ dòng); sinh viên nhóm đã xóa được coi như chưa có nhóm ⇒ tạo được nhóm mới; khôi phục KHÔNG tự lấy lại đề tài cũ; xóa vĩnh viễn chỉ Admin</t>
+  </si>
+  <si>
+    <t>tests/Feature/GroupSoftDeleteTest.php</t>
+  </si>
+  <si>
+    <t>Kèm sửa lỗi cũ: nhóm route `groups.*` thiếu middleware `auth` ⇒ khách vào /groups gây HTTP 500 (nay chuyển hướng về /login).</t>
+  </si>
+  <si>
     <t>TC-CHAT-01</t>
   </si>
   <si>
@@ -5777,7 +5810,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -5823,17 +5856,8 @@
       <color rgb="FF065F46"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FF991B1B"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5858,12 +5882,6 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -5877,7 +5895,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
@@ -5900,9 +5918,6 @@
       <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
@@ -6257,10 +6272,10 @@
         <v>27</v>
       </c>
       <c r="E2" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3">
         <v>1</v>
@@ -6358,10 +6373,10 @@
         <v>26</v>
       </c>
       <c r="D6" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E6" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
@@ -6536,13 +6551,13 @@
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="4">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E13" s="4">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F13" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4">
         <v>20</v>
@@ -6639,7 +6654,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1137</v>
+        <v>1146</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>127</v>
@@ -6648,7 +6663,7 @@
         <v>32</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1138</v>
+        <v>1147</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -6657,19 +6672,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1139</v>
+        <v>1148</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1140</v>
+        <v>1149</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1141</v>
+        <v>1150</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1142</v>
+        <v>1151</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1143</v>
+        <v>1152</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -6678,13 +6693,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1145</v>
+        <v>1154</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>127</v>
@@ -6693,7 +6708,7 @@
         <v>32</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1146</v>
+        <v>1155</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -6702,19 +6717,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1147</v>
+        <v>1156</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1148</v>
+        <v>1157</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1149</v>
+        <v>1158</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1150</v>
+        <v>1159</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1151</v>
+        <v>1160</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -6723,13 +6738,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1152</v>
+        <v>1161</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1153</v>
+        <v>1162</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>127</v>
@@ -6738,7 +6753,7 @@
         <v>32</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1154</v>
+        <v>1163</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -6747,19 +6762,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1155</v>
+        <v>1164</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1156</v>
+        <v>1165</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1157</v>
+        <v>1166</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1159</v>
+        <v>1168</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -6768,13 +6783,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1160</v>
+        <v>1169</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>127</v>
@@ -6783,7 +6798,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1161</v>
+        <v>1170</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -6792,19 +6807,19 @@
         <v>188</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1162</v>
+        <v>1171</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1156</v>
+        <v>1165</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1163</v>
+        <v>1172</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1164</v>
+        <v>1173</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1165</v>
+        <v>1174</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -6813,13 +6828,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1166</v>
+        <v>1175</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1167</v>
+        <v>1176</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>127</v>
@@ -6828,7 +6843,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1168</v>
+        <v>1177</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -6837,19 +6852,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1169</v>
+        <v>1178</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1170</v>
+        <v>1179</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1171</v>
+        <v>1180</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1172</v>
+        <v>1181</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1173</v>
+        <v>1182</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -6858,13 +6873,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1174</v>
+        <v>1183</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>127</v>
@@ -6873,7 +6888,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1168</v>
+        <v>1177</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -6882,19 +6897,19 @@
         <v>188</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1175</v>
+        <v>1184</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1176</v>
+        <v>1185</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1177</v>
+        <v>1186</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1178</v>
+        <v>1187</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1179</v>
+        <v>1188</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -6903,13 +6918,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1152</v>
+        <v>1161</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1180</v>
+        <v>1189</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>127</v>
@@ -6918,7 +6933,7 @@
         <v>32</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1181</v>
+        <v>1190</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -6927,19 +6942,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1182</v>
+        <v>1191</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1183</v>
+        <v>1192</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1184</v>
+        <v>1193</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1185</v>
+        <v>1194</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1186</v>
+        <v>1195</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -6948,13 +6963,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1187</v>
+        <v>1196</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>127</v>
@@ -6963,7 +6978,7 @@
         <v>32</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1188</v>
+        <v>1197</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -6972,19 +6987,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1189</v>
+        <v>1198</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1190</v>
+        <v>1199</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1191</v>
+        <v>1200</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1192</v>
+        <v>1201</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1193</v>
+        <v>1202</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -6993,15 +7008,15 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>1194</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1195</v>
+        <v>1204</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>127</v>
@@ -7010,7 +7025,7 @@
         <v>32</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1196</v>
+        <v>1205</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -7019,19 +7034,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1197</v>
+        <v>1206</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1198</v>
+        <v>1207</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1199</v>
+        <v>1208</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1200</v>
+        <v>1209</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1201</v>
+        <v>1210</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -7040,13 +7055,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1202</v>
+        <v>1211</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -7055,7 +7070,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -7064,19 +7079,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1205</v>
+        <v>1214</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1206</v>
+        <v>1215</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1207</v>
+        <v>1216</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1208</v>
+        <v>1217</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -7085,13 +7100,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1209</v>
+        <v>1218</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1210</v>
+        <v>1219</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -7100,7 +7115,7 @@
         <v>32</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -7109,19 +7124,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1211</v>
+        <v>1220</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1156</v>
+        <v>1165</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1212</v>
+        <v>1221</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1213</v>
+        <v>1222</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1214</v>
+        <v>1223</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -7130,13 +7145,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1215</v>
+        <v>1224</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1216</v>
+        <v>1225</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -7145,7 +7160,7 @@
         <v>32</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -7154,19 +7169,19 @@
         <v>151</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1217</v>
+        <v>1226</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1218</v>
+        <v>1227</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1219</v>
+        <v>1228</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1220</v>
+        <v>1229</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1221</v>
+        <v>1230</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -7175,13 +7190,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1222</v>
+        <v>1231</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1223</v>
+        <v>1232</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>110</v>
@@ -7190,7 +7205,7 @@
         <v>32</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1224</v>
+        <v>1233</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -7199,19 +7214,19 @@
         <v>151</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1225</v>
+        <v>1234</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1226</v>
+        <v>1235</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1227</v>
+        <v>1236</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1228</v>
+        <v>1237</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1229</v>
+        <v>1238</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -7220,13 +7235,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1230</v>
+        <v>1239</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1231</v>
+        <v>1240</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -7235,7 +7250,7 @@
         <v>32</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -7244,19 +7259,19 @@
         <v>188</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1232</v>
+        <v>1241</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1233</v>
+        <v>1242</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1234</v>
+        <v>1243</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1235</v>
+        <v>1244</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1236</v>
+        <v>1245</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -7265,13 +7280,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>1209</v>
+        <v>1218</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>1237</v>
+        <v>1246</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>104</v>
@@ -7280,7 +7295,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1238</v>
+        <v>1247</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>160</v>
@@ -7289,19 +7304,19 @@
         <v>151</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1239</v>
+        <v>1248</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>1240</v>
+        <v>1249</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1241</v>
+        <v>1250</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>1242</v>
+        <v>1251</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>1243</v>
+        <v>1252</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -7310,13 +7325,13 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>1244</v>
+        <v>1253</v>
       </c>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>1245</v>
+        <v>1254</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>104</v>
@@ -7325,7 +7340,7 @@
         <v>32</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1246</v>
+        <v>1255</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>160</v>
@@ -7334,19 +7349,19 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>1247</v>
+        <v>1256</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>1248</v>
+        <v>1257</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>1249</v>
+        <v>1258</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>1250</v>
+        <v>1259</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>1251</v>
+        <v>1260</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>166</v>
@@ -7355,13 +7370,13 @@
         <v>4</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>1252</v>
+        <v>1261</v>
       </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7" t="s">
-        <v>1253</v>
+        <v>1262</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>104</v>
@@ -7370,7 +7385,7 @@
         <v>32</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1254</v>
+        <v>1263</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>160</v>
@@ -7379,19 +7394,19 @@
         <v>151</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>1255</v>
+        <v>1264</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>1256</v>
+        <v>1265</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>1257</v>
+        <v>1266</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>1258</v>
+        <v>1267</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>1259</v>
+        <v>1268</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>166</v>
@@ -7400,13 +7415,13 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>1244</v>
+        <v>1253</v>
       </c>
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="7" t="s">
-        <v>1260</v>
+        <v>1269</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>104</v>
@@ -7415,7 +7430,7 @@
         <v>32</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1261</v>
+        <v>1270</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>160</v>
@@ -7424,19 +7439,19 @@
         <v>188</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>1262</v>
+        <v>1271</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>1263</v>
+        <v>1272</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>1264</v>
+        <v>1273</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>1265</v>
+        <v>1274</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>166</v>
@@ -7445,13 +7460,13 @@
         <v>4</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>1267</v>
+        <v>1276</v>
       </c>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="7" t="s">
-        <v>1268</v>
+        <v>1277</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>104</v>
@@ -7460,7 +7475,7 @@
         <v>32</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1269</v>
+        <v>1278</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>160</v>
@@ -7469,19 +7484,19 @@
         <v>151</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1270</v>
+        <v>1279</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>1271</v>
+        <v>1280</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>1272</v>
+        <v>1281</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>1273</v>
+        <v>1282</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>1274</v>
+        <v>1283</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>166</v>
@@ -7490,13 +7505,13 @@
         <v>4</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>1275</v>
+        <v>1284</v>
       </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="7" t="s">
-        <v>1276</v>
+        <v>1285</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>104</v>
@@ -7505,7 +7520,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1269</v>
+        <v>1278</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>160</v>
@@ -7514,19 +7529,19 @@
         <v>188</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>1278</v>
+        <v>1287</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>1279</v>
+        <v>1288</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>1280</v>
+        <v>1289</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>1281</v>
+        <v>1290</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>166</v>
@@ -7535,13 +7550,13 @@
         <v>4</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>1282</v>
+        <v>1291</v>
       </c>
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="7" t="s">
-        <v>1283</v>
+        <v>1292</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>110</v>
@@ -7550,7 +7565,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1284</v>
+        <v>1293</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>160</v>
@@ -7559,19 +7574,19 @@
         <v>151</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1285</v>
+        <v>1294</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>1286</v>
+        <v>1295</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>1287</v>
+        <v>1296</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>1288</v>
+        <v>1297</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>1289</v>
+        <v>1298</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>166</v>
@@ -7580,13 +7595,13 @@
         <v>4</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>1267</v>
+        <v>1276</v>
       </c>
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="7" t="s">
-        <v>1290</v>
+        <v>1299</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>104</v>
@@ -7595,7 +7610,7 @@
         <v>32</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1291</v>
+        <v>1300</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>150</v>
@@ -7604,19 +7619,19 @@
         <v>188</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>1292</v>
+        <v>1301</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>1293</v>
+        <v>1302</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>1294</v>
+        <v>1303</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>1295</v>
+        <v>1304</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>1296</v>
+        <v>1305</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>166</v>
@@ -7625,13 +7640,13 @@
         <v>4</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>1244</v>
+        <v>1253</v>
       </c>
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="7" t="s">
-        <v>1297</v>
+        <v>1306</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>104</v>
@@ -7640,7 +7655,7 @@
         <v>32</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1298</v>
+        <v>1307</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>150</v>
@@ -7649,19 +7664,19 @@
         <v>254</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1299</v>
+        <v>1308</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>387</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>1300</v>
+        <v>1309</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>1301</v>
+        <v>1310</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>166</v>
@@ -7670,13 +7685,13 @@
         <v>4</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>1244</v>
+        <v>1253</v>
       </c>
       <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="7" t="s">
-        <v>1303</v>
+        <v>1312</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>104</v>
@@ -7685,7 +7700,7 @@
         <v>32</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1304</v>
+        <v>1313</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>150</v>
@@ -7694,19 +7709,19 @@
         <v>188</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>1305</v>
+        <v>1314</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>1306</v>
+        <v>1315</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>1307</v>
+        <v>1316</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>1308</v>
+        <v>1317</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>1309</v>
+        <v>1318</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>166</v>
@@ -7715,13 +7730,13 @@
         <v>4</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>1275</v>
+        <v>1284</v>
       </c>
       <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="7" t="s">
-        <v>1310</v>
+        <v>1319</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>104</v>
@@ -7730,7 +7745,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1269</v>
+        <v>1278</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>160</v>
@@ -7739,19 +7754,19 @@
         <v>188</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>1311</v>
+        <v>1320</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>387</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>1312</v>
+        <v>1321</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>1313</v>
+        <v>1322</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>1314</v>
+        <v>1323</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>166</v>
@@ -7760,13 +7775,13 @@
         <v>4</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>1275</v>
+        <v>1284</v>
       </c>
       <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="7" t="s">
-        <v>1315</v>
+        <v>1324</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>104</v>
@@ -7775,7 +7790,7 @@
         <v>32</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1316</v>
+        <v>1325</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>150</v>
@@ -7784,19 +7799,19 @@
         <v>254</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>1319</v>
+        <v>1328</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>1320</v>
+        <v>1329</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>1321</v>
+        <v>1330</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>166</v>
@@ -7805,13 +7820,13 @@
         <v>4</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>1244</v>
+        <v>1253</v>
       </c>
       <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="7" t="s">
-        <v>1322</v>
+        <v>1331</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>110</v>
@@ -7820,7 +7835,7 @@
         <v>32</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1323</v>
+        <v>1332</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>150</v>
@@ -7829,19 +7844,19 @@
         <v>151</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>1324</v>
+        <v>1333</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>1325</v>
+        <v>1334</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>1326</v>
+        <v>1335</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>1327</v>
+        <v>1336</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>1328</v>
+        <v>1337</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>6</v>
@@ -7850,15 +7865,15 @@
         <v>6</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>1329</v>
+        <v>1338</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>1330</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="7" t="s">
-        <v>1331</v>
+        <v>1340</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>110</v>
@@ -7867,7 +7882,7 @@
         <v>32</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>1332</v>
+        <v>1341</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>160</v>
@@ -7876,19 +7891,19 @@
         <v>151</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>1334</v>
+        <v>1343</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>1335</v>
+        <v>1344</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>1336</v>
+        <v>1345</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>1337</v>
+        <v>1346</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>166</v>
@@ -7897,10 +7912,10 @@
         <v>4</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>1338</v>
+        <v>1347</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>1339</v>
+        <v>1348</v>
       </c>
     </row>
   </sheetData>
@@ -7994,7 +8009,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1340</v>
+        <v>1349</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -8003,7 +8018,7 @@
         <v>36</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1341</v>
+        <v>1350</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -8012,19 +8027,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1342</v>
+        <v>1351</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1343</v>
+        <v>1352</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1344</v>
+        <v>1353</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1345</v>
+        <v>1354</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1346</v>
+        <v>1355</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -8033,13 +8048,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1348</v>
+        <v>1357</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -8048,7 +8063,7 @@
         <v>36</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1349</v>
+        <v>1358</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -8057,19 +8072,19 @@
         <v>188</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1350</v>
+        <v>1359</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1351</v>
+        <v>1360</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1352</v>
+        <v>1361</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1353</v>
+        <v>1362</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1354</v>
+        <v>1363</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -8078,13 +8093,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1355</v>
+        <v>1364</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1356</v>
+        <v>1365</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -8093,7 +8108,7 @@
         <v>36</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1357</v>
+        <v>1366</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -8102,19 +8117,19 @@
         <v>151</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1358</v>
+        <v>1367</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1359</v>
+        <v>1368</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1360</v>
+        <v>1369</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1361</v>
+        <v>1370</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1362</v>
+        <v>1371</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -8123,13 +8138,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1363</v>
+        <v>1372</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -8138,7 +8153,7 @@
         <v>36</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1364</v>
+        <v>1373</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>594</v>
@@ -8147,19 +8162,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1365</v>
+        <v>1374</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1366</v>
+        <v>1375</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1367</v>
+        <v>1376</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1368</v>
+        <v>1377</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1369</v>
+        <v>1378</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -8168,13 +8183,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1370</v>
+        <v>1379</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>110</v>
@@ -8183,7 +8198,7 @@
         <v>36</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1371</v>
+        <v>1380</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -8192,19 +8207,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1372</v>
+        <v>1381</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1373</v>
+        <v>1382</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1374</v>
+        <v>1383</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1375</v>
+        <v>1384</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1376</v>
+        <v>1385</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -8213,13 +8228,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1377</v>
+        <v>1386</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -8228,7 +8243,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1378</v>
+        <v>1387</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -8237,19 +8252,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1379</v>
+        <v>1388</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1380</v>
+        <v>1389</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1381</v>
+        <v>1390</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1382</v>
+        <v>1391</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1383</v>
+        <v>1392</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -8258,15 +8273,15 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1384</v>
+        <v>1393</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>1385</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1386</v>
+        <v>1395</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -8275,7 +8290,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1387</v>
+        <v>1396</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -8284,19 +8299,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1388</v>
+        <v>1397</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1389</v>
+        <v>1398</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1390</v>
+        <v>1399</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1382</v>
+        <v>1391</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1391</v>
+        <v>1400</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -8305,13 +8320,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1384</v>
+        <v>1393</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1392</v>
+        <v>1401</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -8320,7 +8335,7 @@
         <v>36</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1393</v>
+        <v>1402</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -8329,19 +8344,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1394</v>
+        <v>1403</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1395</v>
+        <v>1404</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1396</v>
+        <v>1405</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1397</v>
+        <v>1406</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1398</v>
+        <v>1407</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -8350,13 +8365,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1399</v>
+        <v>1408</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -8365,7 +8380,7 @@
         <v>36</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1400</v>
+        <v>1409</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>150</v>
@@ -8374,19 +8389,19 @@
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1401</v>
+        <v>1410</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1402</v>
+        <v>1411</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1403</v>
+        <v>1412</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>908</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1404</v>
+        <v>1413</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -8395,13 +8410,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1405</v>
+        <v>1414</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>127</v>
@@ -8410,7 +8425,7 @@
         <v>36</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1406</v>
+        <v>1415</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -8419,19 +8434,19 @@
         <v>188</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1407</v>
+        <v>1416</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1408</v>
+        <v>1417</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1409</v>
+        <v>1418</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1410</v>
+        <v>1419</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1411</v>
+        <v>1420</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -8440,13 +8455,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1355</v>
+        <v>1364</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1412</v>
+        <v>1421</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>127</v>
@@ -8455,7 +8470,7 @@
         <v>36</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1413</v>
+        <v>1422</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>594</v>
@@ -8464,19 +8479,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1414</v>
+        <v>1423</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1415</v>
+        <v>1424</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1416</v>
+        <v>1425</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1417</v>
+        <v>1426</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1418</v>
+        <v>1427</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -8485,13 +8500,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1419</v>
+        <v>1428</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1420</v>
+        <v>1429</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>127</v>
@@ -8500,7 +8515,7 @@
         <v>36</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1421</v>
+        <v>1430</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -8509,19 +8524,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1422</v>
+        <v>1431</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1408</v>
+        <v>1417</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1423</v>
+        <v>1432</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1425</v>
+        <v>1434</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -8530,13 +8545,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1355</v>
+        <v>1364</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1426</v>
+        <v>1435</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>127</v>
@@ -8545,7 +8560,7 @@
         <v>36</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1427</v>
+        <v>1436</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -8554,19 +8569,19 @@
         <v>151</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1428</v>
+        <v>1437</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1429</v>
+        <v>1438</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1430</v>
+        <v>1439</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1431</v>
+        <v>1440</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1432</v>
+        <v>1441</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -8575,13 +8590,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1355</v>
+        <v>1364</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1433</v>
+        <v>1442</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>127</v>
@@ -8590,7 +8605,7 @@
         <v>36</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1434</v>
+        <v>1443</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -8599,19 +8614,19 @@
         <v>188</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1435</v>
+        <v>1444</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1436</v>
+        <v>1445</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1437</v>
+        <v>1446</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1438</v>
+        <v>1447</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1439</v>
+        <v>1448</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -8620,13 +8635,13 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>1355</v>
+        <v>1364</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>1440</v>
+        <v>1449</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -8635,7 +8650,7 @@
         <v>36</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1441</v>
+        <v>1450</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>160</v>
@@ -8644,19 +8659,19 @@
         <v>188</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1442</v>
+        <v>1451</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>1443</v>
+        <v>1452</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1444</v>
+        <v>1453</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>1445</v>
+        <v>1454</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>1446</v>
+        <v>1455</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>166</v>
@@ -8665,15 +8680,15 @@
         <v>4</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>1355</v>
+        <v>1364</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>1447</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="7" t="s">
-        <v>1448</v>
+        <v>1457</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>110</v>
@@ -8682,7 +8697,7 @@
         <v>36</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1449</v>
+        <v>1458</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>150</v>
@@ -8691,19 +8706,19 @@
         <v>151</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>1450</v>
+        <v>1459</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>1451</v>
+        <v>1460</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>1452</v>
+        <v>1461</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>1453</v>
+        <v>1462</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>1454</v>
+        <v>1463</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>166</v>
@@ -8712,13 +8727,13 @@
         <v>4</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="7" t="s">
-        <v>1455</v>
+        <v>1464</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>110</v>
@@ -8727,7 +8742,7 @@
         <v>36</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1456</v>
+        <v>1465</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>150</v>
@@ -8736,19 +8751,19 @@
         <v>151</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>1457</v>
+        <v>1466</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>1458</v>
+        <v>1467</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>1459</v>
+        <v>1468</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>908</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>1460</v>
+        <v>1469</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>166</v>
@@ -8757,13 +8772,13 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="7" t="s">
-        <v>1461</v>
+        <v>1470</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>110</v>
@@ -8772,7 +8787,7 @@
         <v>36</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1456</v>
+        <v>1465</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>160</v>
@@ -8781,19 +8796,19 @@
         <v>151</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>1462</v>
+        <v>1471</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>1463</v>
+        <v>1472</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>1464</v>
+        <v>1473</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>1465</v>
+        <v>1474</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>1466</v>
+        <v>1475</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>166</v>
@@ -8802,13 +8817,13 @@
         <v>4</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="7" t="s">
-        <v>1467</v>
+        <v>1476</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>110</v>
@@ -8817,7 +8832,7 @@
         <v>36</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1468</v>
+        <v>1477</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>150</v>
@@ -8826,19 +8841,19 @@
         <v>188</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1469</v>
+        <v>1478</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>1470</v>
+        <v>1479</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>1471</v>
+        <v>1480</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>1472</v>
+        <v>1481</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>1473</v>
+        <v>1482</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>166</v>
@@ -8847,22 +8862,22 @@
         <v>4</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="7" t="s">
-        <v>1474</v>
+        <v>1483</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1475</v>
+        <v>1484</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1476</v>
+        <v>1485</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>160</v>
@@ -8871,19 +8886,19 @@
         <v>151</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>1477</v>
+        <v>1486</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>1478</v>
+        <v>1487</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>1479</v>
+        <v>1488</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>1480</v>
+        <v>1489</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>1481</v>
+        <v>1490</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>166</v>
@@ -8892,10 +8907,10 @@
         <v>4</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>1482</v>
+        <v>1491</v>
       </c>
     </row>
   </sheetData>
@@ -8989,7 +9004,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>107</v>
@@ -8998,7 +9013,7 @@
         <v>40</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1484</v>
+        <v>1493</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -9007,19 +9022,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1485</v>
+        <v>1494</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1486</v>
+        <v>1495</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1487</v>
+        <v>1496</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1488</v>
+        <v>1497</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1489</v>
+        <v>1498</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -9028,13 +9043,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1490</v>
+        <v>1499</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1491</v>
+        <v>1500</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -9043,7 +9058,7 @@
         <v>40</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1492</v>
+        <v>1501</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -9052,19 +9067,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1493</v>
+        <v>1502</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1494</v>
+        <v>1503</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1495</v>
+        <v>1504</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1496</v>
+        <v>1505</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1497</v>
+        <v>1506</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -9073,13 +9088,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1490</v>
+        <v>1499</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1498</v>
+        <v>1507</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -9088,7 +9103,7 @@
         <v>40</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1499</v>
+        <v>1508</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>150</v>
@@ -9097,19 +9112,19 @@
         <v>151</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1500</v>
+        <v>1509</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1501</v>
+        <v>1510</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1502</v>
+        <v>1511</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1503</v>
+        <v>1512</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1504</v>
+        <v>1513</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -9118,13 +9133,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1490</v>
+        <v>1499</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1505</v>
+        <v>1514</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>127</v>
@@ -9133,7 +9148,7 @@
         <v>40</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1506</v>
+        <v>1515</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>594</v>
@@ -9142,19 +9157,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1507</v>
+        <v>1516</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1508</v>
+        <v>1517</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1509</v>
+        <v>1518</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1510</v>
+        <v>1519</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1511</v>
+        <v>1520</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -9163,13 +9178,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1490</v>
+        <v>1499</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1512</v>
+        <v>1521</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>127</v>
@@ -9178,7 +9193,7 @@
         <v>40</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1506</v>
+        <v>1515</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>594</v>
@@ -9187,19 +9202,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1513</v>
+        <v>1522</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1514</v>
+        <v>1523</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1515</v>
+        <v>1524</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1516</v>
+        <v>1525</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -9208,13 +9223,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1490</v>
+        <v>1499</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>127</v>
@@ -9223,7 +9238,7 @@
         <v>40</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1506</v>
+        <v>1515</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>594</v>
@@ -9232,19 +9247,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1519</v>
+        <v>1528</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1521</v>
+        <v>1530</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>869</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1522</v>
+        <v>1531</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -9253,13 +9268,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1490</v>
+        <v>1499</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1523</v>
+        <v>1532</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>107</v>
@@ -9268,7 +9283,7 @@
         <v>40</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -9277,19 +9292,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1525</v>
+        <v>1534</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1526</v>
+        <v>1535</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1527</v>
+        <v>1536</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1528</v>
+        <v>1537</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1529</v>
+        <v>1538</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -9298,13 +9313,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1490</v>
+        <v>1499</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1530</v>
+        <v>1539</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -9313,7 +9328,7 @@
         <v>40</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1531</v>
+        <v>1540</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -9322,19 +9337,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1532</v>
+        <v>1541</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1533</v>
+        <v>1542</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1535</v>
+        <v>1544</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1536</v>
+        <v>1545</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -9343,13 +9358,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1490</v>
+        <v>1499</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1537</v>
+        <v>1546</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>104</v>
@@ -9358,28 +9373,28 @@
         <v>40</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1538</v>
+        <v>1547</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1539</v>
+        <v>1548</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1540</v>
+        <v>1549</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1541</v>
+        <v>1550</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1542</v>
+        <v>1551</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1543</v>
+        <v>1552</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1544</v>
+        <v>1553</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -9388,13 +9403,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1490</v>
+        <v>1499</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1545</v>
+        <v>1554</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>127</v>
@@ -9403,7 +9418,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1546</v>
+        <v>1555</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -9412,19 +9427,19 @@
         <v>151</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1547</v>
+        <v>1556</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1548</v>
+        <v>1557</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1549</v>
+        <v>1558</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1550</v>
+        <v>1559</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1551</v>
+        <v>1560</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -9433,13 +9448,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1490</v>
+        <v>1499</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1552</v>
+        <v>1561</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>127</v>
@@ -9448,7 +9463,7 @@
         <v>40</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1553</v>
+        <v>1562</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -9457,19 +9472,19 @@
         <v>254</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1554</v>
+        <v>1563</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1408</v>
+        <v>1417</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1555</v>
+        <v>1564</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1556</v>
+        <v>1565</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1557</v>
+        <v>1566</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -9478,13 +9493,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1558</v>
+        <v>1567</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1559</v>
+        <v>1568</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>127</v>
@@ -9493,7 +9508,7 @@
         <v>40</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1560</v>
+        <v>1569</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>160</v>
@@ -9502,19 +9517,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1561</v>
+        <v>1570</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1408</v>
+        <v>1417</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1562</v>
+        <v>1571</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1563</v>
+        <v>1572</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1564</v>
+        <v>1573</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -9523,13 +9538,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1558</v>
+        <v>1567</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1565</v>
+        <v>1574</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>127</v>
@@ -9538,7 +9553,7 @@
         <v>40</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1566</v>
+        <v>1575</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>160</v>
@@ -9547,19 +9562,19 @@
         <v>188</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1567</v>
+        <v>1576</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1408</v>
+        <v>1417</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1568</v>
+        <v>1577</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1569</v>
+        <v>1578</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1570</v>
+        <v>1579</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -9568,13 +9583,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1572</v>
+        <v>1581</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>110</v>
@@ -9583,7 +9598,7 @@
         <v>40</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1573</v>
+        <v>1582</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>150</v>
@@ -9592,19 +9607,19 @@
         <v>254</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1574</v>
+        <v>1583</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1575</v>
+        <v>1584</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1576</v>
+        <v>1585</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1577</v>
+        <v>1586</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1578</v>
+        <v>1587</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>6</v>
@@ -9616,12 +9631,12 @@
         <v>157</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
-        <v>1580</v>
+        <v>1589</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>110</v>
@@ -9630,28 +9645,28 @@
         <v>40</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1581</v>
+        <v>1590</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1582</v>
+        <v>1591</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>188</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>1583</v>
+        <v>1592</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>1584</v>
+        <v>1593</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>1585</v>
+        <v>1594</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>1586</v>
+        <v>1595</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>6</v>
@@ -9663,7 +9678,7 @@
         <v>157</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>1588</v>
+        <v>1597</v>
       </c>
     </row>
   </sheetData>
@@ -9757,7 +9772,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1589</v>
+        <v>1598</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -9766,7 +9781,7 @@
         <v>44</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1590</v>
+        <v>1599</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>594</v>
@@ -9775,19 +9790,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1591</v>
+        <v>1600</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1592</v>
+        <v>1601</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1593</v>
+        <v>1602</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1595</v>
+        <v>1604</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -9796,13 +9811,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1596</v>
+        <v>1605</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1597</v>
+        <v>1606</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -9811,7 +9826,7 @@
         <v>44</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1590</v>
+        <v>1599</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>594</v>
@@ -9820,19 +9835,19 @@
         <v>188</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1598</v>
+        <v>1607</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1599</v>
+        <v>1608</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1600</v>
+        <v>1609</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1601</v>
+        <v>1610</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1602</v>
+        <v>1611</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -9841,13 +9856,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1596</v>
+        <v>1605</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1603</v>
+        <v>1612</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -9856,7 +9871,7 @@
         <v>44</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1604</v>
+        <v>1613</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -9865,19 +9880,19 @@
         <v>151</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1605</v>
+        <v>1614</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1606</v>
+        <v>1615</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1607</v>
+        <v>1616</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1608</v>
+        <v>1617</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1609</v>
+        <v>1618</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -9886,13 +9901,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1610</v>
+        <v>1619</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1611</v>
+        <v>1620</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -9901,7 +9916,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1612</v>
+        <v>1621</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -9910,19 +9925,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1613</v>
+        <v>1622</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1614</v>
+        <v>1623</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1615</v>
+        <v>1624</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1616</v>
+        <v>1625</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1617</v>
+        <v>1626</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -9931,13 +9946,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1618</v>
+        <v>1627</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1619</v>
+        <v>1628</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>170</v>
@@ -9946,7 +9961,7 @@
         <v>44</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1612</v>
+        <v>1621</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -9955,19 +9970,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1620</v>
+        <v>1629</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>190</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1621</v>
+        <v>1630</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>604</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1622</v>
+        <v>1631</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -9976,13 +9991,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1596</v>
+        <v>1605</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1623</v>
+        <v>1632</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -9991,7 +10006,7 @@
         <v>44</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1624</v>
+        <v>1633</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>594</v>
@@ -10000,19 +10015,19 @@
         <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1625</v>
+        <v>1634</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1626</v>
+        <v>1635</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1627</v>
+        <v>1636</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1628</v>
+        <v>1637</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1629</v>
+        <v>1638</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -10021,13 +10036,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1630</v>
+        <v>1639</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1631</v>
+        <v>1640</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -10036,28 +10051,28 @@
         <v>44</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1624</v>
+        <v>1633</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1582</v>
+        <v>1591</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1632</v>
+        <v>1641</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1633</v>
+        <v>1642</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1634</v>
+        <v>1643</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1635</v>
+        <v>1644</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1636</v>
+        <v>1645</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -10066,13 +10081,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1630</v>
+        <v>1639</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1637</v>
+        <v>1646</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -10081,7 +10096,7 @@
         <v>44</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1638</v>
+        <v>1647</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -10090,34 +10105,34 @@
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
+        <v>1648</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>1649</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>1650</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>1651</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>1652</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="6" t="s">
         <v>1639</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>1640</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>1641</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>1642</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>1643</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>1630</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>170</v>
@@ -10126,7 +10141,7 @@
         <v>44</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1638</v>
+        <v>1647</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -10135,19 +10150,19 @@
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>190</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>604</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1647</v>
+        <v>1656</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -10156,13 +10171,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1630</v>
+        <v>1639</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1648</v>
+        <v>1657</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -10171,7 +10186,7 @@
         <v>44</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1649</v>
+        <v>1658</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>150</v>
@@ -10180,19 +10195,19 @@
         <v>188</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1650</v>
+        <v>1659</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1651</v>
+        <v>1660</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1652</v>
+        <v>1661</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1082</v>
+        <v>1091</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1653</v>
+        <v>1662</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>6</v>
@@ -10204,12 +10219,12 @@
         <v>157</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>1654</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1655</v>
+        <v>1664</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -10218,7 +10233,7 @@
         <v>44</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1656</v>
+        <v>1665</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>160</v>
@@ -10227,19 +10242,19 @@
         <v>151</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1657</v>
+        <v>1666</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1658</v>
+        <v>1667</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1660</v>
+        <v>1669</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1661</v>
+        <v>1670</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -10248,13 +10263,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1630</v>
+        <v>1639</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
-        <v>1662</v>
+        <v>1671</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>110</v>
@@ -10263,7 +10278,7 @@
         <v>44</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1663</v>
+        <v>1672</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>150</v>
@@ -10272,19 +10287,19 @@
         <v>188</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>1664</v>
+        <v>1673</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>1665</v>
+        <v>1674</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>1666</v>
+        <v>1675</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1667</v>
+        <v>1676</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>1668</v>
+        <v>1677</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>166</v>
@@ -10293,13 +10308,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>1630</v>
+        <v>1639</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
-        <v>1669</v>
+        <v>1678</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>127</v>
@@ -10308,7 +10323,7 @@
         <v>44</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1670</v>
+        <v>1679</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>594</v>
@@ -10317,19 +10332,19 @@
         <v>188</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>1671</v>
+        <v>1680</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1672</v>
+        <v>1681</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>1673</v>
+        <v>1682</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1674</v>
+        <v>1683</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>1675</v>
+        <v>1684</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>166</v>
@@ -10338,13 +10353,13 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>1676</v>
+        <v>1685</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
-        <v>1677</v>
+        <v>1686</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>127</v>
@@ -10353,7 +10368,7 @@
         <v>44</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1678</v>
+        <v>1687</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>160</v>
@@ -10362,19 +10377,19 @@
         <v>254</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>1679</v>
+        <v>1688</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>1680</v>
+        <v>1689</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>1681</v>
+        <v>1690</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>1682</v>
+        <v>1691</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>1683</v>
+        <v>1692</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>166</v>
@@ -10383,7 +10398,7 @@
         <v>4</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>1676</v>
+        <v>1685</v>
       </c>
       <c r="O15" s="6"/>
     </row>
@@ -10478,7 +10493,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1684</v>
+        <v>1693</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -10487,7 +10502,7 @@
         <v>48</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1685</v>
+        <v>1694</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -10496,19 +10511,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1686</v>
+        <v>1695</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1687</v>
+        <v>1696</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1688</v>
+        <v>1697</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1689</v>
+        <v>1698</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1690</v>
+        <v>1699</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -10517,13 +10532,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1691</v>
+        <v>1700</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1692</v>
+        <v>1701</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -10532,7 +10547,7 @@
         <v>48</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1693</v>
+        <v>1702</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>160</v>
@@ -10541,19 +10556,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1694</v>
+        <v>1703</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1695</v>
+        <v>1704</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1696</v>
+        <v>1705</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1697</v>
+        <v>1706</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1698</v>
+        <v>1707</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -10562,13 +10577,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1691</v>
+        <v>1700</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1699</v>
+        <v>1708</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -10577,7 +10592,7 @@
         <v>48</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1700</v>
+        <v>1709</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>160</v>
@@ -10586,19 +10601,19 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1701</v>
+        <v>1710</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1702</v>
+        <v>1711</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1703</v>
+        <v>1712</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1704</v>
+        <v>1713</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>1705</v>
+        <v>1714</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>166</v>
@@ -10607,13 +10622,13 @@
         <v>4</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1691</v>
+        <v>1700</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1706</v>
+        <v>1715</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -10622,7 +10637,7 @@
         <v>48</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1707</v>
+        <v>1716</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -10631,19 +10646,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1708</v>
+        <v>1717</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1709</v>
+        <v>1718</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1710</v>
+        <v>1719</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1711</v>
+        <v>1720</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1712</v>
+        <v>1721</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -10652,13 +10667,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1691</v>
+        <v>1700</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1713</v>
+        <v>1722</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>110</v>
@@ -10667,7 +10682,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1714</v>
+        <v>1723</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>150</v>
@@ -10676,19 +10691,19 @@
         <v>188</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1715</v>
+        <v>1724</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1716</v>
+        <v>1725</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1717</v>
+        <v>1726</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1718</v>
+        <v>1727</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1719</v>
+        <v>1728</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>6</v>
@@ -10700,12 +10715,12 @@
         <v>157</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>1720</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1721</v>
+        <v>1730</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -10714,7 +10729,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1722</v>
+        <v>1731</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -10723,19 +10738,19 @@
         <v>188</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1723</v>
+        <v>1732</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1724</v>
+        <v>1733</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1725</v>
+        <v>1734</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1726</v>
+        <v>1735</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1727</v>
+        <v>1736</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>6</v>
@@ -10747,12 +10762,12 @@
         <v>157</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>1728</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1729</v>
+        <v>1738</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -10761,7 +10776,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1730</v>
+        <v>1739</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -10770,19 +10785,19 @@
         <v>151</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1731</v>
+        <v>1740</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1733</v>
+        <v>1742</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1711</v>
+        <v>1720</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1734</v>
+        <v>1743</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>166</v>
@@ -10791,13 +10806,13 @@
         <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>1691</v>
+        <v>1700</v>
       </c>
       <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1735</v>
+        <v>1744</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -10806,7 +10821,7 @@
         <v>48</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1736</v>
+        <v>1745</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>160</v>
@@ -10815,19 +10830,19 @@
         <v>151</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1737</v>
+        <v>1746</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1738</v>
+        <v>1747</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1739</v>
+        <v>1748</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1711</v>
+        <v>1720</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1740</v>
+        <v>1749</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>166</v>
@@ -10836,13 +10851,13 @@
         <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>1691</v>
+        <v>1700</v>
       </c>
       <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1741</v>
+        <v>1750</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -10851,7 +10866,7 @@
         <v>48</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1742</v>
+        <v>1751</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -10860,19 +10875,19 @@
         <v>188</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1743</v>
+        <v>1752</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1744</v>
+        <v>1753</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1745</v>
+        <v>1754</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1711</v>
+        <v>1720</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1746</v>
+        <v>1755</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>166</v>
@@ -10881,13 +10896,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>1691</v>
+        <v>1700</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1747</v>
+        <v>1756</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>110</v>
@@ -10896,7 +10911,7 @@
         <v>48</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
@@ -10905,19 +10920,19 @@
         <v>188</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1749</v>
+        <v>1758</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1750</v>
+        <v>1759</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1751</v>
+        <v>1760</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1711</v>
+        <v>1720</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1752</v>
+        <v>1761</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>166</v>
@@ -10926,13 +10941,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>1691</v>
+        <v>1700</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
-        <v>1753</v>
+        <v>1762</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>110</v>
@@ -10941,7 +10956,7 @@
         <v>48</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1754</v>
+        <v>1763</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>150</v>
@@ -10950,19 +10965,19 @@
         <v>188</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>1755</v>
+        <v>1764</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>1756</v>
+        <v>1765</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>1757</v>
+        <v>1766</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1758</v>
+        <v>1767</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>1759</v>
+        <v>1768</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>166</v>
@@ -10971,10 +10986,10 @@
         <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>1691</v>
+        <v>1700</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>1760</v>
+        <v>1769</v>
       </c>
     </row>
   </sheetData>
@@ -11789,8 +11804,8 @@
       <c r="L8" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="M8" s="10" t="s">
-        <v>5</v>
+      <c r="M8" s="9" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>201</v>
@@ -11836,8 +11851,8 @@
       <c r="L9" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="M9" s="10" t="s">
-        <v>5</v>
+      <c r="M9" s="9" t="s">
+        <v>4</v>
       </c>
       <c r="N9" s="6" t="s">
         <v>201</v>
@@ -11883,8 +11898,8 @@
       <c r="L10" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="M10" s="10" t="s">
-        <v>5</v>
+      <c r="M10" s="9" t="s">
+        <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
         <v>201</v>
@@ -11975,8 +11990,8 @@
       <c r="L12" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="M12" s="10" t="s">
-        <v>5</v>
+      <c r="M12" s="9" t="s">
+        <v>4</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>240</v>
@@ -12607,8 +12622,8 @@
       <c r="L26" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="M26" s="10" t="s">
-        <v>5</v>
+      <c r="M26" s="9" t="s">
+        <v>4</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>329</v>
@@ -15481,7 +15496,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="true" style="0"/>
@@ -17820,8 +17835,55 @@
       </c>
       <c r="O51" s="6"/>
     </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="7" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>1066</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>1069</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M52" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>1070</v>
+      </c>
+      <c r="O52" s="6" t="s">
+        <v>1071</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O51"/>
+  <autoFilter ref="A1:O52"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
@@ -17911,7 +17973,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
-        <v>1063</v>
+        <v>1072</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>110</v>
@@ -17920,7 +17982,7 @@
         <v>28</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1064</v>
+        <v>1073</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>160</v>
@@ -17929,19 +17991,19 @@
         <v>151</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1065</v>
+        <v>1074</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>1066</v>
+        <v>1075</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1067</v>
+        <v>1076</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1068</v>
+        <v>1077</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>1069</v>
+        <v>1078</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>166</v>
@@ -17950,13 +18012,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>1070</v>
+        <v>1079</v>
       </c>
       <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="7" t="s">
-        <v>1071</v>
+        <v>1080</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>110</v>
@@ -17965,7 +18027,7 @@
         <v>28</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1072</v>
+        <v>1081</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>594</v>
@@ -17974,19 +18036,19 @@
         <v>151</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1073</v>
+        <v>1082</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>1074</v>
+        <v>1083</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1075</v>
+        <v>1084</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1076</v>
+        <v>1085</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>1077</v>
+        <v>1086</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>166</v>
@@ -17995,13 +18057,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>1070</v>
+        <v>1079</v>
       </c>
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="7" t="s">
-        <v>1078</v>
+        <v>1087</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>110</v>
@@ -18010,7 +18072,7 @@
         <v>28</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1072</v>
+        <v>1081</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>150</v>
@@ -18019,34 +18081,34 @@
         <v>188</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>1090</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>1092</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>1079</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>1080</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>1081</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>1082</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>1083</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>1070</v>
       </c>
       <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
-        <v>1084</v>
+        <v>1093</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>110</v>
@@ -18055,7 +18117,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
@@ -18064,19 +18126,19 @@
         <v>151</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1087</v>
+        <v>1096</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1089</v>
+        <v>1098</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>1090</v>
+        <v>1099</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>166</v>
@@ -18085,13 +18147,13 @@
         <v>4</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>1070</v>
+        <v>1079</v>
       </c>
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="7" t="s">
-        <v>1091</v>
+        <v>1100</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>110</v>
@@ -18100,7 +18162,7 @@
         <v>28</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1092</v>
+        <v>1101</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>160</v>
@@ -18109,19 +18171,19 @@
         <v>151</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1093</v>
+        <v>1102</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1094</v>
+        <v>1103</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1095</v>
+        <v>1104</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1096</v>
+        <v>1105</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>166</v>
@@ -18130,13 +18192,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>1070</v>
+        <v>1079</v>
       </c>
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
-        <v>1098</v>
+        <v>1107</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>110</v>
@@ -18145,7 +18207,7 @@
         <v>28</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1099</v>
+        <v>1108</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>160</v>
@@ -18154,19 +18216,19 @@
         <v>188</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1101</v>
+        <v>1110</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1102</v>
+        <v>1111</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1103</v>
+        <v>1112</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>1104</v>
+        <v>1113</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>166</v>
@@ -18175,13 +18237,13 @@
         <v>4</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>1105</v>
+        <v>1114</v>
       </c>
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>110</v>
@@ -18190,7 +18252,7 @@
         <v>28</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1107</v>
+        <v>1116</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>160</v>
@@ -18199,19 +18261,19 @@
         <v>188</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1108</v>
+        <v>1117</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1111</v>
+        <v>1120</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>1112</v>
+        <v>1121</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>6</v>
@@ -18223,12 +18285,12 @@
         <v>157</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>1113</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
-        <v>1114</v>
+        <v>1123</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>110</v>
@@ -18237,7 +18299,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1115</v>
+        <v>1124</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>150</v>
@@ -18246,19 +18308,19 @@
         <v>188</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1117</v>
+        <v>1126</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>6</v>
@@ -18270,12 +18332,12 @@
         <v>157</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>1121</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
-        <v>1122</v>
+        <v>1131</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>110</v>
@@ -18284,7 +18346,7 @@
         <v>28</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1123</v>
+        <v>1132</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>160</v>
@@ -18293,19 +18355,19 @@
         <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1124</v>
+        <v>1133</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1125</v>
+        <v>1134</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1126</v>
+        <v>1135</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1127</v>
+        <v>1136</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>1128</v>
+        <v>1137</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>6</v>
@@ -18317,12 +18379,12 @@
         <v>157</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="7" t="s">
-        <v>1130</v>
+        <v>1139</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>104</v>
@@ -18331,7 +18393,7 @@
         <v>28</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1131</v>
+        <v>1140</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>150</v>
@@ -18340,19 +18402,19 @@
         <v>254</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>1132</v>
+        <v>1141</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>1133</v>
+        <v>1142</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>1134</v>
+        <v>1143</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>1135</v>
+        <v>1144</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>1136</v>
+        <v>1145</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>6</v>

--- a/docs/test-cases/test-cases.xlsx
+++ b/docs/test-cases/test-cases.xlsx
@@ -1833,20 +1833,20 @@
   <si>
     <t>Mở /students/{user_id} — chỉ Admin thấy nút “Reset mật khẩu” (KHÔNG còn nút “Gửi email”)
 Bấm “Reset mật khẩu” ⇒ xác nhận ⇒ đọc flash trên màn hình
-Đăng xuất rồi đăng nhập bằng tài khoản sinh viên vừa reset (mật khẩu "password")
+Đăng xuất rồi đăng nhập bằng tài khoản sinh viên vừa reset (mật khẩu "password") ⇒ vào THẲNG dashboard (không bị đưa sang trang Đổi mật khẩu)
 Đăng nhập giảng viên rồi gọi trực tiếp route reset (case âm)</t>
   </si>
   <si>
     <t>POST /students/{id}/reset-password</t>
   </si>
   <si>
-    <t>Reset: flash thành công, mật khẩu lưu là hash của "password", must_change_password=1, sinh viên đăng nhập bị đưa sang trang Đổi mật khẩu (chưa vào dashboard) · Giảng viên gọi trực tiếp ⇒ 403, không đổi dữ liệu · Không còn chuỗi “Gửi email” trên bất kỳ màn hình nào</t>
+    <t>Reset: flash thành công, mật khẩu lưu là hash của "password", must_change_password=0, sinh viên đăng nhập bằng "password" vào THẲNG dashboard (2026-10-10: không còn ép đổi) · Giảng viên gọi trực tiếp ⇒ 403, không đổi dữ liệu · Không còn chuỗi “Gửi email” trên bất kỳ màn hình nào</t>
   </si>
   <si>
     <t>tests/Feature/StudentQuickActionsTest.php</t>
   </si>
   <si>
-    <t>2026-10-10: gỡ hẳn Gửi email (route `students.send-email`, `StudentController::sendEmail()`, `App\Mail\StudentNotification`, view `emails/student-notification.blade.php`). Reset giữ nguyên: 5b (về "password" + buộc đổi ở lần đăng nhập sau), 5c (đơn lẻ từng sinh viên, không bulk).</t>
+    <t>2026-10-10: (1) gỡ hẳn Gửi email (route `students.send-email`, `StudentController::sendEmail()`, `App\Mail\StudentNotification`, view `emails/student-notification.blade.php`); (2) reset KHÔNG bật cờ buộc đổi nữa — 5b nay là "về 'password' + đăng nhập ngay", 5c (đơn lẻ từng sinh viên, không bulk) giữ nguyên; cơ chế buộc-đổi (middleware + gate login) vẫn còn, test set cờ trực tiếp.</t>
   </si>
   <si>
     <t>TC-ADMIN-30</t>
